--- a/metrics.xlsx
+++ b/metrics.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\github\segmentation_biomarcers_pp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{873A1A13-4981-49F1-AD8A-3D3341208A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEBF2C0F-E130-4297-8684-33A86C02E195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист1 (2)" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="FromArray_1" localSheetId="1">_xlfn.ANCHORARRAY('Лист1 (2)'!$A$32)</definedName>
     <definedName name="FromArray_1">_xlfn.ANCHORARRAY(Лист1!$B$32)</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -61,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="300">
   <si>
     <t>model,class_name,iou,dice,precision,recall</t>
   </si>
@@ -793,12 +795,183 @@
   </si>
   <si>
     <t>0.49235315385095235</t>
+  </si>
+  <si>
+    <t>model</t>
+  </si>
+  <si>
+    <t>class_name</t>
+  </si>
+  <si>
+    <t>iou</t>
+  </si>
+  <si>
+    <t>dice</t>
+  </si>
+  <si>
+    <t>precision</t>
+  </si>
+  <si>
+    <t>recall</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_1_Fold_2,drusen,0.3425674963390841,0.5103169818622869,0.5187938465076949,0.502112680181943</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_1_Fold_2,edema,0.38120064752059374,0.5519844610627581,0.5846875673362015,0.5227459136355913</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_1_Fold_2,epiretinal_fibrosis,0.6409633336660325,0.7812037240759955,0.745143038060556,0.820932173284669</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_1_Fold_2,fibrosis,0.3574449288673427,0.5266437278830841,0.5872720553747234,0.47736218823611226</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_1_Fold_2,geographic_atrophy,0.7303666165567899,0.8441755747809409,0.8254855329802061,0.863731555140654</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_1_Fold_2,hard_exudates,0.5804658416086753,0.7345503158965445,0.733439257637178,0.7356647454597933</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_1_Fold_2,hemorrhages,0.5406093622636293,0.7018123808741598,0.7063945123958123,0.6972893115719454</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_1_Fold_2,laser_coagulates,0.5389543154933164,0.7004162632606192,0.5899125153055977,0.8618622515070996</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_1_Fold_2,macular_hole,0.7820271011408995,0.8776826128404285,0.805952762526959,0.9634277474506203</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_1_Fold_2,microaneurysms,0.14158069503935616,0.24804325380515507,0.23755112456301342,0.2595050409624603</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_1_Fold_2,neovascularization,0.6156706749108222,0.7621239705236396,0.7009449404708502,0.8350037606739735</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_1_Fold_2,soft_exudates,0.3455091912660255,0.5135738849036426,0.6664586513085814,0.4177439536102479</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_1_Fold_2,subretinal_hemorrhage,0.513429134807789,0.6784977545354264,0.6657594123993356,0.6917330648943297</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_1_Fold_2,venous_anomalies,0.20385106298103195,0.33866492168266477,0.3185036885850022,0.3615510456732886</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_1_Fold_2,MEAN,0.47961717160438483,0.6264064162848103,0.6204499218179794,0.6436189594487661</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_2_Fold_3,drusen,0.3807688124017207,0.5515315945460968,0.5718603226464947,0.5325985598839772</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_2_Fold_3,edema,0.28826615048698107,0.4475257700095788,0.5376330066679861,0.383286921381193</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_2_Fold_3,epiretinal_fibrosis,0.6163962639012817,0.7626796444252693,0.6977862994683831,0.8408805991119593</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_2_Fold_3,fibrosis,0.4447708433029288,0.6156974240788614,0.6073625256848619,0.624264266804212</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_2_Fold_3,geographic_atrophy,0.7398764808297295,0.8504931114154608,0.7920493630268552,0.9182488706653593</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_2_Fold_3,hard_exudates,0.5735483617490933,0.7289872693986473,0.7683466664197762,0.6934638275695917</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_2_Fold_3,hemorrhages,0.5200570205778495,0.6842598843826924,0.6780194056684787,0.6906163047348993</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_2_Fold_3,laser_coagulates,0.6039018599539585,0.7530409123302519,0.7130286871943761,0.7978107570804295</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_2_Fold_3,macular_hole,0.8069221297539,0.8931454393818306,0.8141924975516761,0.9890549417644022</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_2_Fold_3,microaneurysms,0.12520947055792786,0.22255317580262374,0.26171546484687597,0.19358562441067292</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_2_Fold_3,neovascularization,0.6462370565448473,0.7851081397732372,0.7209606557083512,0.8617855178460372</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_2_Fold_3,soft_exudates,0.4991055936174937,0.6658711644362574,0.6486812600478785,0.6839969258564711</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_2_Fold_3,subretinal_hemorrhage,0.45535743056222977,0.62576714283352,0.6233215333647896,0.6282320186498123</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_2_Fold_3,venous_anomalies,0.34038821547678316,0.5078949688552808,0.5225746440582746,0.4940174942351529</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_2_Fold_3,MEAN,0.5029146921226232,0.649611117262115,0.6398237380253613,0.6665601878567264</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_3_Fold_1,drusen,0.3684293820361427,0.5384704346057543,0.5201188880886478,0.5581643533008027</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_3_Fold_1,edema,0.41650001275612514,0.5880691973249319,0.6062428205778808,0.5709534596718977</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_3_Fold_1,epiretinal_fibrosis,0.6275894462025496,0.7711888863212101,0.7490729639101212,0.7946504564010587</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_3_Fold_1,fibrosis,0.3971015403907574,0.5684648236515314,0.5739224235183331,0.5631100419527791</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_3_Fold_1,geographic_atrophy,0.7991647219849086,0.8883730458023199,0.8308156028333379,0.9544990611138338</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_3_Fold_1,hard_exudates,0.48091135571277377,0.6494802728841356,0.6878065877316693,0.615199791532289</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_3_Fold_1,hemorrhages,0.582338408774168,0.7360478713593301,0.77185433857516,0.7034162594423673</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_3_Fold_1,laser_coagulates,0.643288723463459,0.7829284218632483,0.7108752700678214,0.8712354150181105</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_3_Fold_1,macular_hole,0.7687007446901396,0.8692264612856361,0.7807264470014121,0.9803556389708654</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_3_Fold_1,microaneurysms,0.11284045129749536,0.20279717755753965,0.2603924331035393,0.16606570749632563</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_3_Fold_1,neovascularization,0.5817155776002738,0.7355501657040431,0.6773527011326,0.8046881656454155</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_3_Fold_1,soft_exudates,0.527657007718683,0.6908055997552177,0.7771912442594842,0.6217026770873036</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_3_Fold_1,subretinal_hemorrhage,0.5435281678781153,0.7042672484886392,0.7216593775851909,0.6876936987516415</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_3_Fold_1,venous_anomalies,0.0,0.0,0.0,0.0</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_3_Fold_1,MEAN,0.4892689671789708,0.6232621147573955,0.6191450784560856,0.635123909027478</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_1_Fold_2</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_2_Fold_3</t>
+  </si>
+  <si>
+    <t>Deeplab_TVERSKY_3_Fold_1</t>
+  </si>
+  <si>
+    <t>Deeplab DICE</t>
+  </si>
+  <si>
+    <t>Deeplab Tversky</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="0.000"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -816,7 +989,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -824,15 +997,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1113,7 +1312,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24.88671875" customWidth="1"/>
@@ -2098,11 +2297,2978 @@
         <v>239</v>
       </c>
     </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>250</v>
+      </c>
+      <c r="B47" t="str" cm="1">
+        <f t="array" ref="B47:G47">_xlfn.TEXTSPLIT(A47,",")</f>
+        <v>Deeplab_TVERSKY_1_Fold_2</v>
+      </c>
+      <c r="C47" t="str">
+        <v>drusen</v>
+      </c>
+      <c r="D47" t="str">
+        <v>0.3425674963390841</v>
+      </c>
+      <c r="E47" t="str">
+        <v>0.5103169818622869</v>
+      </c>
+      <c r="F47" t="str">
+        <v>0.5187938465076949</v>
+      </c>
+      <c r="G47" t="str">
+        <v>0.502112680181943</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>251</v>
+      </c>
+      <c r="B48" t="str" cm="1">
+        <f t="array" ref="B48:G48">_xlfn.TEXTSPLIT(A48,",")</f>
+        <v>Deeplab_TVERSKY_1_Fold_2</v>
+      </c>
+      <c r="C48" t="str">
+        <v>edema</v>
+      </c>
+      <c r="D48" t="str">
+        <v>0.38120064752059374</v>
+      </c>
+      <c r="E48" t="str">
+        <v>0.5519844610627581</v>
+      </c>
+      <c r="F48" t="str">
+        <v>0.5846875673362015</v>
+      </c>
+      <c r="G48" t="str">
+        <v>0.5227459136355913</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>252</v>
+      </c>
+      <c r="B49" t="str" cm="1">
+        <f t="array" ref="B49:G49">_xlfn.TEXTSPLIT(A49,",")</f>
+        <v>Deeplab_TVERSKY_1_Fold_2</v>
+      </c>
+      <c r="C49" t="str">
+        <v>epiretinal_fibrosis</v>
+      </c>
+      <c r="D49" t="str">
+        <v>0.6409633336660325</v>
+      </c>
+      <c r="E49" t="str">
+        <v>0.7812037240759955</v>
+      </c>
+      <c r="F49" t="str">
+        <v>0.745143038060556</v>
+      </c>
+      <c r="G49" t="str">
+        <v>0.820932173284669</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>253</v>
+      </c>
+      <c r="B50" t="str" cm="1">
+        <f t="array" ref="B50:G50">_xlfn.TEXTSPLIT(A50,",")</f>
+        <v>Deeplab_TVERSKY_1_Fold_2</v>
+      </c>
+      <c r="C50" t="str">
+        <v>fibrosis</v>
+      </c>
+      <c r="D50" t="str">
+        <v>0.3574449288673427</v>
+      </c>
+      <c r="E50" t="str">
+        <v>0.5266437278830841</v>
+      </c>
+      <c r="F50" t="str">
+        <v>0.5872720553747234</v>
+      </c>
+      <c r="G50" t="str">
+        <v>0.47736218823611226</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>254</v>
+      </c>
+      <c r="B51" t="str" cm="1">
+        <f t="array" ref="B51:G51">_xlfn.TEXTSPLIT(A51,",")</f>
+        <v>Deeplab_TVERSKY_1_Fold_2</v>
+      </c>
+      <c r="C51" t="str">
+        <v>geographic_atrophy</v>
+      </c>
+      <c r="D51" t="str">
+        <v>0.7303666165567899</v>
+      </c>
+      <c r="E51" t="str">
+        <v>0.8441755747809409</v>
+      </c>
+      <c r="F51" t="str">
+        <v>0.8254855329802061</v>
+      </c>
+      <c r="G51" t="str">
+        <v>0.863731555140654</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>255</v>
+      </c>
+      <c r="B52" t="str" cm="1">
+        <f t="array" ref="B52:G52">_xlfn.TEXTSPLIT(A52,",")</f>
+        <v>Deeplab_TVERSKY_1_Fold_2</v>
+      </c>
+      <c r="C52" t="str">
+        <v>hard_exudates</v>
+      </c>
+      <c r="D52" t="str">
+        <v>0.5804658416086753</v>
+      </c>
+      <c r="E52" t="str">
+        <v>0.7345503158965445</v>
+      </c>
+      <c r="F52" t="str">
+        <v>0.733439257637178</v>
+      </c>
+      <c r="G52" t="str">
+        <v>0.7356647454597933</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>256</v>
+      </c>
+      <c r="B53" t="str" cm="1">
+        <f t="array" ref="B53:G53">_xlfn.TEXTSPLIT(A53,",")</f>
+        <v>Deeplab_TVERSKY_1_Fold_2</v>
+      </c>
+      <c r="C53" t="str">
+        <v>hemorrhages</v>
+      </c>
+      <c r="D53" t="str">
+        <v>0.5406093622636293</v>
+      </c>
+      <c r="E53" t="str">
+        <v>0.7018123808741598</v>
+      </c>
+      <c r="F53" t="str">
+        <v>0.7063945123958123</v>
+      </c>
+      <c r="G53" t="str">
+        <v>0.6972893115719454</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>257</v>
+      </c>
+      <c r="B54" t="str" cm="1">
+        <f t="array" ref="B54:G54">_xlfn.TEXTSPLIT(A54,",")</f>
+        <v>Deeplab_TVERSKY_1_Fold_2</v>
+      </c>
+      <c r="C54" t="str">
+        <v>laser_coagulates</v>
+      </c>
+      <c r="D54" t="str">
+        <v>0.5389543154933164</v>
+      </c>
+      <c r="E54" t="str">
+        <v>0.7004162632606192</v>
+      </c>
+      <c r="F54" t="str">
+        <v>0.5899125153055977</v>
+      </c>
+      <c r="G54" t="str">
+        <v>0.8618622515070996</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>258</v>
+      </c>
+      <c r="B55" t="str" cm="1">
+        <f t="array" ref="B55:G55">_xlfn.TEXTSPLIT(A55,",")</f>
+        <v>Deeplab_TVERSKY_1_Fold_2</v>
+      </c>
+      <c r="C55" t="str">
+        <v>macular_hole</v>
+      </c>
+      <c r="D55" t="str">
+        <v>0.7820271011408995</v>
+      </c>
+      <c r="E55" t="str">
+        <v>0.8776826128404285</v>
+      </c>
+      <c r="F55" t="str">
+        <v>0.805952762526959</v>
+      </c>
+      <c r="G55" t="str">
+        <v>0.9634277474506203</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>259</v>
+      </c>
+      <c r="B56" t="str" cm="1">
+        <f t="array" ref="B56:G56">_xlfn.TEXTSPLIT(A56,",")</f>
+        <v>Deeplab_TVERSKY_1_Fold_2</v>
+      </c>
+      <c r="C56" t="str">
+        <v>microaneurysms</v>
+      </c>
+      <c r="D56" t="str">
+        <v>0.14158069503935616</v>
+      </c>
+      <c r="E56" t="str">
+        <v>0.24804325380515507</v>
+      </c>
+      <c r="F56" t="str">
+        <v>0.23755112456301342</v>
+      </c>
+      <c r="G56" t="str">
+        <v>0.2595050409624603</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>260</v>
+      </c>
+      <c r="B57" t="str" cm="1">
+        <f t="array" ref="B57:G57">_xlfn.TEXTSPLIT(A57,",")</f>
+        <v>Deeplab_TVERSKY_1_Fold_2</v>
+      </c>
+      <c r="C57" t="str">
+        <v>neovascularization</v>
+      </c>
+      <c r="D57" t="str">
+        <v>0.6156706749108222</v>
+      </c>
+      <c r="E57" t="str">
+        <v>0.7621239705236396</v>
+      </c>
+      <c r="F57" t="str">
+        <v>0.7009449404708502</v>
+      </c>
+      <c r="G57" t="str">
+        <v>0.8350037606739735</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>261</v>
+      </c>
+      <c r="B58" t="str" cm="1">
+        <f t="array" ref="B58:G58">_xlfn.TEXTSPLIT(A58,",")</f>
+        <v>Deeplab_TVERSKY_1_Fold_2</v>
+      </c>
+      <c r="C58" t="str">
+        <v>soft_exudates</v>
+      </c>
+      <c r="D58" t="str">
+        <v>0.3455091912660255</v>
+      </c>
+      <c r="E58" t="str">
+        <v>0.5135738849036426</v>
+      </c>
+      <c r="F58" t="str">
+        <v>0.6664586513085814</v>
+      </c>
+      <c r="G58" t="str">
+        <v>0.4177439536102479</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>262</v>
+      </c>
+      <c r="B59" t="str" cm="1">
+        <f t="array" ref="B59:G59">_xlfn.TEXTSPLIT(A59,",")</f>
+        <v>Deeplab_TVERSKY_1_Fold_2</v>
+      </c>
+      <c r="C59" t="str">
+        <v>subretinal_hemorrhage</v>
+      </c>
+      <c r="D59" t="str">
+        <v>0.513429134807789</v>
+      </c>
+      <c r="E59" t="str">
+        <v>0.6784977545354264</v>
+      </c>
+      <c r="F59" t="str">
+        <v>0.6657594123993356</v>
+      </c>
+      <c r="G59" t="str">
+        <v>0.6917330648943297</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>263</v>
+      </c>
+      <c r="B60" t="str" cm="1">
+        <f t="array" ref="B60:G60">_xlfn.TEXTSPLIT(A60,",")</f>
+        <v>Deeplab_TVERSKY_1_Fold_2</v>
+      </c>
+      <c r="C60" t="str">
+        <v>venous_anomalies</v>
+      </c>
+      <c r="D60" t="str">
+        <v>0.20385106298103195</v>
+      </c>
+      <c r="E60" t="str">
+        <v>0.33866492168266477</v>
+      </c>
+      <c r="F60" t="str">
+        <v>0.3185036885850022</v>
+      </c>
+      <c r="G60" t="str">
+        <v>0.3615510456732886</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>264</v>
+      </c>
+      <c r="B61" t="str" cm="1">
+        <f t="array" ref="B61:G61">_xlfn.TEXTSPLIT(A61,",")</f>
+        <v>Deeplab_TVERSKY_1_Fold_2</v>
+      </c>
+      <c r="C61" t="str">
+        <v>MEAN</v>
+      </c>
+      <c r="D61" t="str">
+        <v>0.47961717160438483</v>
+      </c>
+      <c r="E61" t="str">
+        <v>0.6264064162848103</v>
+      </c>
+      <c r="F61" t="str">
+        <v>0.6204499218179794</v>
+      </c>
+      <c r="G61" t="str">
+        <v>0.6436189594487661</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>265</v>
+      </c>
+      <c r="B62" t="str" cm="1">
+        <f t="array" ref="B62:G62">_xlfn.TEXTSPLIT(A62,",")</f>
+        <v>Deeplab_TVERSKY_2_Fold_3</v>
+      </c>
+      <c r="C62" t="str">
+        <v>drusen</v>
+      </c>
+      <c r="D62" t="str">
+        <v>0.3807688124017207</v>
+      </c>
+      <c r="E62" t="str">
+        <v>0.5515315945460968</v>
+      </c>
+      <c r="F62" t="str">
+        <v>0.5718603226464947</v>
+      </c>
+      <c r="G62" t="str">
+        <v>0.5325985598839772</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>266</v>
+      </c>
+      <c r="B63" t="str" cm="1">
+        <f t="array" ref="B63:G63">_xlfn.TEXTSPLIT(A63,",")</f>
+        <v>Deeplab_TVERSKY_2_Fold_3</v>
+      </c>
+      <c r="C63" t="str">
+        <v>edema</v>
+      </c>
+      <c r="D63" t="str">
+        <v>0.28826615048698107</v>
+      </c>
+      <c r="E63" t="str">
+        <v>0.4475257700095788</v>
+      </c>
+      <c r="F63" t="str">
+        <v>0.5376330066679861</v>
+      </c>
+      <c r="G63" t="str">
+        <v>0.383286921381193</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>267</v>
+      </c>
+      <c r="B64" t="str" cm="1">
+        <f t="array" ref="B64:G64">_xlfn.TEXTSPLIT(A64,",")</f>
+        <v>Deeplab_TVERSKY_2_Fold_3</v>
+      </c>
+      <c r="C64" t="str">
+        <v>epiretinal_fibrosis</v>
+      </c>
+      <c r="D64" t="str">
+        <v>0.6163962639012817</v>
+      </c>
+      <c r="E64" t="str">
+        <v>0.7626796444252693</v>
+      </c>
+      <c r="F64" t="str">
+        <v>0.6977862994683831</v>
+      </c>
+      <c r="G64" t="str">
+        <v>0.8408805991119593</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>268</v>
+      </c>
+      <c r="B65" t="str" cm="1">
+        <f t="array" ref="B65:G65">_xlfn.TEXTSPLIT(A65,",")</f>
+        <v>Deeplab_TVERSKY_2_Fold_3</v>
+      </c>
+      <c r="C65" t="str">
+        <v>fibrosis</v>
+      </c>
+      <c r="D65" t="str">
+        <v>0.4447708433029288</v>
+      </c>
+      <c r="E65" t="str">
+        <v>0.6156974240788614</v>
+      </c>
+      <c r="F65" t="str">
+        <v>0.6073625256848619</v>
+      </c>
+      <c r="G65" t="str">
+        <v>0.624264266804212</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>269</v>
+      </c>
+      <c r="B66" t="str" cm="1">
+        <f t="array" ref="B66:G66">_xlfn.TEXTSPLIT(A66,",")</f>
+        <v>Deeplab_TVERSKY_2_Fold_3</v>
+      </c>
+      <c r="C66" t="str">
+        <v>geographic_atrophy</v>
+      </c>
+      <c r="D66" t="str">
+        <v>0.7398764808297295</v>
+      </c>
+      <c r="E66" t="str">
+        <v>0.8504931114154608</v>
+      </c>
+      <c r="F66" t="str">
+        <v>0.7920493630268552</v>
+      </c>
+      <c r="G66" t="str">
+        <v>0.9182488706653593</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>270</v>
+      </c>
+      <c r="B67" t="str" cm="1">
+        <f t="array" ref="B67:G67">_xlfn.TEXTSPLIT(A67,",")</f>
+        <v>Deeplab_TVERSKY_2_Fold_3</v>
+      </c>
+      <c r="C67" t="str">
+        <v>hard_exudates</v>
+      </c>
+      <c r="D67" t="str">
+        <v>0.5735483617490933</v>
+      </c>
+      <c r="E67" t="str">
+        <v>0.7289872693986473</v>
+      </c>
+      <c r="F67" t="str">
+        <v>0.7683466664197762</v>
+      </c>
+      <c r="G67" t="str">
+        <v>0.6934638275695917</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>271</v>
+      </c>
+      <c r="B68" t="str" cm="1">
+        <f t="array" ref="B68:G68">_xlfn.TEXTSPLIT(A68,",")</f>
+        <v>Deeplab_TVERSKY_2_Fold_3</v>
+      </c>
+      <c r="C68" t="str">
+        <v>hemorrhages</v>
+      </c>
+      <c r="D68" t="str">
+        <v>0.5200570205778495</v>
+      </c>
+      <c r="E68" t="str">
+        <v>0.6842598843826924</v>
+      </c>
+      <c r="F68" t="str">
+        <v>0.6780194056684787</v>
+      </c>
+      <c r="G68" t="str">
+        <v>0.6906163047348993</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>272</v>
+      </c>
+      <c r="B69" t="str" cm="1">
+        <f t="array" ref="B69:G69">_xlfn.TEXTSPLIT(A69,",")</f>
+        <v>Deeplab_TVERSKY_2_Fold_3</v>
+      </c>
+      <c r="C69" t="str">
+        <v>laser_coagulates</v>
+      </c>
+      <c r="D69" t="str">
+        <v>0.6039018599539585</v>
+      </c>
+      <c r="E69" t="str">
+        <v>0.7530409123302519</v>
+      </c>
+      <c r="F69" t="str">
+        <v>0.7130286871943761</v>
+      </c>
+      <c r="G69" t="str">
+        <v>0.7978107570804295</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>273</v>
+      </c>
+      <c r="B70" t="str" cm="1">
+        <f t="array" ref="B70:G70">_xlfn.TEXTSPLIT(A70,",")</f>
+        <v>Deeplab_TVERSKY_2_Fold_3</v>
+      </c>
+      <c r="C70" t="str">
+        <v>macular_hole</v>
+      </c>
+      <c r="D70" t="str">
+        <v>0.8069221297539</v>
+      </c>
+      <c r="E70" t="str">
+        <v>0.8931454393818306</v>
+      </c>
+      <c r="F70" t="str">
+        <v>0.8141924975516761</v>
+      </c>
+      <c r="G70" t="str">
+        <v>0.9890549417644022</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>274</v>
+      </c>
+      <c r="B71" t="str" cm="1">
+        <f t="array" ref="B71:G71">_xlfn.TEXTSPLIT(A71,",")</f>
+        <v>Deeplab_TVERSKY_2_Fold_3</v>
+      </c>
+      <c r="C71" t="str">
+        <v>microaneurysms</v>
+      </c>
+      <c r="D71" t="str">
+        <v>0.12520947055792786</v>
+      </c>
+      <c r="E71" t="str">
+        <v>0.22255317580262374</v>
+      </c>
+      <c r="F71" t="str">
+        <v>0.26171546484687597</v>
+      </c>
+      <c r="G71" t="str">
+        <v>0.19358562441067292</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>275</v>
+      </c>
+      <c r="B72" t="str" cm="1">
+        <f t="array" ref="B72:G72">_xlfn.TEXTSPLIT(A72,",")</f>
+        <v>Deeplab_TVERSKY_2_Fold_3</v>
+      </c>
+      <c r="C72" t="str">
+        <v>neovascularization</v>
+      </c>
+      <c r="D72" t="str">
+        <v>0.6462370565448473</v>
+      </c>
+      <c r="E72" t="str">
+        <v>0.7851081397732372</v>
+      </c>
+      <c r="F72" t="str">
+        <v>0.7209606557083512</v>
+      </c>
+      <c r="G72" t="str">
+        <v>0.8617855178460372</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>276</v>
+      </c>
+      <c r="B73" t="str" cm="1">
+        <f t="array" ref="B73:G73">_xlfn.TEXTSPLIT(A73,",")</f>
+        <v>Deeplab_TVERSKY_2_Fold_3</v>
+      </c>
+      <c r="C73" t="str">
+        <v>soft_exudates</v>
+      </c>
+      <c r="D73" t="str">
+        <v>0.4991055936174937</v>
+      </c>
+      <c r="E73" t="str">
+        <v>0.6658711644362574</v>
+      </c>
+      <c r="F73" t="str">
+        <v>0.6486812600478785</v>
+      </c>
+      <c r="G73" t="str">
+        <v>0.6839969258564711</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>277</v>
+      </c>
+      <c r="B74" t="str" cm="1">
+        <f t="array" ref="B74:G74">_xlfn.TEXTSPLIT(A74,",")</f>
+        <v>Deeplab_TVERSKY_2_Fold_3</v>
+      </c>
+      <c r="C74" t="str">
+        <v>subretinal_hemorrhage</v>
+      </c>
+      <c r="D74" t="str">
+        <v>0.45535743056222977</v>
+      </c>
+      <c r="E74" t="str">
+        <v>0.62576714283352</v>
+      </c>
+      <c r="F74" t="str">
+        <v>0.6233215333647896</v>
+      </c>
+      <c r="G74" t="str">
+        <v>0.6282320186498123</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>278</v>
+      </c>
+      <c r="B75" t="str" cm="1">
+        <f t="array" ref="B75:G75">_xlfn.TEXTSPLIT(A75,",")</f>
+        <v>Deeplab_TVERSKY_2_Fold_3</v>
+      </c>
+      <c r="C75" t="str">
+        <v>venous_anomalies</v>
+      </c>
+      <c r="D75" t="str">
+        <v>0.34038821547678316</v>
+      </c>
+      <c r="E75" t="str">
+        <v>0.5078949688552808</v>
+      </c>
+      <c r="F75" t="str">
+        <v>0.5225746440582746</v>
+      </c>
+      <c r="G75" t="str">
+        <v>0.4940174942351529</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>279</v>
+      </c>
+      <c r="B76" t="str" cm="1">
+        <f t="array" ref="B76:G76">_xlfn.TEXTSPLIT(A76,",")</f>
+        <v>Deeplab_TVERSKY_2_Fold_3</v>
+      </c>
+      <c r="C76" t="str">
+        <v>MEAN</v>
+      </c>
+      <c r="D76" t="str">
+        <v>0.5029146921226232</v>
+      </c>
+      <c r="E76" t="str">
+        <v>0.649611117262115</v>
+      </c>
+      <c r="F76" t="str">
+        <v>0.6398237380253613</v>
+      </c>
+      <c r="G76" t="str">
+        <v>0.6665601878567264</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>280</v>
+      </c>
+      <c r="B77" t="str" cm="1">
+        <f t="array" ref="B77:G77">_xlfn.TEXTSPLIT(A77,",")</f>
+        <v>Deeplab_TVERSKY_3_Fold_1</v>
+      </c>
+      <c r="C77" t="str">
+        <v>drusen</v>
+      </c>
+      <c r="D77" t="str">
+        <v>0.3684293820361427</v>
+      </c>
+      <c r="E77" t="str">
+        <v>0.5384704346057543</v>
+      </c>
+      <c r="F77" t="str">
+        <v>0.5201188880886478</v>
+      </c>
+      <c r="G77" t="str">
+        <v>0.5581643533008027</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>281</v>
+      </c>
+      <c r="B78" t="str" cm="1">
+        <f t="array" ref="B78:G78">_xlfn.TEXTSPLIT(A78,",")</f>
+        <v>Deeplab_TVERSKY_3_Fold_1</v>
+      </c>
+      <c r="C78" t="str">
+        <v>edema</v>
+      </c>
+      <c r="D78" t="str">
+        <v>0.41650001275612514</v>
+      </c>
+      <c r="E78" t="str">
+        <v>0.5880691973249319</v>
+      </c>
+      <c r="F78" t="str">
+        <v>0.6062428205778808</v>
+      </c>
+      <c r="G78" t="str">
+        <v>0.5709534596718977</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>282</v>
+      </c>
+      <c r="B79" t="str" cm="1">
+        <f t="array" ref="B79:G79">_xlfn.TEXTSPLIT(A79,",")</f>
+        <v>Deeplab_TVERSKY_3_Fold_1</v>
+      </c>
+      <c r="C79" t="str">
+        <v>epiretinal_fibrosis</v>
+      </c>
+      <c r="D79" t="str">
+        <v>0.6275894462025496</v>
+      </c>
+      <c r="E79" t="str">
+        <v>0.7711888863212101</v>
+      </c>
+      <c r="F79" t="str">
+        <v>0.7490729639101212</v>
+      </c>
+      <c r="G79" t="str">
+        <v>0.7946504564010587</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>283</v>
+      </c>
+      <c r="B80" t="str" cm="1">
+        <f t="array" ref="B80:G80">_xlfn.TEXTSPLIT(A80,",")</f>
+        <v>Deeplab_TVERSKY_3_Fold_1</v>
+      </c>
+      <c r="C80" t="str">
+        <v>fibrosis</v>
+      </c>
+      <c r="D80" t="str">
+        <v>0.3971015403907574</v>
+      </c>
+      <c r="E80" t="str">
+        <v>0.5684648236515314</v>
+      </c>
+      <c r="F80" t="str">
+        <v>0.5739224235183331</v>
+      </c>
+      <c r="G80" t="str">
+        <v>0.5631100419527791</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>284</v>
+      </c>
+      <c r="B81" t="str" cm="1">
+        <f t="array" ref="B81:G81">_xlfn.TEXTSPLIT(A81,",")</f>
+        <v>Deeplab_TVERSKY_3_Fold_1</v>
+      </c>
+      <c r="C81" t="str">
+        <v>geographic_atrophy</v>
+      </c>
+      <c r="D81" t="str">
+        <v>0.7991647219849086</v>
+      </c>
+      <c r="E81" t="str">
+        <v>0.8883730458023199</v>
+      </c>
+      <c r="F81" t="str">
+        <v>0.8308156028333379</v>
+      </c>
+      <c r="G81" t="str">
+        <v>0.9544990611138338</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>285</v>
+      </c>
+      <c r="B82" t="str" cm="1">
+        <f t="array" ref="B82:G82">_xlfn.TEXTSPLIT(A82,",")</f>
+        <v>Deeplab_TVERSKY_3_Fold_1</v>
+      </c>
+      <c r="C82" t="str">
+        <v>hard_exudates</v>
+      </c>
+      <c r="D82" t="str">
+        <v>0.48091135571277377</v>
+      </c>
+      <c r="E82" t="str">
+        <v>0.6494802728841356</v>
+      </c>
+      <c r="F82" t="str">
+        <v>0.6878065877316693</v>
+      </c>
+      <c r="G82" t="str">
+        <v>0.615199791532289</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>286</v>
+      </c>
+      <c r="B83" t="str" cm="1">
+        <f t="array" ref="B83:G83">_xlfn.TEXTSPLIT(A83,",")</f>
+        <v>Deeplab_TVERSKY_3_Fold_1</v>
+      </c>
+      <c r="C83" t="str">
+        <v>hemorrhages</v>
+      </c>
+      <c r="D83" t="str">
+        <v>0.582338408774168</v>
+      </c>
+      <c r="E83" t="str">
+        <v>0.7360478713593301</v>
+      </c>
+      <c r="F83" t="str">
+        <v>0.77185433857516</v>
+      </c>
+      <c r="G83" t="str">
+        <v>0.7034162594423673</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>287</v>
+      </c>
+      <c r="B84" t="str" cm="1">
+        <f t="array" ref="B84:G84">_xlfn.TEXTSPLIT(A84,",")</f>
+        <v>Deeplab_TVERSKY_3_Fold_1</v>
+      </c>
+      <c r="C84" t="str">
+        <v>laser_coagulates</v>
+      </c>
+      <c r="D84" t="str">
+        <v>0.643288723463459</v>
+      </c>
+      <c r="E84" t="str">
+        <v>0.7829284218632483</v>
+      </c>
+      <c r="F84" t="str">
+        <v>0.7108752700678214</v>
+      </c>
+      <c r="G84" t="str">
+        <v>0.8712354150181105</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>288</v>
+      </c>
+      <c r="B85" t="str" cm="1">
+        <f t="array" ref="B85:G85">_xlfn.TEXTSPLIT(A85,",")</f>
+        <v>Deeplab_TVERSKY_3_Fold_1</v>
+      </c>
+      <c r="C85" t="str">
+        <v>macular_hole</v>
+      </c>
+      <c r="D85" t="str">
+        <v>0.7687007446901396</v>
+      </c>
+      <c r="E85" t="str">
+        <v>0.8692264612856361</v>
+      </c>
+      <c r="F85" t="str">
+        <v>0.7807264470014121</v>
+      </c>
+      <c r="G85" t="str">
+        <v>0.9803556389708654</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>289</v>
+      </c>
+      <c r="B86" t="str" cm="1">
+        <f t="array" ref="B86:G86">_xlfn.TEXTSPLIT(A86,",")</f>
+        <v>Deeplab_TVERSKY_3_Fold_1</v>
+      </c>
+      <c r="C86" t="str">
+        <v>microaneurysms</v>
+      </c>
+      <c r="D86" t="str">
+        <v>0.11284045129749536</v>
+      </c>
+      <c r="E86" t="str">
+        <v>0.20279717755753965</v>
+      </c>
+      <c r="F86" t="str">
+        <v>0.2603924331035393</v>
+      </c>
+      <c r="G86" t="str">
+        <v>0.16606570749632563</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>290</v>
+      </c>
+      <c r="B87" t="str" cm="1">
+        <f t="array" ref="B87:G87">_xlfn.TEXTSPLIT(A87,",")</f>
+        <v>Deeplab_TVERSKY_3_Fold_1</v>
+      </c>
+      <c r="C87" t="str">
+        <v>neovascularization</v>
+      </c>
+      <c r="D87" t="str">
+        <v>0.5817155776002738</v>
+      </c>
+      <c r="E87" t="str">
+        <v>0.7355501657040431</v>
+      </c>
+      <c r="F87" t="str">
+        <v>0.6773527011326</v>
+      </c>
+      <c r="G87" t="str">
+        <v>0.8046881656454155</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>291</v>
+      </c>
+      <c r="B88" t="str" cm="1">
+        <f t="array" ref="B88:G88">_xlfn.TEXTSPLIT(A88,",")</f>
+        <v>Deeplab_TVERSKY_3_Fold_1</v>
+      </c>
+      <c r="C88" t="str">
+        <v>soft_exudates</v>
+      </c>
+      <c r="D88" t="str">
+        <v>0.527657007718683</v>
+      </c>
+      <c r="E88" t="str">
+        <v>0.6908055997552177</v>
+      </c>
+      <c r="F88" t="str">
+        <v>0.7771912442594842</v>
+      </c>
+      <c r="G88" t="str">
+        <v>0.6217026770873036</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>292</v>
+      </c>
+      <c r="B89" t="str" cm="1">
+        <f t="array" ref="B89:G89">_xlfn.TEXTSPLIT(A89,",")</f>
+        <v>Deeplab_TVERSKY_3_Fold_1</v>
+      </c>
+      <c r="C89" t="str">
+        <v>subretinal_hemorrhage</v>
+      </c>
+      <c r="D89" t="str">
+        <v>0.5435281678781153</v>
+      </c>
+      <c r="E89" t="str">
+        <v>0.7042672484886392</v>
+      </c>
+      <c r="F89" t="str">
+        <v>0.7216593775851909</v>
+      </c>
+      <c r="G89" t="str">
+        <v>0.6876936987516415</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>293</v>
+      </c>
+      <c r="B90" t="str" cm="1">
+        <f t="array" ref="B90:G90">_xlfn.TEXTSPLIT(A90,",")</f>
+        <v>Deeplab_TVERSKY_3_Fold_1</v>
+      </c>
+      <c r="C90" t="str">
+        <v>venous_anomalies</v>
+      </c>
+      <c r="D90" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="E90" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="F90" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="G90" t="str">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>294</v>
+      </c>
+      <c r="B91" t="str" cm="1">
+        <f t="array" ref="B91:G91">_xlfn.TEXTSPLIT(A91,",")</f>
+        <v>Deeplab_TVERSKY_3_Fold_1</v>
+      </c>
+      <c r="C91" t="str">
+        <v>MEAN</v>
+      </c>
+      <c r="D91" t="str">
+        <v>0.4892689671789708</v>
+      </c>
+      <c r="E91" t="str">
+        <v>0.6232621147573955</v>
+      </c>
+      <c r="F91" t="str">
+        <v>0.6191450784560856</v>
+      </c>
+      <c r="G91" t="str">
+        <v>0.635123909027478</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:B16"/>
     <mergeCell ref="B32:B46"/>
     <mergeCell ref="B17:B31"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47FF012F-A572-4070-8576-1CD113E43C0F}">
+  <dimension ref="A1:R91"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.88671875" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="10.77734375" customWidth="1"/>
+    <col min="4" max="4" width="13.21875" customWidth="1"/>
+    <col min="6" max="6" width="11.77734375" customWidth="1"/>
+    <col min="8" max="8" width="25.5546875" customWidth="1"/>
+    <col min="14" max="14" width="17.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="G1" s="2"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="6">
+        <v>0.33971188298596999</v>
+      </c>
+      <c r="D2" s="6">
+        <v>0.50714170307844897</v>
+      </c>
+      <c r="E2" s="6">
+        <v>0.58487299440614704</v>
+      </c>
+      <c r="F2" s="6">
+        <v>0.44764800478042499</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="4"/>
+      <c r="B3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="6">
+        <v>0.369328801790407</v>
+      </c>
+      <c r="D3" s="6">
+        <v>0.53943041482441201</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0.54435978810580099</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0.53458951487421003</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I3" s="6">
+        <v>0.46134664184725299</v>
+      </c>
+      <c r="J3" s="6">
+        <v>0.608489664053254</v>
+      </c>
+      <c r="K3" s="6">
+        <v>0.62419701880038703</v>
+      </c>
+      <c r="L3" s="6">
+        <v>0.61500231410869299</v>
+      </c>
+      <c r="N3" t="s">
+        <v>298</v>
+      </c>
+      <c r="O3" s="7">
+        <f>AVERAGE(I3:I5)</f>
+        <v>0.48235261073196534</v>
+      </c>
+      <c r="P3" s="7">
+        <f>AVERAGE(J3:J5)</f>
+        <v>0.62677504211025326</v>
+      </c>
+      <c r="Q3" s="7">
+        <f t="shared" ref="P3:R3" si="0">AVERAGE(K3:K5)</f>
+        <v>0.6453518346409034</v>
+      </c>
+      <c r="R3" s="7">
+        <f t="shared" si="0"/>
+        <v>0.63652623645490536</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="4"/>
+      <c r="B4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.61370826912064302</v>
+      </c>
+      <c r="D4" s="6">
+        <v>0.76061860853581698</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0.70173546729434699</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0.83028875071652097</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0.494077291772059</v>
+      </c>
+      <c r="J4" s="6">
+        <v>0.64189951299723702</v>
+      </c>
+      <c r="K4" s="6">
+        <v>0.63425758562163403</v>
+      </c>
+      <c r="L4" s="6">
+        <v>0.65991566761756504</v>
+      </c>
+      <c r="N4" t="s">
+        <v>299</v>
+      </c>
+      <c r="O4" s="7">
+        <f>AVERAGE(I6:I8)</f>
+        <v>0.49060027696865899</v>
+      </c>
+      <c r="P4" s="7">
+        <f t="shared" ref="P4:R4" si="1">AVERAGE(J6:J8)</f>
+        <v>0.63309321610143998</v>
+      </c>
+      <c r="Q4" s="7">
+        <f t="shared" si="1"/>
+        <v>0.62647291276647499</v>
+      </c>
+      <c r="R4" s="7">
+        <f t="shared" si="1"/>
+        <v>0.64843435211098999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" s="4"/>
+      <c r="B5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.32915328187489001</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0.49528265304448499</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0.62144706560014995</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0.41170040906327598</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="I5" s="6">
+        <v>0.49163389857658402</v>
+      </c>
+      <c r="J5" s="6">
+        <v>0.62993594928026897</v>
+      </c>
+      <c r="K5" s="6">
+        <v>0.67760089950068902</v>
+      </c>
+      <c r="L5" s="6">
+        <v>0.63466072763845804</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" s="4"/>
+      <c r="B6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.71644917826667898</v>
+      </c>
+      <c r="D6" s="6">
+        <v>0.83480383496139399</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0.81181673677266797</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0.85913065634836305</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="I6" s="6">
+        <v>0.479617171604384</v>
+      </c>
+      <c r="J6" s="6">
+        <v>0.62640641628480997</v>
+      </c>
+      <c r="K6" s="6">
+        <v>0.62044992181797898</v>
+      </c>
+      <c r="L6" s="6">
+        <v>0.64361895944876601</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.58270324189242395</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0.73633922831381904</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.72522717384876201</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0.74779710308453295</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0.50291469212262296</v>
+      </c>
+      <c r="J7" s="6">
+        <v>0.64961111726211496</v>
+      </c>
+      <c r="K7" s="6">
+        <v>0.63982373802536097</v>
+      </c>
+      <c r="L7" s="6">
+        <v>0.66656018785672599</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" s="4"/>
+      <c r="B8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.54465806541614803</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0.70521506035630099</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.72748889133609795</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0.68426464418961197</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0.48926896717897</v>
+      </c>
+      <c r="J8" s="6">
+        <v>0.62326211475739501</v>
+      </c>
+      <c r="K8" s="6">
+        <v>0.61914507845608502</v>
+      </c>
+      <c r="L8" s="6">
+        <v>0.63512390902747795</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" s="4"/>
+      <c r="B9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.54135660125221696</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0.70244173322696701</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.60942028827127703</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0.82897599229386798</v>
+      </c>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="4"/>
+      <c r="B10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.72637375403692295</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.84150231354987104</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.74544208841279502</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0.96598207848368101</v>
+      </c>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" s="4"/>
+      <c r="B11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.162017006564732</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0.27885479411992897</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.31349026052461298</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0.25111117994126497</v>
+      </c>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" s="4"/>
+      <c r="B12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.585951062806081</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0.738927040749084</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.67427258870173101</v>
+      </c>
+      <c r="F12" s="6">
+        <v>0.81729564570034896</v>
+      </c>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" s="4"/>
+      <c r="B13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.32011139129892502</v>
+      </c>
+      <c r="D13" s="6">
+        <v>0.484976333677344</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.71479160205688597</v>
+      </c>
+      <c r="F13" s="6">
+        <v>0.36698548502905698</v>
+      </c>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" s="4"/>
+      <c r="B14" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.498890140468289</v>
+      </c>
+      <c r="D14" s="6">
+        <v>0.66567939437165702</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.64537090292710197</v>
+      </c>
+      <c r="F14" s="6">
+        <v>0.68730754547635098</v>
+      </c>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15" s="4"/>
+      <c r="B15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.12844030808720799</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0.227642183936029</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.31902241494704098</v>
+      </c>
+      <c r="F15" s="6">
+        <v>0.176955387540189</v>
+      </c>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" s="4"/>
+      <c r="B16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.46134664184725299</v>
+      </c>
+      <c r="D16" s="6">
+        <v>0.608489664053254</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.62419701880038703</v>
+      </c>
+      <c r="F16" s="6">
+        <v>0.61500231410869299</v>
+      </c>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.362191524818194</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0.53177768062612796</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.57806551088236602</v>
+      </c>
+      <c r="F17" s="6">
+        <v>0.49235315385095202</v>
+      </c>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="4"/>
+      <c r="B18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.305468086594191</v>
+      </c>
+      <c r="D18" s="6">
+        <v>0.46798246503462299</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.47158010680510298</v>
+      </c>
+      <c r="F18" s="6">
+        <v>0.46443929983147703</v>
+      </c>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.62163749441418203</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0.766678738689067</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.70895581763779303</v>
+      </c>
+      <c r="F19" s="6">
+        <v>0.83463436030615401</v>
+      </c>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="4"/>
+      <c r="B20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.39795410082275301</v>
+      </c>
+      <c r="D20" s="6">
+        <v>0.56933786393779395</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.553470158047081</v>
+      </c>
+      <c r="F20" s="6">
+        <v>0.58614226232022704</v>
+      </c>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="4"/>
+      <c r="B21" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.74578354144299097</v>
+      </c>
+      <c r="D21" s="6">
+        <v>0.85438260097991003</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.803987847007818</v>
+      </c>
+      <c r="F21" s="6">
+        <v>0.911517414677537</v>
+      </c>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="4"/>
+      <c r="B22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0.56862375917376295</v>
+      </c>
+      <c r="D22" s="6">
+        <v>0.72499699924636196</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0.77104957880960401</v>
+      </c>
+      <c r="F22" s="6">
+        <v>0.68413554557280698</v>
+      </c>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="4"/>
+      <c r="B23" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.52737845711995102</v>
+      </c>
+      <c r="D23" s="6">
+        <v>0.69056683975284505</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0.692953002666861</v>
+      </c>
+      <c r="F23" s="6">
+        <v>0.68819705380630702</v>
+      </c>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="4"/>
+      <c r="B24" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0.60125874921646305</v>
+      </c>
+      <c r="D24" s="6">
+        <v>0.75098262477650701</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0.73435308503088403</v>
+      </c>
+      <c r="F24" s="6">
+        <v>0.76838277207419603</v>
+      </c>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="4"/>
+      <c r="B25" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0.80415464417522697</v>
+      </c>
+      <c r="D25" s="6">
+        <v>0.89144757825662801</v>
+      </c>
+      <c r="E25" s="6">
+        <v>0.81105125003510203</v>
+      </c>
+      <c r="F25" s="6">
+        <v>0.989536443402114</v>
+      </c>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="4"/>
+      <c r="B26" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0.13451248083758299</v>
+      </c>
+      <c r="D26" s="6">
+        <v>0.23712825219564901</v>
+      </c>
+      <c r="E26" s="6">
+        <v>0.35137891953110201</v>
+      </c>
+      <c r="F26" s="6">
+        <v>0.178944533158782</v>
+      </c>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="4"/>
+      <c r="B27" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="6">
+        <v>0.57575994762528604</v>
+      </c>
+      <c r="D27" s="6">
+        <v>0.73077114124263998</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0.63027987242098205</v>
+      </c>
+      <c r="F27" s="6">
+        <v>0.86938514445598702</v>
+      </c>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="4"/>
+      <c r="B28" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="6">
+        <v>0.49112218735145702</v>
+      </c>
+      <c r="D28" s="6">
+        <v>0.65872829405589095</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0.64140720895849701</v>
+      </c>
+      <c r="F28" s="6">
+        <v>0.67701084898082098</v>
+      </c>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="4"/>
+      <c r="B29" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.47939236775147798</v>
+      </c>
+      <c r="D29" s="6">
+        <v>0.64809360680980699</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0.67112210178944198</v>
+      </c>
+      <c r="F29" s="6">
+        <v>0.62659305571869595</v>
+      </c>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="4"/>
+      <c r="B30" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.30184474346530799</v>
+      </c>
+      <c r="D30" s="6">
+        <v>0.46371849635747597</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0.45995173908024101</v>
+      </c>
+      <c r="F30" s="6">
+        <v>0.46754745848985801</v>
+      </c>
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="4"/>
+      <c r="B31" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.494077291772059</v>
+      </c>
+      <c r="D31" s="6">
+        <v>0.64189951299723702</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0.63425758562163403</v>
+      </c>
+      <c r="F31" s="6">
+        <v>0.65991566761756504</v>
+      </c>
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.36945233038494302</v>
+      </c>
+      <c r="D32" s="6">
+        <v>0.53956216246109501</v>
+      </c>
+      <c r="E32" s="6">
+        <v>0.58332883739475505</v>
+      </c>
+      <c r="F32" s="6">
+        <v>0.50190467439636599</v>
+      </c>
+      <c r="G32" s="2"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="4"/>
+      <c r="B33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.41263959909724102</v>
+      </c>
+      <c r="D33" s="6">
+        <v>0.58421072064090795</v>
+      </c>
+      <c r="E33" s="6">
+        <v>0.58173745838649504</v>
+      </c>
+      <c r="F33" s="6">
+        <v>0.58670510288243205</v>
+      </c>
+      <c r="G33" s="2"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="4"/>
+      <c r="B34" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" s="6">
+        <v>0.60407341520808899</v>
+      </c>
+      <c r="D34" s="6">
+        <v>0.75317427429557604</v>
+      </c>
+      <c r="E34" s="6">
+        <v>0.69393849897559601</v>
+      </c>
+      <c r="F34" s="6">
+        <v>0.82346680720293997</v>
+      </c>
+      <c r="G34" s="2"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="4"/>
+      <c r="B35" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="6">
+        <v>0.39101377937631698</v>
+      </c>
+      <c r="D35" s="6">
+        <v>0.56219972105759397</v>
+      </c>
+      <c r="E35" s="6">
+        <v>0.60676431554863597</v>
+      </c>
+      <c r="F35" s="6">
+        <v>0.52373343742466505</v>
+      </c>
+      <c r="G35" s="2"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="4"/>
+      <c r="B36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="6">
+        <v>0.79108313280514897</v>
+      </c>
+      <c r="D36" s="6">
+        <v>0.88335724714929897</v>
+      </c>
+      <c r="E36" s="6">
+        <v>0.82561253355201503</v>
+      </c>
+      <c r="F36" s="6">
+        <v>0.94978692412641696</v>
+      </c>
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="4"/>
+      <c r="B37" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.49878937317280603</v>
+      </c>
+      <c r="D37" s="6">
+        <v>0.66558968471588897</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0.71704993541002504</v>
+      </c>
+      <c r="F37" s="6">
+        <v>0.62102109908847802</v>
+      </c>
+      <c r="G37" s="2"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="4"/>
+      <c r="B38" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0.58011168863526796</v>
+      </c>
+      <c r="D38" s="6">
+        <v>0.73426668862415201</v>
+      </c>
+      <c r="E38" s="6">
+        <v>0.79692390627595899</v>
+      </c>
+      <c r="F38" s="6">
+        <v>0.68074398268876002</v>
+      </c>
+      <c r="G38" s="2"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="4"/>
+      <c r="B39" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="6">
+        <v>0.64594001498533105</v>
+      </c>
+      <c r="D39" s="6">
+        <v>0.78488888915078403</v>
+      </c>
+      <c r="E39" s="6">
+        <v>0.72174457903225797</v>
+      </c>
+      <c r="F39" s="6">
+        <v>0.86014131427787199</v>
+      </c>
+      <c r="G39" s="2"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="4"/>
+      <c r="B40" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.75102696645043399</v>
+      </c>
+      <c r="D40" s="6">
+        <v>0.85781313576553997</v>
+      </c>
+      <c r="E40" s="6">
+        <v>0.76640146623886796</v>
+      </c>
+      <c r="F40" s="6">
+        <v>0.97398397459010699</v>
+      </c>
+      <c r="G40" s="2"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="4"/>
+      <c r="B41" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.15356190634887701</v>
+      </c>
+      <c r="D41" s="6">
+        <v>0.26623955854248699</v>
+      </c>
+      <c r="E41" s="6">
+        <v>0.34217048650724302</v>
+      </c>
+      <c r="F41" s="6">
+        <v>0.217888091550582</v>
+      </c>
+      <c r="G41" s="2"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="4"/>
+      <c r="B42" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.59565915197838104</v>
+      </c>
+      <c r="D42" s="6">
+        <v>0.74659948678870702</v>
+      </c>
+      <c r="E42" s="6">
+        <v>0.70405163715291597</v>
+      </c>
+      <c r="F42" s="6">
+        <v>0.794620682285197</v>
+      </c>
+      <c r="G42" s="2"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="4"/>
+      <c r="B43" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.51716625236911296</v>
+      </c>
+      <c r="D43" s="6">
+        <v>0.68175290817540701</v>
+      </c>
+      <c r="E43" s="6">
+        <v>0.82851294186704205</v>
+      </c>
+      <c r="F43" s="6">
+        <v>0.57916206204239695</v>
+      </c>
+      <c r="G43" s="2"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="4"/>
+      <c r="B44" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0.54434607471601104</v>
+      </c>
+      <c r="D44" s="6">
+        <v>0.70495348630469501</v>
+      </c>
+      <c r="E44" s="6">
+        <v>0.67008619753750498</v>
+      </c>
+      <c r="F44" s="6">
+        <v>0.74364851952088196</v>
+      </c>
+      <c r="G44" s="2"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="4"/>
+      <c r="B45" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C45" s="6">
+        <v>2.8010894544210501E-2</v>
+      </c>
+      <c r="D45" s="6">
+        <v>5.4495326251634203E-2</v>
+      </c>
+      <c r="E45" s="6">
+        <v>0.64808979913032605</v>
+      </c>
+      <c r="F45" s="6">
+        <v>2.84435148613198E-2</v>
+      </c>
+      <c r="G45" s="2"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="4"/>
+      <c r="B46" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C46" s="6">
+        <v>0.49163389857658402</v>
+      </c>
+      <c r="D46" s="6">
+        <v>0.62993594928026897</v>
+      </c>
+      <c r="E46" s="6">
+        <v>0.67760089950068902</v>
+      </c>
+      <c r="F46" s="6">
+        <v>0.63466072763845804</v>
+      </c>
+      <c r="G46" s="2"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" s="6">
+        <v>0.34256749633908401</v>
+      </c>
+      <c r="D47" s="6">
+        <v>0.51031698186228602</v>
+      </c>
+      <c r="E47" s="6">
+        <v>0.518793846507694</v>
+      </c>
+      <c r="F47" s="6">
+        <v>0.50211268018194299</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="4"/>
+      <c r="B48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48" s="6">
+        <v>0.38120064752059302</v>
+      </c>
+      <c r="D48" s="6">
+        <v>0.551984461062758</v>
+      </c>
+      <c r="E48" s="6">
+        <v>0.58468756733620098</v>
+      </c>
+      <c r="F48" s="6">
+        <v>0.52274591363559098</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="4"/>
+      <c r="B49" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="6">
+        <v>0.64096333366603198</v>
+      </c>
+      <c r="D49" s="6">
+        <v>0.78120372407599503</v>
+      </c>
+      <c r="E49" s="6">
+        <v>0.74514303806055604</v>
+      </c>
+      <c r="F49" s="6">
+        <v>0.82093217328466905</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="4"/>
+      <c r="B50" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="6">
+        <v>0.35744492886734203</v>
+      </c>
+      <c r="D50" s="6">
+        <v>0.526643727883084</v>
+      </c>
+      <c r="E50" s="6">
+        <v>0.58727205537472305</v>
+      </c>
+      <c r="F50" s="6">
+        <v>0.47736218823611198</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="4"/>
+      <c r="B51" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C51" s="6">
+        <v>0.73036661655678903</v>
+      </c>
+      <c r="D51" s="6">
+        <v>0.84417557478093996</v>
+      </c>
+      <c r="E51" s="6">
+        <v>0.82548553298020599</v>
+      </c>
+      <c r="F51" s="6">
+        <v>0.86373155514065403</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="4"/>
+      <c r="B52" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="6">
+        <v>0.58046584160867498</v>
+      </c>
+      <c r="D52" s="6">
+        <v>0.73455031589654396</v>
+      </c>
+      <c r="E52" s="6">
+        <v>0.73343925763717799</v>
+      </c>
+      <c r="F52" s="6">
+        <v>0.73566474545979299</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="4"/>
+      <c r="B53" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C53" s="6">
+        <v>0.54060936226362899</v>
+      </c>
+      <c r="D53" s="6">
+        <v>0.70181238087415898</v>
+      </c>
+      <c r="E53" s="6">
+        <v>0.70639451239581197</v>
+      </c>
+      <c r="F53" s="6">
+        <v>0.69728931157194496</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="4"/>
+      <c r="B54" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C54" s="6">
+        <v>0.53895431549331596</v>
+      </c>
+      <c r="D54" s="6">
+        <v>0.70041626326061901</v>
+      </c>
+      <c r="E54" s="6">
+        <v>0.58991251530559696</v>
+      </c>
+      <c r="F54" s="6">
+        <v>0.86186225150709905</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="4"/>
+      <c r="B55" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C55" s="6">
+        <v>0.78202710114089902</v>
+      </c>
+      <c r="D55" s="6">
+        <v>0.87768261284042803</v>
+      </c>
+      <c r="E55" s="6">
+        <v>0.80595276252695902</v>
+      </c>
+      <c r="F55" s="6">
+        <v>0.96342774745061999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="4"/>
+      <c r="B56" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C56" s="6">
+        <v>0.141580695039356</v>
+      </c>
+      <c r="D56" s="6">
+        <v>0.24804325380515499</v>
+      </c>
+      <c r="E56" s="6">
+        <v>0.237551124563013</v>
+      </c>
+      <c r="F56" s="6">
+        <v>0.25950504096246002</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="4"/>
+      <c r="B57" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C57" s="6">
+        <v>0.61567067491082195</v>
+      </c>
+      <c r="D57" s="6">
+        <v>0.762123970523639</v>
+      </c>
+      <c r="E57" s="6">
+        <v>0.70094494047084999</v>
+      </c>
+      <c r="F57" s="6">
+        <v>0.83500376067397297</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="4"/>
+      <c r="B58" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C58" s="6">
+        <v>0.34550919126602497</v>
+      </c>
+      <c r="D58" s="6">
+        <v>0.51357388490364198</v>
+      </c>
+      <c r="E58" s="6">
+        <v>0.66645865130858095</v>
+      </c>
+      <c r="F58" s="6">
+        <v>0.41774395361024702</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="4"/>
+      <c r="B59" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C59" s="6">
+        <v>0.51342913480778896</v>
+      </c>
+      <c r="D59" s="6">
+        <v>0.67849775453542605</v>
+      </c>
+      <c r="E59" s="6">
+        <v>0.665759412399335</v>
+      </c>
+      <c r="F59" s="6">
+        <v>0.69173306489432895</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="4"/>
+      <c r="B60" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C60" s="6">
+        <v>0.20385106298103101</v>
+      </c>
+      <c r="D60" s="6">
+        <v>0.33866492168266399</v>
+      </c>
+      <c r="E60" s="6">
+        <v>0.318503688585002</v>
+      </c>
+      <c r="F60" s="6">
+        <v>0.361551045673288</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="4"/>
+      <c r="B61" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C61" s="6">
+        <v>0.479617171604384</v>
+      </c>
+      <c r="D61" s="6">
+        <v>0.62640641628480997</v>
+      </c>
+      <c r="E61" s="6">
+        <v>0.62044992181797898</v>
+      </c>
+      <c r="F61" s="6">
+        <v>0.64361895944876601</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" s="6">
+        <v>0.38076881240172</v>
+      </c>
+      <c r="D62" s="6">
+        <v>0.55153159454609602</v>
+      </c>
+      <c r="E62" s="6">
+        <v>0.571860322646494</v>
+      </c>
+      <c r="F62" s="6">
+        <v>0.53259855988397697</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="4"/>
+      <c r="B63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C63" s="6">
+        <v>0.28826615048698101</v>
+      </c>
+      <c r="D63" s="6">
+        <v>0.44752577000957799</v>
+      </c>
+      <c r="E63" s="6">
+        <v>0.53763300666798597</v>
+      </c>
+      <c r="F63" s="6">
+        <v>0.38328692138119302</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="4"/>
+      <c r="B64" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C64" s="6">
+        <v>0.61639626390128099</v>
+      </c>
+      <c r="D64" s="6">
+        <v>0.76267964442526903</v>
+      </c>
+      <c r="E64" s="6">
+        <v>0.697786299468383</v>
+      </c>
+      <c r="F64" s="6">
+        <v>0.840880599111959</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="4"/>
+      <c r="B65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="6">
+        <v>0.44477084330292799</v>
+      </c>
+      <c r="D65" s="6">
+        <v>0.61569742407886097</v>
+      </c>
+      <c r="E65" s="6">
+        <v>0.60736252568486104</v>
+      </c>
+      <c r="F65" s="6">
+        <v>0.62426426680421199</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="4"/>
+      <c r="B66" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C66" s="6">
+        <v>0.73987648082972901</v>
+      </c>
+      <c r="D66" s="6">
+        <v>0.85049311141546002</v>
+      </c>
+      <c r="E66" s="6">
+        <v>0.79204936302685502</v>
+      </c>
+      <c r="F66" s="6">
+        <v>0.91824887066535898</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="4"/>
+      <c r="B67" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C67" s="6">
+        <v>0.57354836174909296</v>
+      </c>
+      <c r="D67" s="6">
+        <v>0.728987269398647</v>
+      </c>
+      <c r="E67" s="6">
+        <v>0.768346666419776</v>
+      </c>
+      <c r="F67" s="6">
+        <v>0.69346382756959102</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" s="4"/>
+      <c r="B68" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C68" s="6">
+        <v>0.52005702057784897</v>
+      </c>
+      <c r="D68" s="6">
+        <v>0.68425988438269203</v>
+      </c>
+      <c r="E68" s="6">
+        <v>0.67801940566847796</v>
+      </c>
+      <c r="F68" s="6">
+        <v>0.69061630473489899</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" s="4"/>
+      <c r="B69" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C69" s="6">
+        <v>0.60390185995395795</v>
+      </c>
+      <c r="D69" s="6">
+        <v>0.75304091233025106</v>
+      </c>
+      <c r="E69" s="6">
+        <v>0.71302868719437595</v>
+      </c>
+      <c r="F69" s="6">
+        <v>0.79781075708042903</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" s="4"/>
+      <c r="B70" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C70" s="6">
+        <v>0.80692212975389999</v>
+      </c>
+      <c r="D70" s="6">
+        <v>0.89314543938183</v>
+      </c>
+      <c r="E70" s="6">
+        <v>0.814192497551676</v>
+      </c>
+      <c r="F70" s="6">
+        <v>0.98905494176440201</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="4"/>
+      <c r="B71" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C71" s="6">
+        <v>0.125209470557927</v>
+      </c>
+      <c r="D71" s="6">
+        <v>0.22255317580262299</v>
+      </c>
+      <c r="E71" s="6">
+        <v>0.26171546484687502</v>
+      </c>
+      <c r="F71" s="6">
+        <v>0.19358562441067201</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="4"/>
+      <c r="B72" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C72" s="6">
+        <v>0.64623705654484698</v>
+      </c>
+      <c r="D72" s="6">
+        <v>0.78510813977323701</v>
+      </c>
+      <c r="E72" s="6">
+        <v>0.72096065570835099</v>
+      </c>
+      <c r="F72" s="6">
+        <v>0.86178551784603696</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" s="4"/>
+      <c r="B73" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C73" s="6">
+        <v>0.49910559361749302</v>
+      </c>
+      <c r="D73" s="6">
+        <v>0.66587116443625705</v>
+      </c>
+      <c r="E73" s="6">
+        <v>0.64868126004787796</v>
+      </c>
+      <c r="F73" s="6">
+        <v>0.68399692585647098</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" s="4"/>
+      <c r="B74" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C74" s="6">
+        <v>0.45535743056222899</v>
+      </c>
+      <c r="D74" s="6">
+        <v>0.62576714283351997</v>
+      </c>
+      <c r="E74" s="6">
+        <v>0.62332153336478902</v>
+      </c>
+      <c r="F74" s="6">
+        <v>0.62823201864981204</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="4"/>
+      <c r="B75" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C75" s="6">
+        <v>0.340388215476783</v>
+      </c>
+      <c r="D75" s="6">
+        <v>0.50789496885527996</v>
+      </c>
+      <c r="E75" s="6">
+        <v>0.52257464405827403</v>
+      </c>
+      <c r="F75" s="6">
+        <v>0.49401749423515201</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="4"/>
+      <c r="B76" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C76" s="6">
+        <v>0.50291469212262296</v>
+      </c>
+      <c r="D76" s="6">
+        <v>0.64961111726211496</v>
+      </c>
+      <c r="E76" s="6">
+        <v>0.63982373802536097</v>
+      </c>
+      <c r="F76" s="6">
+        <v>0.66656018785672599</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" s="6">
+        <v>0.36842938203614201</v>
+      </c>
+      <c r="D77" s="6">
+        <v>0.53847043460575394</v>
+      </c>
+      <c r="E77" s="6">
+        <v>0.52011888808864704</v>
+      </c>
+      <c r="F77" s="6">
+        <v>0.55816435330080205</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="4"/>
+      <c r="B78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C78" s="6">
+        <v>0.41650001275612503</v>
+      </c>
+      <c r="D78" s="6">
+        <v>0.58806919732493101</v>
+      </c>
+      <c r="E78" s="6">
+        <v>0.60624282057788004</v>
+      </c>
+      <c r="F78" s="6">
+        <v>0.57095345967189703</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="4"/>
+      <c r="B79" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C79" s="6">
+        <v>0.62758944620254897</v>
+      </c>
+      <c r="D79" s="6">
+        <v>0.77118888632120997</v>
+      </c>
+      <c r="E79" s="6">
+        <v>0.74907296391012101</v>
+      </c>
+      <c r="F79" s="6">
+        <v>0.79465045640105803</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" s="4"/>
+      <c r="B80" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>0.39710154039075701</v>
+      </c>
+      <c r="D80" s="6">
+        <v>0.56846482365153095</v>
+      </c>
+      <c r="E80" s="6">
+        <v>0.573922423518333</v>
+      </c>
+      <c r="F80" s="6">
+        <v>0.56311004195277903</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="4"/>
+      <c r="B81" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C81" s="6">
+        <v>0.79916472198490796</v>
+      </c>
+      <c r="D81" s="6">
+        <v>0.88837304580231902</v>
+      </c>
+      <c r="E81" s="6">
+        <v>0.830815602833337</v>
+      </c>
+      <c r="F81" s="6">
+        <v>0.95449906111383298</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="4"/>
+      <c r="B82" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C82" s="6">
+        <v>0.48091135571277299</v>
+      </c>
+      <c r="D82" s="6">
+        <v>0.64948027288413501</v>
+      </c>
+      <c r="E82" s="6">
+        <v>0.68780658773166903</v>
+      </c>
+      <c r="F82" s="6">
+        <v>0.61519979153228899</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" s="4"/>
+      <c r="B83" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C83" s="6">
+        <v>0.58233840877416798</v>
+      </c>
+      <c r="D83" s="6">
+        <v>0.73604787135933003</v>
+      </c>
+      <c r="E83" s="6">
+        <v>0.77185433857515995</v>
+      </c>
+      <c r="F83" s="6">
+        <v>0.70341625944236696</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="4"/>
+      <c r="B84" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C84" s="6">
+        <v>0.643288723463459</v>
+      </c>
+      <c r="D84" s="6">
+        <v>0.78292842186324796</v>
+      </c>
+      <c r="E84" s="6">
+        <v>0.71087527006782103</v>
+      </c>
+      <c r="F84" s="6">
+        <v>0.87123541501810997</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="4"/>
+      <c r="B85" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C85" s="6">
+        <v>0.76870074469013905</v>
+      </c>
+      <c r="D85" s="6">
+        <v>0.86922646128563597</v>
+      </c>
+      <c r="E85" s="6">
+        <v>0.78072644700141203</v>
+      </c>
+      <c r="F85" s="6">
+        <v>0.98035563897086497</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="4"/>
+      <c r="B86" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C86" s="6">
+        <v>0.112840451297495</v>
+      </c>
+      <c r="D86" s="6">
+        <v>0.20279717755753901</v>
+      </c>
+      <c r="E86" s="6">
+        <v>0.26039243310353899</v>
+      </c>
+      <c r="F86" s="6">
+        <v>0.16606570749632499</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="4"/>
+      <c r="B87" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C87" s="6">
+        <v>0.58171557760027304</v>
+      </c>
+      <c r="D87" s="6">
+        <v>0.73555016570404297</v>
+      </c>
+      <c r="E87" s="6">
+        <v>0.67735270113260004</v>
+      </c>
+      <c r="F87" s="6">
+        <v>0.80468816564541501</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="4"/>
+      <c r="B88" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C88" s="6">
+        <v>0.52765700771868296</v>
+      </c>
+      <c r="D88" s="6">
+        <v>0.69080559975521705</v>
+      </c>
+      <c r="E88" s="6">
+        <v>0.77719124425948405</v>
+      </c>
+      <c r="F88" s="6">
+        <v>0.62170267708730298</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" s="4"/>
+      <c r="B89" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C89" s="6">
+        <v>0.54352816787811498</v>
+      </c>
+      <c r="D89" s="6">
+        <v>0.70426724848863897</v>
+      </c>
+      <c r="E89" s="6">
+        <v>0.72165937758519005</v>
+      </c>
+      <c r="F89" s="6">
+        <v>0.68769369875164099</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" s="4"/>
+      <c r="B90" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C90" s="6">
+        <v>0</v>
+      </c>
+      <c r="D90" s="6">
+        <v>0</v>
+      </c>
+      <c r="E90" s="6">
+        <v>0</v>
+      </c>
+      <c r="F90" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" s="4"/>
+      <c r="B91" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C91" s="6">
+        <v>0.48926896717897</v>
+      </c>
+      <c r="D91" s="6">
+        <v>0.62326211475739501</v>
+      </c>
+      <c r="E91" s="6">
+        <v>0.61914507845608502</v>
+      </c>
+      <c r="F91" s="6">
+        <v>0.63512390902747795</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A62:A76"/>
+    <mergeCell ref="A77:A91"/>
+    <mergeCell ref="A2:A16"/>
+    <mergeCell ref="A17:A31"/>
+    <mergeCell ref="A32:A46"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="A47:A61"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/metrics.xlsx
+++ b/metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\github\segmentation_biomarcers_pp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEBF2C0F-E130-4297-8684-33A86C02E195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B206D32-1AA1-4523-BD78-BBC89A64A434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="398">
   <si>
     <t>model,class_name,iou,dice,precision,recall</t>
   </si>
@@ -963,6 +963,300 @@
   </si>
   <si>
     <t>Deeplab Tversky</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_1_Fold_1,drusen,0.23212999981496318,0.37679465616424185,0.34554295221533726,0.4142614170394462</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_1_Fold_1,edema,0.41678663948761485,0.5883548416836384,0.6293462480241142,0.5523767159871148</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_1_Fold_1,epiretinal_fibrosis,0.5917930397561068,0.7435552549554819,0.7492787482393027,0.7379185385673204</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_1_Fold_1,fibrosis,0.42834265329105925,0.5997757643155309,0.6619206121943563,0.5482984108300717</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_1_Fold_1,geographic_atrophy,0.8241537937130494,0.9036012166885244,0.8959814220186795,0.9113517267540386</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_1_Fold_1,hard_exudates,0.3993885519954344,0.5708043722752097,0.5606258405849294,0.5813593342093761</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_1_Fold_1,hemorrhages,0.5953191604289844,0.746332364326273,0.7344956215020728,0.7585568654270772</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_1_Fold_1,laser_coagulates,0.5933578977562355,0.7447892260637755,0.6870756169260339,0.8130877152498183</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_1_Fold_1,macular_hole,0.7149395296731403,0.8337781213888101,0.7308067228107504,0.9705262398034191</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_1_Fold_1,microaneurysms,0.0,0.0,0.0,0.0</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_1_Fold_1,neovascularization,0.582395446116372,0.7360934304326121,0.7202068687065007,0.752696662801238</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_1_Fold_1,soft_exudates,0.3733316794126075,0.5436875665349634,0.48365896127088154,0.6207283306250105</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_1_Fold_1,subretinal_hemorrhage,0.5711178039534691,0.7270209815156338,0.7319243232304312,0.7221828999996946</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_1_Fold_1,venous_anomalies,0.0,0.0,0.0,0.0</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_1_Fold_1,MEAN,0.4516468710999312,0.5796134140246211,0.5664902812659565,0.5988103469495448</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_2_Fold_2,drusen,0.1848870082688525,0.3120753404815818,0.2812661344187824,0.35046435026112466</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_2_Fold_2,edema,0.33951918690615124,0.5069269484527936,0.5329206505393211,0.4833510498990907</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_2_Fold_2,epiretinal_fibrosis,0.6281179003371706,0.7715877335506136,0.7884748903562409,0.7554087701990485</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_2_Fold_2,fibrosis,0.3311720426832589,0.49756460031373795,0.5001984249067041,0.4949583675547959</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_2_Fold_2,geographic_atrophy,0.7205336360931476,0.8375699503664209,0.8608227222729457,0.8155403577130133</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_2_Fold_2,hard_exudates,0.4534897531029233,0.624001307384258,0.6087840304707669,0.639998835264538</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_2_Fold_2,hemorrhages,0.544517736168519,0.7050974209196234,0.6866349011465338,0.7245802302044364</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_2_Fold_2,laser_coagulates,0.4845809169361145,0.6528184639961492,0.5470367751050591,0.8093180530508719</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_2_Fold_2,macular_hole,0.7279322391990747,0.8425472049025297,0.7617411340077911,0.9425316716446714</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_2_Fold_2,microaneurysms,0.0,0.0,0.0,0.0</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_2_Fold_2,neovascularization,0.5438208448155831,0.7045128929847363,0.6605061860150535,0.7548021365149022</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_2_Fold_2,soft_exudates,0.24056409764176656,0.38783017838266254,0.4359462490236518,0.3492796374673902</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_2_Fold_2,subretinal_hemorrhage,0.5431463808755829,0.703946673636238,0.6931205893076275,0.7151163166511124</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_2_Fold_2,venous_anomalies,0.0,0.0,0.0,0.0</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_2_Fold_2,MEAN,0.4101629816448675,0.539034193955096,0.5255323348264627,0.559667841173214</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_3_Fold_3,drusen,0.18924188081997487,0.3182563343455308,0.3501570521246846,0.2916828517385825</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_3_Fold_3,edema,0.2822989154219523,0.440301262095444,0.523845516251553,0.3797394246429138</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_3_Fold_3,epiretinal_fibrosis,0.5937256633669873,0.7450788765146088,0.7862946450194488,0.7079687713239181</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_3_Fold_3,fibrosis,0.38478964723184633,0.5557373251613045,0.5350197797727418,0.5781239929383379</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_3_Fold_3,geographic_atrophy,0.7304301791341224,0.8442180308015863,0.7939650606950046,0.9012622337965097</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_3_Fold_3,hard_exudates,0.4619802537421038,0.6319924671480522,0.638168906675592,0.6259344374312111</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_3_Fold_3,hemorrhages,0.52328604394686,0.6870489571230062,0.7094952114789346,0.665979409397666</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_3_Fold_3,laser_coagulates,0.5784206176826306,0.7329106211648995,0.6621254296057498,0.8206422101503844</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_3_Fold_3,macular_hole,0.7570273777189118,0.8617138097207506,0.7883255785846764,0.9501686267288134</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_3_Fold_3,microaneurysms,0.0,0.0,0.0,0.0</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_3_Fold_3,neovascularization,0.5432580266299357,0.7040404355663926,0.6428526771877275,0.7781013848642054</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_3_Fold_3,soft_exudates,0.420013491664061,0.5915626775797218,0.5824166230137597,0.601000567515288</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_3_Fold_3,subretinal_hemorrhage,0.44385121076425826,0.6148157198681424,0.5188494857031954,0.754337796295935</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_3_Fold_3,venous_anomalies,0.0,0.0,0.0,0.0</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_3_Fold_3,MEAN,0.4220230934374031,0.5519768940778171,0.5379654261509336,0.5753529790588404</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_1_Fold_1,drusen,0.2496919864124048,0.3996056454346266,0.3810593447526431,0.4200496172465673</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_1_Fold_1,edema,0.4137564545469185,0.5853291820047173,0.5815687876734621,0.5891385218538594</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_1_Fold_1,epiretinal_fibrosis,0.6327211807196673,0.7750511087763041,0.7560742739095191,0.7950050743248249</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_1_Fold_1,fibrosis,0.4472409816154722,0.6180601396682986,0.6531860117054296,0.586519348509499</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_1_Fold_1,geographic_atrophy,0.8120655673130199,0.8962871785232065,0.8538515453133781,0.9431614305450527</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_1_Fold_1,hard_exudates,0.40766306449611606,0.5792054572974709,0.5594955660197566,0.6003547339918568</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_1_Fold_1,hemorrhages,0.5518435194887943,0.7112102638680757,0.7697959140175012,0.6609113225298988</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_1_Fold_1,laser_coagulates,0.6270487130177557,0.7707805033750244,0.7083926293061017,0.8452185885276252</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_1_Fold_1,macular_hole,0.7332199727557456,0.846078379295338,0.7698930501327216,0.938997569719931</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_1_Fold_1,microaneurysms,0.0,0.0,0.0,0.0</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_1_Fold_1,neovascularization,0.5858922746145425,0.7388802934385262,0.7273689609638245,0.7507618413584835</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_1_Fold_1,soft_exudates,0.44958773472685093,0.6202973769111916,0.606567570904039,0.6346631328666977</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_1_Fold_1,subretinal_hemorrhage,0.5842856914637697,0.7376014245561108,0.7674234002753859,0.7100105065828614</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_1_Fold_1,venous_anomalies,0.0,0.0,0.0,0.0</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_1_Fold_1,MEAN,0.4639297957979327,0.5913133537963493,0.5810483610695545,0.6053422634326541</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_2_Fold_2,drusen,0.20747655792023598,0.3436531443353148,0.32680247522691475,0.3623360018278029</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_2_Fold_2,edema,0.4046804497871812,0.5761886268844891,0.6580304502875206,0.512452858529369</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_2_Fold_2,epiretinal_fibrosis,0.6802965754615655,0.8097339307790863,0.8117111324877643,0.8077663379745292</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_2_Fold_2,fibrosis,0.32535970167281086,0.49097569703101146,0.4552466407376793,0.5327906267701569</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_2_Fold_2,geographic_atrophy,0.7473069304687684,0.8553814071672922,0.8375356212349269,0.8740042481803127</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_2_Fold_2,hard_exudates,0.45845008174175916,0.6286812109390176,0.5705567448167174,0.6999916284639378</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_2_Fold_2,hemorrhages,0.5662587715076288,0.7230717960641547,0.7057324920563112,0.7412845876912647</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_2_Fold_2,laser_coagulates,0.6058697502394893,0.7545689806400969,0.6710521115928784,0.8618293357298669</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_2_Fold_2,macular_hole,0.7169343070215367,0.8351330672228728,0.7430120957771155,0.9533299000925011</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_2_Fold_2,microaneurysms,0.0,0.0,0.0,0.0</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_2_Fold_2,neovascularization,0.5642985728460055,0.7214716968249216,0.669710865635012,0.781903726319306</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_2_Fold_2,soft_exudates,0.27756885975704054,0.43452665214433417,0.5471507357638734,0.36035260886731924</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_2_Fold_2,subretinal_hemorrhage,0.58265345859768,0.7362994791215302,0.67523595720459,0.8095053685387372</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_2_Fold_2,venous_anomalies,0.0,0.0,0.0,0.0</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_2_Fold_2,MEAN,0.4383681440729787,0.5649775492252944,0.547984094487236,0.5926819449275075</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_3_Fold_3,drusen,0.21260467106935865,0.3506578461088545,0.2704425757837189,0.49852365248948505</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_3_Fold_3,edema,0.2923664644977183,0.45245133254265824,0.5318745982287642,0.3936663039733882</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_3_Fold_3,epiretinal_fibrosis,0.6428250649747695,0.7825849248101678,0.7223645923184511,0.8537590287545256</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_3_Fold_3,fibrosis,0.42902692307614465,0.6004462423319707,0.5587069605059082,0.648925472201991</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_3_Fold_3,geographic_atrophy,0.7659690068612773,0.8674772930728413,0.8272273481163372,0.911844403433319</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_3_Fold_3,hard_exudates,0.46496957222268476,0.6347839314057868,0.5774148145922638,0.7048104572817</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_3_Fold_3,hemorrhages,0.5129100419092395,0.6780443353551477,0.6272859313033132,0.737740441286266</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_3_Fold_3,laser_coagulates,0.6142691039793988,0.7610491986313058,0.6825095093501308,0.8600153482666558</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_3_Fold_3,macular_hole,0.778602533327561,0.8755216736039223,0.7996775224085464,0.967259911751479</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_3_Fold_3,microaneurysms,0.0,0.0,0.0,0.0</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_3_Fold_3,neovascularization,0.6232912734091975,0.7679352234798579,0.7195371714955504,0.8233135612730872</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_3_Fold_3,soft_exudates,0.4579914842314886,0.6282498755099344,0.5881256100937666,0.6742498807972258</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_3_Fold_3,subretinal_hemorrhage,0.5256744898271786,0.6891043841032232,0.6703328301659763,0.7089575592173939</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_3_Fold_3,venous_anomalies,0.0,0.0,0.0,0.0</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_3_Fold_3,MEAN,0.4514643306704298,0.5777361614968336,0.5411071045973376,0.6273618586233226</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_1_Fold_1</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_2_Fold_2</t>
+  </si>
+  <si>
+    <t>TransUNet_DICE_3_Fold_3</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_1_Fold_1</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_2_Fold_2</t>
+  </si>
+  <si>
+    <t>TransUNet_TVERSKY_3_Fold_3</t>
+  </si>
+  <si>
+    <t>TransUNet DICE</t>
+  </si>
+  <si>
+    <t>TransUNet Tversky</t>
   </si>
 </sst>
 </file>
@@ -970,7 +1264,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -1018,19 +1312,21 @@
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1312,7 +1608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G181"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24.88671875" customWidth="1"/>
@@ -1350,7 +1646,7 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="6" t="s">
         <v>91</v>
       </c>
       <c r="C2" t="s">
@@ -1373,7 +1669,7 @@
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1"/>
+      <c r="B3" s="6"/>
       <c r="C3" t="s">
         <v>21</v>
       </c>
@@ -1394,7 +1690,7 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="6"/>
       <c r="C4" t="s">
         <v>26</v>
       </c>
@@ -1415,7 +1711,7 @@
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="1"/>
+      <c r="B5" s="6"/>
       <c r="C5" t="s">
         <v>31</v>
       </c>
@@ -1436,7 +1732,7 @@
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="1"/>
+      <c r="B6" s="6"/>
       <c r="C6" t="s">
         <v>36</v>
       </c>
@@ -1457,7 +1753,7 @@
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="1"/>
+      <c r="B7" s="6"/>
       <c r="C7" t="s">
         <v>41</v>
       </c>
@@ -1478,7 +1774,7 @@
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="6"/>
       <c r="C8" t="s">
         <v>46</v>
       </c>
@@ -1499,7 +1795,7 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1"/>
+      <c r="B9" s="6"/>
       <c r="C9" t="s">
         <v>51</v>
       </c>
@@ -1520,7 +1816,7 @@
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="1"/>
+      <c r="B10" s="6"/>
       <c r="C10" t="s">
         <v>56</v>
       </c>
@@ -1541,7 +1837,7 @@
       <c r="A11" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="1"/>
+      <c r="B11" s="6"/>
       <c r="C11" t="s">
         <v>61</v>
       </c>
@@ -1562,7 +1858,7 @@
       <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="1"/>
+      <c r="B12" s="6"/>
       <c r="C12" t="s">
         <v>66</v>
       </c>
@@ -1583,7 +1879,7 @@
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="1"/>
+      <c r="B13" s="6"/>
       <c r="C13" t="s">
         <v>71</v>
       </c>
@@ -1604,7 +1900,7 @@
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="1"/>
+      <c r="B14" s="6"/>
       <c r="C14" t="s">
         <v>76</v>
       </c>
@@ -1625,7 +1921,7 @@
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="1"/>
+      <c r="B15" s="6"/>
       <c r="C15" t="s">
         <v>81</v>
       </c>
@@ -1646,7 +1942,7 @@
       <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="1"/>
+      <c r="B16" s="6"/>
       <c r="C16" t="s">
         <v>86</v>
       </c>
@@ -1667,7 +1963,7 @@
       <c r="A17" t="s">
         <v>92</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="6" t="s">
         <v>122</v>
       </c>
       <c r="C17" t="s">
@@ -1690,7 +1986,7 @@
       <c r="A18" t="s">
         <v>93</v>
       </c>
-      <c r="B18" s="1"/>
+      <c r="B18" s="6"/>
       <c r="C18" t="s">
         <v>21</v>
       </c>
@@ -1711,7 +2007,7 @@
       <c r="A19" t="s">
         <v>94</v>
       </c>
-      <c r="B19" s="1"/>
+      <c r="B19" s="6"/>
       <c r="C19" t="s">
         <v>26</v>
       </c>
@@ -1732,7 +2028,7 @@
       <c r="A20" t="s">
         <v>95</v>
       </c>
-      <c r="B20" s="1"/>
+      <c r="B20" s="6"/>
       <c r="C20" t="s">
         <v>31</v>
       </c>
@@ -1753,7 +2049,7 @@
       <c r="A21" t="s">
         <v>96</v>
       </c>
-      <c r="B21" s="1"/>
+      <c r="B21" s="6"/>
       <c r="C21" t="s">
         <v>36</v>
       </c>
@@ -1774,7 +2070,7 @@
       <c r="A22" t="s">
         <v>97</v>
       </c>
-      <c r="B22" s="1"/>
+      <c r="B22" s="6"/>
       <c r="C22" t="s">
         <v>41</v>
       </c>
@@ -1795,7 +2091,7 @@
       <c r="A23" t="s">
         <v>98</v>
       </c>
-      <c r="B23" s="1"/>
+      <c r="B23" s="6"/>
       <c r="C23" t="s">
         <v>46</v>
       </c>
@@ -1816,7 +2112,7 @@
       <c r="A24" t="s">
         <v>99</v>
       </c>
-      <c r="B24" s="1"/>
+      <c r="B24" s="6"/>
       <c r="C24" t="s">
         <v>51</v>
       </c>
@@ -1837,7 +2133,7 @@
       <c r="A25" t="s">
         <v>100</v>
       </c>
-      <c r="B25" s="1"/>
+      <c r="B25" s="6"/>
       <c r="C25" t="s">
         <v>56</v>
       </c>
@@ -1858,7 +2154,7 @@
       <c r="A26" t="s">
         <v>101</v>
       </c>
-      <c r="B26" s="1"/>
+      <c r="B26" s="6"/>
       <c r="C26" t="s">
         <v>61</v>
       </c>
@@ -1879,7 +2175,7 @@
       <c r="A27" t="s">
         <v>102</v>
       </c>
-      <c r="B27" s="1"/>
+      <c r="B27" s="6"/>
       <c r="C27" t="s">
         <v>66</v>
       </c>
@@ -1900,7 +2196,7 @@
       <c r="A28" t="s">
         <v>103</v>
       </c>
-      <c r="B28" s="1"/>
+      <c r="B28" s="6"/>
       <c r="C28" t="s">
         <v>71</v>
       </c>
@@ -1921,7 +2217,7 @@
       <c r="A29" t="s">
         <v>104</v>
       </c>
-      <c r="B29" s="1"/>
+      <c r="B29" s="6"/>
       <c r="C29" t="s">
         <v>76</v>
       </c>
@@ -1942,7 +2238,7 @@
       <c r="A30" t="s">
         <v>105</v>
       </c>
-      <c r="B30" s="1"/>
+      <c r="B30" s="6"/>
       <c r="C30" t="s">
         <v>81</v>
       </c>
@@ -1963,7 +2259,7 @@
       <c r="A31" t="s">
         <v>106</v>
       </c>
-      <c r="B31" s="1"/>
+      <c r="B31" s="6"/>
       <c r="C31" t="s">
         <v>86</v>
       </c>
@@ -1984,7 +2280,7 @@
       <c r="A32" t="s">
         <v>107</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="6" t="s">
         <v>179</v>
       </c>
       <c r="C32" t="s">
@@ -2007,7 +2303,7 @@
       <c r="A33" t="s">
         <v>108</v>
       </c>
-      <c r="B33" s="1"/>
+      <c r="B33" s="6"/>
       <c r="C33" t="s">
         <v>21</v>
       </c>
@@ -2028,7 +2324,7 @@
       <c r="A34" t="s">
         <v>109</v>
       </c>
-      <c r="B34" s="1"/>
+      <c r="B34" s="6"/>
       <c r="C34" t="s">
         <v>26</v>
       </c>
@@ -2049,7 +2345,7 @@
       <c r="A35" t="s">
         <v>110</v>
       </c>
-      <c r="B35" s="1"/>
+      <c r="B35" s="6"/>
       <c r="C35" t="s">
         <v>31</v>
       </c>
@@ -2070,7 +2366,7 @@
       <c r="A36" t="s">
         <v>111</v>
       </c>
-      <c r="B36" s="1"/>
+      <c r="B36" s="6"/>
       <c r="C36" t="s">
         <v>36</v>
       </c>
@@ -2091,7 +2387,7 @@
       <c r="A37" t="s">
         <v>112</v>
       </c>
-      <c r="B37" s="1"/>
+      <c r="B37" s="6"/>
       <c r="C37" t="s">
         <v>41</v>
       </c>
@@ -2112,7 +2408,7 @@
       <c r="A38" t="s">
         <v>113</v>
       </c>
-      <c r="B38" s="1"/>
+      <c r="B38" s="6"/>
       <c r="C38" t="s">
         <v>46</v>
       </c>
@@ -2133,7 +2429,7 @@
       <c r="A39" t="s">
         <v>114</v>
       </c>
-      <c r="B39" s="1"/>
+      <c r="B39" s="6"/>
       <c r="C39" t="s">
         <v>51</v>
       </c>
@@ -2154,7 +2450,7 @@
       <c r="A40" t="s">
         <v>115</v>
       </c>
-      <c r="B40" s="1"/>
+      <c r="B40" s="6"/>
       <c r="C40" t="s">
         <v>56</v>
       </c>
@@ -2175,7 +2471,7 @@
       <c r="A41" t="s">
         <v>116</v>
       </c>
-      <c r="B41" s="1"/>
+      <c r="B41" s="6"/>
       <c r="C41" t="s">
         <v>61</v>
       </c>
@@ -2196,7 +2492,7 @@
       <c r="A42" t="s">
         <v>117</v>
       </c>
-      <c r="B42" s="1"/>
+      <c r="B42" s="6"/>
       <c r="C42" t="s">
         <v>66</v>
       </c>
@@ -2217,7 +2513,7 @@
       <c r="A43" t="s">
         <v>118</v>
       </c>
-      <c r="B43" s="1"/>
+      <c r="B43" s="6"/>
       <c r="C43" t="s">
         <v>71</v>
       </c>
@@ -2238,7 +2534,7 @@
       <c r="A44" t="s">
         <v>119</v>
       </c>
-      <c r="B44" s="1"/>
+      <c r="B44" s="6"/>
       <c r="C44" t="s">
         <v>76</v>
       </c>
@@ -2259,7 +2555,7 @@
       <c r="A45" t="s">
         <v>120</v>
       </c>
-      <c r="B45" s="1"/>
+      <c r="B45" s="6"/>
       <c r="C45" t="s">
         <v>81</v>
       </c>
@@ -2280,7 +2576,7 @@
       <c r="A46" t="s">
         <v>121</v>
       </c>
-      <c r="B46" s="1"/>
+      <c r="B46" s="6"/>
       <c r="C46" t="s">
         <v>86</v>
       </c>
@@ -3375,6 +3671,2166 @@
       </c>
       <c r="G91" t="str">
         <v>0.635123909027478</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>300</v>
+      </c>
+      <c r="B92" t="str" cm="1">
+        <f t="array" ref="B92:G92">_xlfn.TEXTSPLIT(A92,",")</f>
+        <v>TransUNet_DICE_1_Fold_1</v>
+      </c>
+      <c r="C92" t="str">
+        <v>drusen</v>
+      </c>
+      <c r="D92" t="str">
+        <v>0.23212999981496318</v>
+      </c>
+      <c r="E92" t="str">
+        <v>0.37679465616424185</v>
+      </c>
+      <c r="F92" t="str">
+        <v>0.34554295221533726</v>
+      </c>
+      <c r="G92" t="str">
+        <v>0.4142614170394462</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>301</v>
+      </c>
+      <c r="B93" t="str" cm="1">
+        <f t="array" ref="B93:G93">_xlfn.TEXTSPLIT(A93,",")</f>
+        <v>TransUNet_DICE_1_Fold_1</v>
+      </c>
+      <c r="C93" t="str">
+        <v>edema</v>
+      </c>
+      <c r="D93" t="str">
+        <v>0.41678663948761485</v>
+      </c>
+      <c r="E93" t="str">
+        <v>0.5883548416836384</v>
+      </c>
+      <c r="F93" t="str">
+        <v>0.6293462480241142</v>
+      </c>
+      <c r="G93" t="str">
+        <v>0.5523767159871148</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>302</v>
+      </c>
+      <c r="B94" t="str" cm="1">
+        <f t="array" ref="B94:G94">_xlfn.TEXTSPLIT(A94,",")</f>
+        <v>TransUNet_DICE_1_Fold_1</v>
+      </c>
+      <c r="C94" t="str">
+        <v>epiretinal_fibrosis</v>
+      </c>
+      <c r="D94" t="str">
+        <v>0.5917930397561068</v>
+      </c>
+      <c r="E94" t="str">
+        <v>0.7435552549554819</v>
+      </c>
+      <c r="F94" t="str">
+        <v>0.7492787482393027</v>
+      </c>
+      <c r="G94" t="str">
+        <v>0.7379185385673204</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>303</v>
+      </c>
+      <c r="B95" t="str" cm="1">
+        <f t="array" ref="B95:G95">_xlfn.TEXTSPLIT(A95,",")</f>
+        <v>TransUNet_DICE_1_Fold_1</v>
+      </c>
+      <c r="C95" t="str">
+        <v>fibrosis</v>
+      </c>
+      <c r="D95" t="str">
+        <v>0.42834265329105925</v>
+      </c>
+      <c r="E95" t="str">
+        <v>0.5997757643155309</v>
+      </c>
+      <c r="F95" t="str">
+        <v>0.6619206121943563</v>
+      </c>
+      <c r="G95" t="str">
+        <v>0.5482984108300717</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>304</v>
+      </c>
+      <c r="B96" t="str" cm="1">
+        <f t="array" ref="B96:G96">_xlfn.TEXTSPLIT(A96,",")</f>
+        <v>TransUNet_DICE_1_Fold_1</v>
+      </c>
+      <c r="C96" t="str">
+        <v>geographic_atrophy</v>
+      </c>
+      <c r="D96" t="str">
+        <v>0.8241537937130494</v>
+      </c>
+      <c r="E96" t="str">
+        <v>0.9036012166885244</v>
+      </c>
+      <c r="F96" t="str">
+        <v>0.8959814220186795</v>
+      </c>
+      <c r="G96" t="str">
+        <v>0.9113517267540386</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>305</v>
+      </c>
+      <c r="B97" t="str" cm="1">
+        <f t="array" ref="B97:G97">_xlfn.TEXTSPLIT(A97,",")</f>
+        <v>TransUNet_DICE_1_Fold_1</v>
+      </c>
+      <c r="C97" t="str">
+        <v>hard_exudates</v>
+      </c>
+      <c r="D97" t="str">
+        <v>0.3993885519954344</v>
+      </c>
+      <c r="E97" t="str">
+        <v>0.5708043722752097</v>
+      </c>
+      <c r="F97" t="str">
+        <v>0.5606258405849294</v>
+      </c>
+      <c r="G97" t="str">
+        <v>0.5813593342093761</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>306</v>
+      </c>
+      <c r="B98" t="str" cm="1">
+        <f t="array" ref="B98:G98">_xlfn.TEXTSPLIT(A98,",")</f>
+        <v>TransUNet_DICE_1_Fold_1</v>
+      </c>
+      <c r="C98" t="str">
+        <v>hemorrhages</v>
+      </c>
+      <c r="D98" t="str">
+        <v>0.5953191604289844</v>
+      </c>
+      <c r="E98" t="str">
+        <v>0.746332364326273</v>
+      </c>
+      <c r="F98" t="str">
+        <v>0.7344956215020728</v>
+      </c>
+      <c r="G98" t="str">
+        <v>0.7585568654270772</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>307</v>
+      </c>
+      <c r="B99" t="str" cm="1">
+        <f t="array" ref="B99:G99">_xlfn.TEXTSPLIT(A99,",")</f>
+        <v>TransUNet_DICE_1_Fold_1</v>
+      </c>
+      <c r="C99" t="str">
+        <v>laser_coagulates</v>
+      </c>
+      <c r="D99" t="str">
+        <v>0.5933578977562355</v>
+      </c>
+      <c r="E99" t="str">
+        <v>0.7447892260637755</v>
+      </c>
+      <c r="F99" t="str">
+        <v>0.6870756169260339</v>
+      </c>
+      <c r="G99" t="str">
+        <v>0.8130877152498183</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>308</v>
+      </c>
+      <c r="B100" t="str" cm="1">
+        <f t="array" ref="B100:G100">_xlfn.TEXTSPLIT(A100,",")</f>
+        <v>TransUNet_DICE_1_Fold_1</v>
+      </c>
+      <c r="C100" t="str">
+        <v>macular_hole</v>
+      </c>
+      <c r="D100" t="str">
+        <v>0.7149395296731403</v>
+      </c>
+      <c r="E100" t="str">
+        <v>0.8337781213888101</v>
+      </c>
+      <c r="F100" t="str">
+        <v>0.7308067228107504</v>
+      </c>
+      <c r="G100" t="str">
+        <v>0.9705262398034191</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>309</v>
+      </c>
+      <c r="B101" t="str" cm="1">
+        <f t="array" ref="B101:G101">_xlfn.TEXTSPLIT(A101,",")</f>
+        <v>TransUNet_DICE_1_Fold_1</v>
+      </c>
+      <c r="C101" t="str">
+        <v>microaneurysms</v>
+      </c>
+      <c r="D101" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="E101" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="F101" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="G101" t="str">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>310</v>
+      </c>
+      <c r="B102" t="str" cm="1">
+        <f t="array" ref="B102:G102">_xlfn.TEXTSPLIT(A102,",")</f>
+        <v>TransUNet_DICE_1_Fold_1</v>
+      </c>
+      <c r="C102" t="str">
+        <v>neovascularization</v>
+      </c>
+      <c r="D102" t="str">
+        <v>0.582395446116372</v>
+      </c>
+      <c r="E102" t="str">
+        <v>0.7360934304326121</v>
+      </c>
+      <c r="F102" t="str">
+        <v>0.7202068687065007</v>
+      </c>
+      <c r="G102" t="str">
+        <v>0.752696662801238</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>311</v>
+      </c>
+      <c r="B103" t="str" cm="1">
+        <f t="array" ref="B103:G103">_xlfn.TEXTSPLIT(A103,",")</f>
+        <v>TransUNet_DICE_1_Fold_1</v>
+      </c>
+      <c r="C103" t="str">
+        <v>soft_exudates</v>
+      </c>
+      <c r="D103" t="str">
+        <v>0.3733316794126075</v>
+      </c>
+      <c r="E103" t="str">
+        <v>0.5436875665349634</v>
+      </c>
+      <c r="F103" t="str">
+        <v>0.48365896127088154</v>
+      </c>
+      <c r="G103" t="str">
+        <v>0.6207283306250105</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>312</v>
+      </c>
+      <c r="B104" t="str" cm="1">
+        <f t="array" ref="B104:G104">_xlfn.TEXTSPLIT(A104,",")</f>
+        <v>TransUNet_DICE_1_Fold_1</v>
+      </c>
+      <c r="C104" t="str">
+        <v>subretinal_hemorrhage</v>
+      </c>
+      <c r="D104" t="str">
+        <v>0.5711178039534691</v>
+      </c>
+      <c r="E104" t="str">
+        <v>0.7270209815156338</v>
+      </c>
+      <c r="F104" t="str">
+        <v>0.7319243232304312</v>
+      </c>
+      <c r="G104" t="str">
+        <v>0.7221828999996946</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>313</v>
+      </c>
+      <c r="B105" t="str" cm="1">
+        <f t="array" ref="B105:G105">_xlfn.TEXTSPLIT(A105,",")</f>
+        <v>TransUNet_DICE_1_Fold_1</v>
+      </c>
+      <c r="C105" t="str">
+        <v>venous_anomalies</v>
+      </c>
+      <c r="D105" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="E105" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="F105" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="G105" t="str">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>314</v>
+      </c>
+      <c r="B106" t="str" cm="1">
+        <f t="array" ref="B106:G106">_xlfn.TEXTSPLIT(A106,",")</f>
+        <v>TransUNet_DICE_1_Fold_1</v>
+      </c>
+      <c r="C106" t="str">
+        <v>MEAN</v>
+      </c>
+      <c r="D106" t="str">
+        <v>0.4516468710999312</v>
+      </c>
+      <c r="E106" t="str">
+        <v>0.5796134140246211</v>
+      </c>
+      <c r="F106" t="str">
+        <v>0.5664902812659565</v>
+      </c>
+      <c r="G106" t="str">
+        <v>0.5988103469495448</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>315</v>
+      </c>
+      <c r="B107" t="str" cm="1">
+        <f t="array" ref="B107:G107">_xlfn.TEXTSPLIT(A107,",")</f>
+        <v>TransUNet_DICE_2_Fold_2</v>
+      </c>
+      <c r="C107" t="str">
+        <v>drusen</v>
+      </c>
+      <c r="D107" t="str">
+        <v>0.1848870082688525</v>
+      </c>
+      <c r="E107" t="str">
+        <v>0.3120753404815818</v>
+      </c>
+      <c r="F107" t="str">
+        <v>0.2812661344187824</v>
+      </c>
+      <c r="G107" t="str">
+        <v>0.35046435026112466</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>316</v>
+      </c>
+      <c r="B108" t="str" cm="1">
+        <f t="array" ref="B108:G108">_xlfn.TEXTSPLIT(A108,",")</f>
+        <v>TransUNet_DICE_2_Fold_2</v>
+      </c>
+      <c r="C108" t="str">
+        <v>edema</v>
+      </c>
+      <c r="D108" t="str">
+        <v>0.33951918690615124</v>
+      </c>
+      <c r="E108" t="str">
+        <v>0.5069269484527936</v>
+      </c>
+      <c r="F108" t="str">
+        <v>0.5329206505393211</v>
+      </c>
+      <c r="G108" t="str">
+        <v>0.4833510498990907</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>317</v>
+      </c>
+      <c r="B109" t="str" cm="1">
+        <f t="array" ref="B109:G109">_xlfn.TEXTSPLIT(A109,",")</f>
+        <v>TransUNet_DICE_2_Fold_2</v>
+      </c>
+      <c r="C109" t="str">
+        <v>epiretinal_fibrosis</v>
+      </c>
+      <c r="D109" t="str">
+        <v>0.6281179003371706</v>
+      </c>
+      <c r="E109" t="str">
+        <v>0.7715877335506136</v>
+      </c>
+      <c r="F109" t="str">
+        <v>0.7884748903562409</v>
+      </c>
+      <c r="G109" t="str">
+        <v>0.7554087701990485</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>318</v>
+      </c>
+      <c r="B110" t="str" cm="1">
+        <f t="array" ref="B110:G110">_xlfn.TEXTSPLIT(A110,",")</f>
+        <v>TransUNet_DICE_2_Fold_2</v>
+      </c>
+      <c r="C110" t="str">
+        <v>fibrosis</v>
+      </c>
+      <c r="D110" t="str">
+        <v>0.3311720426832589</v>
+      </c>
+      <c r="E110" t="str">
+        <v>0.49756460031373795</v>
+      </c>
+      <c r="F110" t="str">
+        <v>0.5001984249067041</v>
+      </c>
+      <c r="G110" t="str">
+        <v>0.4949583675547959</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>319</v>
+      </c>
+      <c r="B111" t="str" cm="1">
+        <f t="array" ref="B111:G111">_xlfn.TEXTSPLIT(A111,",")</f>
+        <v>TransUNet_DICE_2_Fold_2</v>
+      </c>
+      <c r="C111" t="str">
+        <v>geographic_atrophy</v>
+      </c>
+      <c r="D111" t="str">
+        <v>0.7205336360931476</v>
+      </c>
+      <c r="E111" t="str">
+        <v>0.8375699503664209</v>
+      </c>
+      <c r="F111" t="str">
+        <v>0.8608227222729457</v>
+      </c>
+      <c r="G111" t="str">
+        <v>0.8155403577130133</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>320</v>
+      </c>
+      <c r="B112" t="str" cm="1">
+        <f t="array" ref="B112:G112">_xlfn.TEXTSPLIT(A112,",")</f>
+        <v>TransUNet_DICE_2_Fold_2</v>
+      </c>
+      <c r="C112" t="str">
+        <v>hard_exudates</v>
+      </c>
+      <c r="D112" t="str">
+        <v>0.4534897531029233</v>
+      </c>
+      <c r="E112" t="str">
+        <v>0.624001307384258</v>
+      </c>
+      <c r="F112" t="str">
+        <v>0.6087840304707669</v>
+      </c>
+      <c r="G112" t="str">
+        <v>0.639998835264538</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>321</v>
+      </c>
+      <c r="B113" t="str" cm="1">
+        <f t="array" ref="B113:G113">_xlfn.TEXTSPLIT(A113,",")</f>
+        <v>TransUNet_DICE_2_Fold_2</v>
+      </c>
+      <c r="C113" t="str">
+        <v>hemorrhages</v>
+      </c>
+      <c r="D113" t="str">
+        <v>0.544517736168519</v>
+      </c>
+      <c r="E113" t="str">
+        <v>0.7050974209196234</v>
+      </c>
+      <c r="F113" t="str">
+        <v>0.6866349011465338</v>
+      </c>
+      <c r="G113" t="str">
+        <v>0.7245802302044364</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>322</v>
+      </c>
+      <c r="B114" t="str" cm="1">
+        <f t="array" ref="B114:G114">_xlfn.TEXTSPLIT(A114,",")</f>
+        <v>TransUNet_DICE_2_Fold_2</v>
+      </c>
+      <c r="C114" t="str">
+        <v>laser_coagulates</v>
+      </c>
+      <c r="D114" t="str">
+        <v>0.4845809169361145</v>
+      </c>
+      <c r="E114" t="str">
+        <v>0.6528184639961492</v>
+      </c>
+      <c r="F114" t="str">
+        <v>0.5470367751050591</v>
+      </c>
+      <c r="G114" t="str">
+        <v>0.8093180530508719</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>323</v>
+      </c>
+      <c r="B115" t="str" cm="1">
+        <f t="array" ref="B115:G115">_xlfn.TEXTSPLIT(A115,",")</f>
+        <v>TransUNet_DICE_2_Fold_2</v>
+      </c>
+      <c r="C115" t="str">
+        <v>macular_hole</v>
+      </c>
+      <c r="D115" t="str">
+        <v>0.7279322391990747</v>
+      </c>
+      <c r="E115" t="str">
+        <v>0.8425472049025297</v>
+      </c>
+      <c r="F115" t="str">
+        <v>0.7617411340077911</v>
+      </c>
+      <c r="G115" t="str">
+        <v>0.9425316716446714</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>324</v>
+      </c>
+      <c r="B116" t="str" cm="1">
+        <f t="array" ref="B116:G116">_xlfn.TEXTSPLIT(A116,",")</f>
+        <v>TransUNet_DICE_2_Fold_2</v>
+      </c>
+      <c r="C116" t="str">
+        <v>microaneurysms</v>
+      </c>
+      <c r="D116" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="E116" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="F116" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="G116" t="str">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>325</v>
+      </c>
+      <c r="B117" t="str" cm="1">
+        <f t="array" ref="B117:G117">_xlfn.TEXTSPLIT(A117,",")</f>
+        <v>TransUNet_DICE_2_Fold_2</v>
+      </c>
+      <c r="C117" t="str">
+        <v>neovascularization</v>
+      </c>
+      <c r="D117" t="str">
+        <v>0.5438208448155831</v>
+      </c>
+      <c r="E117" t="str">
+        <v>0.7045128929847363</v>
+      </c>
+      <c r="F117" t="str">
+        <v>0.6605061860150535</v>
+      </c>
+      <c r="G117" t="str">
+        <v>0.7548021365149022</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>326</v>
+      </c>
+      <c r="B118" t="str" cm="1">
+        <f t="array" ref="B118:G118">_xlfn.TEXTSPLIT(A118,",")</f>
+        <v>TransUNet_DICE_2_Fold_2</v>
+      </c>
+      <c r="C118" t="str">
+        <v>soft_exudates</v>
+      </c>
+      <c r="D118" t="str">
+        <v>0.24056409764176656</v>
+      </c>
+      <c r="E118" t="str">
+        <v>0.38783017838266254</v>
+      </c>
+      <c r="F118" t="str">
+        <v>0.4359462490236518</v>
+      </c>
+      <c r="G118" t="str">
+        <v>0.3492796374673902</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>327</v>
+      </c>
+      <c r="B119" t="str" cm="1">
+        <f t="array" ref="B119:G119">_xlfn.TEXTSPLIT(A119,",")</f>
+        <v>TransUNet_DICE_2_Fold_2</v>
+      </c>
+      <c r="C119" t="str">
+        <v>subretinal_hemorrhage</v>
+      </c>
+      <c r="D119" t="str">
+        <v>0.5431463808755829</v>
+      </c>
+      <c r="E119" t="str">
+        <v>0.703946673636238</v>
+      </c>
+      <c r="F119" t="str">
+        <v>0.6931205893076275</v>
+      </c>
+      <c r="G119" t="str">
+        <v>0.7151163166511124</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>328</v>
+      </c>
+      <c r="B120" t="str" cm="1">
+        <f t="array" ref="B120:G120">_xlfn.TEXTSPLIT(A120,",")</f>
+        <v>TransUNet_DICE_2_Fold_2</v>
+      </c>
+      <c r="C120" t="str">
+        <v>venous_anomalies</v>
+      </c>
+      <c r="D120" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="E120" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="F120" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="G120" t="str">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>329</v>
+      </c>
+      <c r="B121" t="str" cm="1">
+        <f t="array" ref="B121:G121">_xlfn.TEXTSPLIT(A121,",")</f>
+        <v>TransUNet_DICE_2_Fold_2</v>
+      </c>
+      <c r="C121" t="str">
+        <v>MEAN</v>
+      </c>
+      <c r="D121" t="str">
+        <v>0.4101629816448675</v>
+      </c>
+      <c r="E121" t="str">
+        <v>0.539034193955096</v>
+      </c>
+      <c r="F121" t="str">
+        <v>0.5255323348264627</v>
+      </c>
+      <c r="G121" t="str">
+        <v>0.559667841173214</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>330</v>
+      </c>
+      <c r="B122" t="str" cm="1">
+        <f t="array" ref="B122:G122">_xlfn.TEXTSPLIT(A122,",")</f>
+        <v>TransUNet_DICE_3_Fold_3</v>
+      </c>
+      <c r="C122" t="str">
+        <v>drusen</v>
+      </c>
+      <c r="D122" t="str">
+        <v>0.18924188081997487</v>
+      </c>
+      <c r="E122" t="str">
+        <v>0.3182563343455308</v>
+      </c>
+      <c r="F122" t="str">
+        <v>0.3501570521246846</v>
+      </c>
+      <c r="G122" t="str">
+        <v>0.2916828517385825</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>331</v>
+      </c>
+      <c r="B123" t="str" cm="1">
+        <f t="array" ref="B123:G123">_xlfn.TEXTSPLIT(A123,",")</f>
+        <v>TransUNet_DICE_3_Fold_3</v>
+      </c>
+      <c r="C123" t="str">
+        <v>edema</v>
+      </c>
+      <c r="D123" t="str">
+        <v>0.2822989154219523</v>
+      </c>
+      <c r="E123" t="str">
+        <v>0.440301262095444</v>
+      </c>
+      <c r="F123" t="str">
+        <v>0.523845516251553</v>
+      </c>
+      <c r="G123" t="str">
+        <v>0.3797394246429138</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>332</v>
+      </c>
+      <c r="B124" t="str" cm="1">
+        <f t="array" ref="B124:G124">_xlfn.TEXTSPLIT(A124,",")</f>
+        <v>TransUNet_DICE_3_Fold_3</v>
+      </c>
+      <c r="C124" t="str">
+        <v>epiretinal_fibrosis</v>
+      </c>
+      <c r="D124" t="str">
+        <v>0.5937256633669873</v>
+      </c>
+      <c r="E124" t="str">
+        <v>0.7450788765146088</v>
+      </c>
+      <c r="F124" t="str">
+        <v>0.7862946450194488</v>
+      </c>
+      <c r="G124" t="str">
+        <v>0.7079687713239181</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>333</v>
+      </c>
+      <c r="B125" t="str" cm="1">
+        <f t="array" ref="B125:G125">_xlfn.TEXTSPLIT(A125,",")</f>
+        <v>TransUNet_DICE_3_Fold_3</v>
+      </c>
+      <c r="C125" t="str">
+        <v>fibrosis</v>
+      </c>
+      <c r="D125" t="str">
+        <v>0.38478964723184633</v>
+      </c>
+      <c r="E125" t="str">
+        <v>0.5557373251613045</v>
+      </c>
+      <c r="F125" t="str">
+        <v>0.5350197797727418</v>
+      </c>
+      <c r="G125" t="str">
+        <v>0.5781239929383379</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>334</v>
+      </c>
+      <c r="B126" t="str" cm="1">
+        <f t="array" ref="B126:G126">_xlfn.TEXTSPLIT(A126,",")</f>
+        <v>TransUNet_DICE_3_Fold_3</v>
+      </c>
+      <c r="C126" t="str">
+        <v>geographic_atrophy</v>
+      </c>
+      <c r="D126" t="str">
+        <v>0.7304301791341224</v>
+      </c>
+      <c r="E126" t="str">
+        <v>0.8442180308015863</v>
+      </c>
+      <c r="F126" t="str">
+        <v>0.7939650606950046</v>
+      </c>
+      <c r="G126" t="str">
+        <v>0.9012622337965097</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>335</v>
+      </c>
+      <c r="B127" t="str" cm="1">
+        <f t="array" ref="B127:G127">_xlfn.TEXTSPLIT(A127,",")</f>
+        <v>TransUNet_DICE_3_Fold_3</v>
+      </c>
+      <c r="C127" t="str">
+        <v>hard_exudates</v>
+      </c>
+      <c r="D127" t="str">
+        <v>0.4619802537421038</v>
+      </c>
+      <c r="E127" t="str">
+        <v>0.6319924671480522</v>
+      </c>
+      <c r="F127" t="str">
+        <v>0.638168906675592</v>
+      </c>
+      <c r="G127" t="str">
+        <v>0.6259344374312111</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>336</v>
+      </c>
+      <c r="B128" t="str" cm="1">
+        <f t="array" ref="B128:G128">_xlfn.TEXTSPLIT(A128,",")</f>
+        <v>TransUNet_DICE_3_Fold_3</v>
+      </c>
+      <c r="C128" t="str">
+        <v>hemorrhages</v>
+      </c>
+      <c r="D128" t="str">
+        <v>0.52328604394686</v>
+      </c>
+      <c r="E128" t="str">
+        <v>0.6870489571230062</v>
+      </c>
+      <c r="F128" t="str">
+        <v>0.7094952114789346</v>
+      </c>
+      <c r="G128" t="str">
+        <v>0.665979409397666</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>337</v>
+      </c>
+      <c r="B129" t="str" cm="1">
+        <f t="array" ref="B129:G129">_xlfn.TEXTSPLIT(A129,",")</f>
+        <v>TransUNet_DICE_3_Fold_3</v>
+      </c>
+      <c r="C129" t="str">
+        <v>laser_coagulates</v>
+      </c>
+      <c r="D129" t="str">
+        <v>0.5784206176826306</v>
+      </c>
+      <c r="E129" t="str">
+        <v>0.7329106211648995</v>
+      </c>
+      <c r="F129" t="str">
+        <v>0.6621254296057498</v>
+      </c>
+      <c r="G129" t="str">
+        <v>0.8206422101503844</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>338</v>
+      </c>
+      <c r="B130" t="str" cm="1">
+        <f t="array" ref="B130:G130">_xlfn.TEXTSPLIT(A130,",")</f>
+        <v>TransUNet_DICE_3_Fold_3</v>
+      </c>
+      <c r="C130" t="str">
+        <v>macular_hole</v>
+      </c>
+      <c r="D130" t="str">
+        <v>0.7570273777189118</v>
+      </c>
+      <c r="E130" t="str">
+        <v>0.8617138097207506</v>
+      </c>
+      <c r="F130" t="str">
+        <v>0.7883255785846764</v>
+      </c>
+      <c r="G130" t="str">
+        <v>0.9501686267288134</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>339</v>
+      </c>
+      <c r="B131" t="str" cm="1">
+        <f t="array" ref="B131:G131">_xlfn.TEXTSPLIT(A131,",")</f>
+        <v>TransUNet_DICE_3_Fold_3</v>
+      </c>
+      <c r="C131" t="str">
+        <v>microaneurysms</v>
+      </c>
+      <c r="D131" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="E131" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="F131" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="G131" t="str">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>340</v>
+      </c>
+      <c r="B132" t="str" cm="1">
+        <f t="array" ref="B132:G132">_xlfn.TEXTSPLIT(A132,",")</f>
+        <v>TransUNet_DICE_3_Fold_3</v>
+      </c>
+      <c r="C132" t="str">
+        <v>neovascularization</v>
+      </c>
+      <c r="D132" t="str">
+        <v>0.5432580266299357</v>
+      </c>
+      <c r="E132" t="str">
+        <v>0.7040404355663926</v>
+      </c>
+      <c r="F132" t="str">
+        <v>0.6428526771877275</v>
+      </c>
+      <c r="G132" t="str">
+        <v>0.7781013848642054</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>341</v>
+      </c>
+      <c r="B133" t="str" cm="1">
+        <f t="array" ref="B133:G133">_xlfn.TEXTSPLIT(A133,",")</f>
+        <v>TransUNet_DICE_3_Fold_3</v>
+      </c>
+      <c r="C133" t="str">
+        <v>soft_exudates</v>
+      </c>
+      <c r="D133" t="str">
+        <v>0.420013491664061</v>
+      </c>
+      <c r="E133" t="str">
+        <v>0.5915626775797218</v>
+      </c>
+      <c r="F133" t="str">
+        <v>0.5824166230137597</v>
+      </c>
+      <c r="G133" t="str">
+        <v>0.601000567515288</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>342</v>
+      </c>
+      <c r="B134" t="str" cm="1">
+        <f t="array" ref="B134:G134">_xlfn.TEXTSPLIT(A134,",")</f>
+        <v>TransUNet_DICE_3_Fold_3</v>
+      </c>
+      <c r="C134" t="str">
+        <v>subretinal_hemorrhage</v>
+      </c>
+      <c r="D134" t="str">
+        <v>0.44385121076425826</v>
+      </c>
+      <c r="E134" t="str">
+        <v>0.6148157198681424</v>
+      </c>
+      <c r="F134" t="str">
+        <v>0.5188494857031954</v>
+      </c>
+      <c r="G134" t="str">
+        <v>0.754337796295935</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>343</v>
+      </c>
+      <c r="B135" t="str" cm="1">
+        <f t="array" ref="B135:G135">_xlfn.TEXTSPLIT(A135,",")</f>
+        <v>TransUNet_DICE_3_Fold_3</v>
+      </c>
+      <c r="C135" t="str">
+        <v>venous_anomalies</v>
+      </c>
+      <c r="D135" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="E135" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="F135" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="G135" t="str">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>344</v>
+      </c>
+      <c r="B136" t="str" cm="1">
+        <f t="array" ref="B136:G136">_xlfn.TEXTSPLIT(A136,",")</f>
+        <v>TransUNet_DICE_3_Fold_3</v>
+      </c>
+      <c r="C136" t="str">
+        <v>MEAN</v>
+      </c>
+      <c r="D136" t="str">
+        <v>0.4220230934374031</v>
+      </c>
+      <c r="E136" t="str">
+        <v>0.5519768940778171</v>
+      </c>
+      <c r="F136" t="str">
+        <v>0.5379654261509336</v>
+      </c>
+      <c r="G136" t="str">
+        <v>0.5753529790588404</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>345</v>
+      </c>
+      <c r="B137" t="str" cm="1">
+        <f t="array" ref="B137:G137">_xlfn.TEXTSPLIT(A137,",")</f>
+        <v>TransUNet_TVERSKY_1_Fold_1</v>
+      </c>
+      <c r="C137" t="str">
+        <v>drusen</v>
+      </c>
+      <c r="D137" t="str">
+        <v>0.2496919864124048</v>
+      </c>
+      <c r="E137" t="str">
+        <v>0.3996056454346266</v>
+      </c>
+      <c r="F137" t="str">
+        <v>0.3810593447526431</v>
+      </c>
+      <c r="G137" t="str">
+        <v>0.4200496172465673</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>346</v>
+      </c>
+      <c r="B138" t="str" cm="1">
+        <f t="array" ref="B138:G138">_xlfn.TEXTSPLIT(A138,",")</f>
+        <v>TransUNet_TVERSKY_1_Fold_1</v>
+      </c>
+      <c r="C138" t="str">
+        <v>edema</v>
+      </c>
+      <c r="D138" t="str">
+        <v>0.4137564545469185</v>
+      </c>
+      <c r="E138" t="str">
+        <v>0.5853291820047173</v>
+      </c>
+      <c r="F138" t="str">
+        <v>0.5815687876734621</v>
+      </c>
+      <c r="G138" t="str">
+        <v>0.5891385218538594</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>347</v>
+      </c>
+      <c r="B139" t="str" cm="1">
+        <f t="array" ref="B139:G139">_xlfn.TEXTSPLIT(A139,",")</f>
+        <v>TransUNet_TVERSKY_1_Fold_1</v>
+      </c>
+      <c r="C139" t="str">
+        <v>epiretinal_fibrosis</v>
+      </c>
+      <c r="D139" t="str">
+        <v>0.6327211807196673</v>
+      </c>
+      <c r="E139" t="str">
+        <v>0.7750511087763041</v>
+      </c>
+      <c r="F139" t="str">
+        <v>0.7560742739095191</v>
+      </c>
+      <c r="G139" t="str">
+        <v>0.7950050743248249</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>348</v>
+      </c>
+      <c r="B140" t="str" cm="1">
+        <f t="array" ref="B140:G140">_xlfn.TEXTSPLIT(A140,",")</f>
+        <v>TransUNet_TVERSKY_1_Fold_1</v>
+      </c>
+      <c r="C140" t="str">
+        <v>fibrosis</v>
+      </c>
+      <c r="D140" t="str">
+        <v>0.4472409816154722</v>
+      </c>
+      <c r="E140" t="str">
+        <v>0.6180601396682986</v>
+      </c>
+      <c r="F140" t="str">
+        <v>0.6531860117054296</v>
+      </c>
+      <c r="G140" t="str">
+        <v>0.586519348509499</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>349</v>
+      </c>
+      <c r="B141" t="str" cm="1">
+        <f t="array" ref="B141:G141">_xlfn.TEXTSPLIT(A141,",")</f>
+        <v>TransUNet_TVERSKY_1_Fold_1</v>
+      </c>
+      <c r="C141" t="str">
+        <v>geographic_atrophy</v>
+      </c>
+      <c r="D141" t="str">
+        <v>0.8120655673130199</v>
+      </c>
+      <c r="E141" t="str">
+        <v>0.8962871785232065</v>
+      </c>
+      <c r="F141" t="str">
+        <v>0.8538515453133781</v>
+      </c>
+      <c r="G141" t="str">
+        <v>0.9431614305450527</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>350</v>
+      </c>
+      <c r="B142" t="str" cm="1">
+        <f t="array" ref="B142:G142">_xlfn.TEXTSPLIT(A142,",")</f>
+        <v>TransUNet_TVERSKY_1_Fold_1</v>
+      </c>
+      <c r="C142" t="str">
+        <v>hard_exudates</v>
+      </c>
+      <c r="D142" t="str">
+        <v>0.40766306449611606</v>
+      </c>
+      <c r="E142" t="str">
+        <v>0.5792054572974709</v>
+      </c>
+      <c r="F142" t="str">
+        <v>0.5594955660197566</v>
+      </c>
+      <c r="G142" t="str">
+        <v>0.6003547339918568</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>351</v>
+      </c>
+      <c r="B143" t="str" cm="1">
+        <f t="array" ref="B143:G143">_xlfn.TEXTSPLIT(A143,",")</f>
+        <v>TransUNet_TVERSKY_1_Fold_1</v>
+      </c>
+      <c r="C143" t="str">
+        <v>hemorrhages</v>
+      </c>
+      <c r="D143" t="str">
+        <v>0.5518435194887943</v>
+      </c>
+      <c r="E143" t="str">
+        <v>0.7112102638680757</v>
+      </c>
+      <c r="F143" t="str">
+        <v>0.7697959140175012</v>
+      </c>
+      <c r="G143" t="str">
+        <v>0.6609113225298988</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>352</v>
+      </c>
+      <c r="B144" t="str" cm="1">
+        <f t="array" ref="B144:G144">_xlfn.TEXTSPLIT(A144,",")</f>
+        <v>TransUNet_TVERSKY_1_Fold_1</v>
+      </c>
+      <c r="C144" t="str">
+        <v>laser_coagulates</v>
+      </c>
+      <c r="D144" t="str">
+        <v>0.6270487130177557</v>
+      </c>
+      <c r="E144" t="str">
+        <v>0.7707805033750244</v>
+      </c>
+      <c r="F144" t="str">
+        <v>0.7083926293061017</v>
+      </c>
+      <c r="G144" t="str">
+        <v>0.8452185885276252</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>353</v>
+      </c>
+      <c r="B145" t="str" cm="1">
+        <f t="array" ref="B145:G145">_xlfn.TEXTSPLIT(A145,",")</f>
+        <v>TransUNet_TVERSKY_1_Fold_1</v>
+      </c>
+      <c r="C145" t="str">
+        <v>macular_hole</v>
+      </c>
+      <c r="D145" t="str">
+        <v>0.7332199727557456</v>
+      </c>
+      <c r="E145" t="str">
+        <v>0.846078379295338</v>
+      </c>
+      <c r="F145" t="str">
+        <v>0.7698930501327216</v>
+      </c>
+      <c r="G145" t="str">
+        <v>0.938997569719931</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>354</v>
+      </c>
+      <c r="B146" t="str" cm="1">
+        <f t="array" ref="B146:G146">_xlfn.TEXTSPLIT(A146,",")</f>
+        <v>TransUNet_TVERSKY_1_Fold_1</v>
+      </c>
+      <c r="C146" t="str">
+        <v>microaneurysms</v>
+      </c>
+      <c r="D146" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="E146" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="F146" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="G146" t="str">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>355</v>
+      </c>
+      <c r="B147" t="str" cm="1">
+        <f t="array" ref="B147:G147">_xlfn.TEXTSPLIT(A147,",")</f>
+        <v>TransUNet_TVERSKY_1_Fold_1</v>
+      </c>
+      <c r="C147" t="str">
+        <v>neovascularization</v>
+      </c>
+      <c r="D147" t="str">
+        <v>0.5858922746145425</v>
+      </c>
+      <c r="E147" t="str">
+        <v>0.7388802934385262</v>
+      </c>
+      <c r="F147" t="str">
+        <v>0.7273689609638245</v>
+      </c>
+      <c r="G147" t="str">
+        <v>0.7507618413584835</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>356</v>
+      </c>
+      <c r="B148" t="str" cm="1">
+        <f t="array" ref="B148:G148">_xlfn.TEXTSPLIT(A148,",")</f>
+        <v>TransUNet_TVERSKY_1_Fold_1</v>
+      </c>
+      <c r="C148" t="str">
+        <v>soft_exudates</v>
+      </c>
+      <c r="D148" t="str">
+        <v>0.44958773472685093</v>
+      </c>
+      <c r="E148" t="str">
+        <v>0.6202973769111916</v>
+      </c>
+      <c r="F148" t="str">
+        <v>0.606567570904039</v>
+      </c>
+      <c r="G148" t="str">
+        <v>0.6346631328666977</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>357</v>
+      </c>
+      <c r="B149" t="str" cm="1">
+        <f t="array" ref="B149:G149">_xlfn.TEXTSPLIT(A149,",")</f>
+        <v>TransUNet_TVERSKY_1_Fold_1</v>
+      </c>
+      <c r="C149" t="str">
+        <v>subretinal_hemorrhage</v>
+      </c>
+      <c r="D149" t="str">
+        <v>0.5842856914637697</v>
+      </c>
+      <c r="E149" t="str">
+        <v>0.7376014245561108</v>
+      </c>
+      <c r="F149" t="str">
+        <v>0.7674234002753859</v>
+      </c>
+      <c r="G149" t="str">
+        <v>0.7100105065828614</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>358</v>
+      </c>
+      <c r="B150" t="str" cm="1">
+        <f t="array" ref="B150:G150">_xlfn.TEXTSPLIT(A150,",")</f>
+        <v>TransUNet_TVERSKY_1_Fold_1</v>
+      </c>
+      <c r="C150" t="str">
+        <v>venous_anomalies</v>
+      </c>
+      <c r="D150" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="E150" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="F150" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="G150" t="str">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>359</v>
+      </c>
+      <c r="B151" t="str" cm="1">
+        <f t="array" ref="B151:G151">_xlfn.TEXTSPLIT(A151,",")</f>
+        <v>TransUNet_TVERSKY_1_Fold_1</v>
+      </c>
+      <c r="C151" t="str">
+        <v>MEAN</v>
+      </c>
+      <c r="D151" t="str">
+        <v>0.4639297957979327</v>
+      </c>
+      <c r="E151" t="str">
+        <v>0.5913133537963493</v>
+      </c>
+      <c r="F151" t="str">
+        <v>0.5810483610695545</v>
+      </c>
+      <c r="G151" t="str">
+        <v>0.6053422634326541</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>360</v>
+      </c>
+      <c r="B152" t="str" cm="1">
+        <f t="array" ref="B152:G152">_xlfn.TEXTSPLIT(A152,",")</f>
+        <v>TransUNet_TVERSKY_2_Fold_2</v>
+      </c>
+      <c r="C152" t="str">
+        <v>drusen</v>
+      </c>
+      <c r="D152" t="str">
+        <v>0.20747655792023598</v>
+      </c>
+      <c r="E152" t="str">
+        <v>0.3436531443353148</v>
+      </c>
+      <c r="F152" t="str">
+        <v>0.32680247522691475</v>
+      </c>
+      <c r="G152" t="str">
+        <v>0.3623360018278029</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>361</v>
+      </c>
+      <c r="B153" t="str" cm="1">
+        <f t="array" ref="B153:G153">_xlfn.TEXTSPLIT(A153,",")</f>
+        <v>TransUNet_TVERSKY_2_Fold_2</v>
+      </c>
+      <c r="C153" t="str">
+        <v>edema</v>
+      </c>
+      <c r="D153" t="str">
+        <v>0.4046804497871812</v>
+      </c>
+      <c r="E153" t="str">
+        <v>0.5761886268844891</v>
+      </c>
+      <c r="F153" t="str">
+        <v>0.6580304502875206</v>
+      </c>
+      <c r="G153" t="str">
+        <v>0.512452858529369</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>362</v>
+      </c>
+      <c r="B154" t="str" cm="1">
+        <f t="array" ref="B154:G154">_xlfn.TEXTSPLIT(A154,",")</f>
+        <v>TransUNet_TVERSKY_2_Fold_2</v>
+      </c>
+      <c r="C154" t="str">
+        <v>epiretinal_fibrosis</v>
+      </c>
+      <c r="D154" t="str">
+        <v>0.6802965754615655</v>
+      </c>
+      <c r="E154" t="str">
+        <v>0.8097339307790863</v>
+      </c>
+      <c r="F154" t="str">
+        <v>0.8117111324877643</v>
+      </c>
+      <c r="G154" t="str">
+        <v>0.8077663379745292</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>363</v>
+      </c>
+      <c r="B155" t="str" cm="1">
+        <f t="array" ref="B155:G155">_xlfn.TEXTSPLIT(A155,",")</f>
+        <v>TransUNet_TVERSKY_2_Fold_2</v>
+      </c>
+      <c r="C155" t="str">
+        <v>fibrosis</v>
+      </c>
+      <c r="D155" t="str">
+        <v>0.32535970167281086</v>
+      </c>
+      <c r="E155" t="str">
+        <v>0.49097569703101146</v>
+      </c>
+      <c r="F155" t="str">
+        <v>0.4552466407376793</v>
+      </c>
+      <c r="G155" t="str">
+        <v>0.5327906267701569</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>364</v>
+      </c>
+      <c r="B156" t="str" cm="1">
+        <f t="array" ref="B156:G156">_xlfn.TEXTSPLIT(A156,",")</f>
+        <v>TransUNet_TVERSKY_2_Fold_2</v>
+      </c>
+      <c r="C156" t="str">
+        <v>geographic_atrophy</v>
+      </c>
+      <c r="D156" t="str">
+        <v>0.7473069304687684</v>
+      </c>
+      <c r="E156" t="str">
+        <v>0.8553814071672922</v>
+      </c>
+      <c r="F156" t="str">
+        <v>0.8375356212349269</v>
+      </c>
+      <c r="G156" t="str">
+        <v>0.8740042481803127</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>365</v>
+      </c>
+      <c r="B157" t="str" cm="1">
+        <f t="array" ref="B157:G157">_xlfn.TEXTSPLIT(A157,",")</f>
+        <v>TransUNet_TVERSKY_2_Fold_2</v>
+      </c>
+      <c r="C157" t="str">
+        <v>hard_exudates</v>
+      </c>
+      <c r="D157" t="str">
+        <v>0.45845008174175916</v>
+      </c>
+      <c r="E157" t="str">
+        <v>0.6286812109390176</v>
+      </c>
+      <c r="F157" t="str">
+        <v>0.5705567448167174</v>
+      </c>
+      <c r="G157" t="str">
+        <v>0.6999916284639378</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>366</v>
+      </c>
+      <c r="B158" t="str" cm="1">
+        <f t="array" ref="B158:G158">_xlfn.TEXTSPLIT(A158,",")</f>
+        <v>TransUNet_TVERSKY_2_Fold_2</v>
+      </c>
+      <c r="C158" t="str">
+        <v>hemorrhages</v>
+      </c>
+      <c r="D158" t="str">
+        <v>0.5662587715076288</v>
+      </c>
+      <c r="E158" t="str">
+        <v>0.7230717960641547</v>
+      </c>
+      <c r="F158" t="str">
+        <v>0.7057324920563112</v>
+      </c>
+      <c r="G158" t="str">
+        <v>0.7412845876912647</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>367</v>
+      </c>
+      <c r="B159" t="str" cm="1">
+        <f t="array" ref="B159:G159">_xlfn.TEXTSPLIT(A159,",")</f>
+        <v>TransUNet_TVERSKY_2_Fold_2</v>
+      </c>
+      <c r="C159" t="str">
+        <v>laser_coagulates</v>
+      </c>
+      <c r="D159" t="str">
+        <v>0.6058697502394893</v>
+      </c>
+      <c r="E159" t="str">
+        <v>0.7545689806400969</v>
+      </c>
+      <c r="F159" t="str">
+        <v>0.6710521115928784</v>
+      </c>
+      <c r="G159" t="str">
+        <v>0.8618293357298669</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>368</v>
+      </c>
+      <c r="B160" t="str" cm="1">
+        <f t="array" ref="B160:G160">_xlfn.TEXTSPLIT(A160,",")</f>
+        <v>TransUNet_TVERSKY_2_Fold_2</v>
+      </c>
+      <c r="C160" t="str">
+        <v>macular_hole</v>
+      </c>
+      <c r="D160" t="str">
+        <v>0.7169343070215367</v>
+      </c>
+      <c r="E160" t="str">
+        <v>0.8351330672228728</v>
+      </c>
+      <c r="F160" t="str">
+        <v>0.7430120957771155</v>
+      </c>
+      <c r="G160" t="str">
+        <v>0.9533299000925011</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>369</v>
+      </c>
+      <c r="B161" t="str" cm="1">
+        <f t="array" ref="B161:G161">_xlfn.TEXTSPLIT(A161,",")</f>
+        <v>TransUNet_TVERSKY_2_Fold_2</v>
+      </c>
+      <c r="C161" t="str">
+        <v>microaneurysms</v>
+      </c>
+      <c r="D161" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="E161" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="F161" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="G161" t="str">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>370</v>
+      </c>
+      <c r="B162" t="str" cm="1">
+        <f t="array" ref="B162:G162">_xlfn.TEXTSPLIT(A162,",")</f>
+        <v>TransUNet_TVERSKY_2_Fold_2</v>
+      </c>
+      <c r="C162" t="str">
+        <v>neovascularization</v>
+      </c>
+      <c r="D162" t="str">
+        <v>0.5642985728460055</v>
+      </c>
+      <c r="E162" t="str">
+        <v>0.7214716968249216</v>
+      </c>
+      <c r="F162" t="str">
+        <v>0.669710865635012</v>
+      </c>
+      <c r="G162" t="str">
+        <v>0.781903726319306</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>371</v>
+      </c>
+      <c r="B163" t="str" cm="1">
+        <f t="array" ref="B163:G163">_xlfn.TEXTSPLIT(A163,",")</f>
+        <v>TransUNet_TVERSKY_2_Fold_2</v>
+      </c>
+      <c r="C163" t="str">
+        <v>soft_exudates</v>
+      </c>
+      <c r="D163" t="str">
+        <v>0.27756885975704054</v>
+      </c>
+      <c r="E163" t="str">
+        <v>0.43452665214433417</v>
+      </c>
+      <c r="F163" t="str">
+        <v>0.5471507357638734</v>
+      </c>
+      <c r="G163" t="str">
+        <v>0.36035260886731924</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>372</v>
+      </c>
+      <c r="B164" t="str" cm="1">
+        <f t="array" ref="B164:G164">_xlfn.TEXTSPLIT(A164,",")</f>
+        <v>TransUNet_TVERSKY_2_Fold_2</v>
+      </c>
+      <c r="C164" t="str">
+        <v>subretinal_hemorrhage</v>
+      </c>
+      <c r="D164" t="str">
+        <v>0.58265345859768</v>
+      </c>
+      <c r="E164" t="str">
+        <v>0.7362994791215302</v>
+      </c>
+      <c r="F164" t="str">
+        <v>0.67523595720459</v>
+      </c>
+      <c r="G164" t="str">
+        <v>0.8095053685387372</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>373</v>
+      </c>
+      <c r="B165" t="str" cm="1">
+        <f t="array" ref="B165:G165">_xlfn.TEXTSPLIT(A165,",")</f>
+        <v>TransUNet_TVERSKY_2_Fold_2</v>
+      </c>
+      <c r="C165" t="str">
+        <v>venous_anomalies</v>
+      </c>
+      <c r="D165" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="E165" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="F165" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="G165" t="str">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>374</v>
+      </c>
+      <c r="B166" t="str" cm="1">
+        <f t="array" ref="B166:G166">_xlfn.TEXTSPLIT(A166,",")</f>
+        <v>TransUNet_TVERSKY_2_Fold_2</v>
+      </c>
+      <c r="C166" t="str">
+        <v>MEAN</v>
+      </c>
+      <c r="D166" t="str">
+        <v>0.4383681440729787</v>
+      </c>
+      <c r="E166" t="str">
+        <v>0.5649775492252944</v>
+      </c>
+      <c r="F166" t="str">
+        <v>0.547984094487236</v>
+      </c>
+      <c r="G166" t="str">
+        <v>0.5926819449275075</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>375</v>
+      </c>
+      <c r="B167" t="str" cm="1">
+        <f t="array" ref="B167:G167">_xlfn.TEXTSPLIT(A167,",")</f>
+        <v>TransUNet_TVERSKY_3_Fold_3</v>
+      </c>
+      <c r="C167" t="str">
+        <v>drusen</v>
+      </c>
+      <c r="D167" t="str">
+        <v>0.21260467106935865</v>
+      </c>
+      <c r="E167" t="str">
+        <v>0.3506578461088545</v>
+      </c>
+      <c r="F167" t="str">
+        <v>0.2704425757837189</v>
+      </c>
+      <c r="G167" t="str">
+        <v>0.49852365248948505</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>376</v>
+      </c>
+      <c r="B168" t="str" cm="1">
+        <f t="array" ref="B168:G168">_xlfn.TEXTSPLIT(A168,",")</f>
+        <v>TransUNet_TVERSKY_3_Fold_3</v>
+      </c>
+      <c r="C168" t="str">
+        <v>edema</v>
+      </c>
+      <c r="D168" t="str">
+        <v>0.2923664644977183</v>
+      </c>
+      <c r="E168" t="str">
+        <v>0.45245133254265824</v>
+      </c>
+      <c r="F168" t="str">
+        <v>0.5318745982287642</v>
+      </c>
+      <c r="G168" t="str">
+        <v>0.3936663039733882</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>377</v>
+      </c>
+      <c r="B169" t="str" cm="1">
+        <f t="array" ref="B169:G169">_xlfn.TEXTSPLIT(A169,",")</f>
+        <v>TransUNet_TVERSKY_3_Fold_3</v>
+      </c>
+      <c r="C169" t="str">
+        <v>epiretinal_fibrosis</v>
+      </c>
+      <c r="D169" t="str">
+        <v>0.6428250649747695</v>
+      </c>
+      <c r="E169" t="str">
+        <v>0.7825849248101678</v>
+      </c>
+      <c r="F169" t="str">
+        <v>0.7223645923184511</v>
+      </c>
+      <c r="G169" t="str">
+        <v>0.8537590287545256</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>378</v>
+      </c>
+      <c r="B170" t="str" cm="1">
+        <f t="array" ref="B170:G170">_xlfn.TEXTSPLIT(A170,",")</f>
+        <v>TransUNet_TVERSKY_3_Fold_3</v>
+      </c>
+      <c r="C170" t="str">
+        <v>fibrosis</v>
+      </c>
+      <c r="D170" t="str">
+        <v>0.42902692307614465</v>
+      </c>
+      <c r="E170" t="str">
+        <v>0.6004462423319707</v>
+      </c>
+      <c r="F170" t="str">
+        <v>0.5587069605059082</v>
+      </c>
+      <c r="G170" t="str">
+        <v>0.648925472201991</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>379</v>
+      </c>
+      <c r="B171" t="str" cm="1">
+        <f t="array" ref="B171:G171">_xlfn.TEXTSPLIT(A171,",")</f>
+        <v>TransUNet_TVERSKY_3_Fold_3</v>
+      </c>
+      <c r="C171" t="str">
+        <v>geographic_atrophy</v>
+      </c>
+      <c r="D171" t="str">
+        <v>0.7659690068612773</v>
+      </c>
+      <c r="E171" t="str">
+        <v>0.8674772930728413</v>
+      </c>
+      <c r="F171" t="str">
+        <v>0.8272273481163372</v>
+      </c>
+      <c r="G171" t="str">
+        <v>0.911844403433319</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>380</v>
+      </c>
+      <c r="B172" t="str" cm="1">
+        <f t="array" ref="B172:G172">_xlfn.TEXTSPLIT(A172,",")</f>
+        <v>TransUNet_TVERSKY_3_Fold_3</v>
+      </c>
+      <c r="C172" t="str">
+        <v>hard_exudates</v>
+      </c>
+      <c r="D172" t="str">
+        <v>0.46496957222268476</v>
+      </c>
+      <c r="E172" t="str">
+        <v>0.6347839314057868</v>
+      </c>
+      <c r="F172" t="str">
+        <v>0.5774148145922638</v>
+      </c>
+      <c r="G172" t="str">
+        <v>0.7048104572817</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>381</v>
+      </c>
+      <c r="B173" t="str" cm="1">
+        <f t="array" ref="B173:G173">_xlfn.TEXTSPLIT(A173,",")</f>
+        <v>TransUNet_TVERSKY_3_Fold_3</v>
+      </c>
+      <c r="C173" t="str">
+        <v>hemorrhages</v>
+      </c>
+      <c r="D173" t="str">
+        <v>0.5129100419092395</v>
+      </c>
+      <c r="E173" t="str">
+        <v>0.6780443353551477</v>
+      </c>
+      <c r="F173" t="str">
+        <v>0.6272859313033132</v>
+      </c>
+      <c r="G173" t="str">
+        <v>0.737740441286266</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>382</v>
+      </c>
+      <c r="B174" t="str" cm="1">
+        <f t="array" ref="B174:G174">_xlfn.TEXTSPLIT(A174,",")</f>
+        <v>TransUNet_TVERSKY_3_Fold_3</v>
+      </c>
+      <c r="C174" t="str">
+        <v>laser_coagulates</v>
+      </c>
+      <c r="D174" t="str">
+        <v>0.6142691039793988</v>
+      </c>
+      <c r="E174" t="str">
+        <v>0.7610491986313058</v>
+      </c>
+      <c r="F174" t="str">
+        <v>0.6825095093501308</v>
+      </c>
+      <c r="G174" t="str">
+        <v>0.8600153482666558</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>383</v>
+      </c>
+      <c r="B175" t="str" cm="1">
+        <f t="array" ref="B175:G175">_xlfn.TEXTSPLIT(A175,",")</f>
+        <v>TransUNet_TVERSKY_3_Fold_3</v>
+      </c>
+      <c r="C175" t="str">
+        <v>macular_hole</v>
+      </c>
+      <c r="D175" t="str">
+        <v>0.778602533327561</v>
+      </c>
+      <c r="E175" t="str">
+        <v>0.8755216736039223</v>
+      </c>
+      <c r="F175" t="str">
+        <v>0.7996775224085464</v>
+      </c>
+      <c r="G175" t="str">
+        <v>0.967259911751479</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>384</v>
+      </c>
+      <c r="B176" t="str" cm="1">
+        <f t="array" ref="B176:G176">_xlfn.TEXTSPLIT(A176,",")</f>
+        <v>TransUNet_TVERSKY_3_Fold_3</v>
+      </c>
+      <c r="C176" t="str">
+        <v>microaneurysms</v>
+      </c>
+      <c r="D176" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="E176" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="F176" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="G176" t="str">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>385</v>
+      </c>
+      <c r="B177" t="str" cm="1">
+        <f t="array" ref="B177:G177">_xlfn.TEXTSPLIT(A177,",")</f>
+        <v>TransUNet_TVERSKY_3_Fold_3</v>
+      </c>
+      <c r="C177" t="str">
+        <v>neovascularization</v>
+      </c>
+      <c r="D177" t="str">
+        <v>0.6232912734091975</v>
+      </c>
+      <c r="E177" t="str">
+        <v>0.7679352234798579</v>
+      </c>
+      <c r="F177" t="str">
+        <v>0.7195371714955504</v>
+      </c>
+      <c r="G177" t="str">
+        <v>0.8233135612730872</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>386</v>
+      </c>
+      <c r="B178" t="str" cm="1">
+        <f t="array" ref="B178:G178">_xlfn.TEXTSPLIT(A178,",")</f>
+        <v>TransUNet_TVERSKY_3_Fold_3</v>
+      </c>
+      <c r="C178" t="str">
+        <v>soft_exudates</v>
+      </c>
+      <c r="D178" t="str">
+        <v>0.4579914842314886</v>
+      </c>
+      <c r="E178" t="str">
+        <v>0.6282498755099344</v>
+      </c>
+      <c r="F178" t="str">
+        <v>0.5881256100937666</v>
+      </c>
+      <c r="G178" t="str">
+        <v>0.6742498807972258</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>387</v>
+      </c>
+      <c r="B179" t="str" cm="1">
+        <f t="array" ref="B179:G179">_xlfn.TEXTSPLIT(A179,",")</f>
+        <v>TransUNet_TVERSKY_3_Fold_3</v>
+      </c>
+      <c r="C179" t="str">
+        <v>subretinal_hemorrhage</v>
+      </c>
+      <c r="D179" t="str">
+        <v>0.5256744898271786</v>
+      </c>
+      <c r="E179" t="str">
+        <v>0.6891043841032232</v>
+      </c>
+      <c r="F179" t="str">
+        <v>0.6703328301659763</v>
+      </c>
+      <c r="G179" t="str">
+        <v>0.7089575592173939</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>388</v>
+      </c>
+      <c r="B180" t="str" cm="1">
+        <f t="array" ref="B180:G180">_xlfn.TEXTSPLIT(A180,",")</f>
+        <v>TransUNet_TVERSKY_3_Fold_3</v>
+      </c>
+      <c r="C180" t="str">
+        <v>venous_anomalies</v>
+      </c>
+      <c r="D180" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="E180" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="F180" t="str">
+        <v>0.0</v>
+      </c>
+      <c r="G180" t="str">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>389</v>
+      </c>
+      <c r="B181" t="str" cm="1">
+        <f t="array" ref="B181:G181">_xlfn.TEXTSPLIT(A181,",")</f>
+        <v>TransUNet_TVERSKY_3_Fold_3</v>
+      </c>
+      <c r="C181" t="str">
+        <v>MEAN</v>
+      </c>
+      <c r="D181" t="str">
+        <v>0.4514643306704298</v>
+      </c>
+      <c r="E181" t="str">
+        <v>0.5777361614968336</v>
+      </c>
+      <c r="F181" t="str">
+        <v>0.5411071045973376</v>
+      </c>
+      <c r="G181" t="str">
+        <v>0.6273618586233226</v>
       </c>
     </row>
   </sheetData>
@@ -3390,7 +5846,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47FF012F-A572-4070-8576-1CD113E43C0F}">
-  <dimension ref="A1:R91"/>
+  <dimension ref="A1:R181"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" customWidth="1"/>
@@ -3403,1872 +5859,3592 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="G1" s="2"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="4" t="s">
+      <c r="H1" s="1"/>
+      <c r="I1" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="3">
         <v>0.33971188298596999</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="3">
         <v>0.50714170307844897</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="3">
         <v>0.58487299440614704</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="3">
         <v>0.44764800478042499</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="5" t="s">
+      <c r="H2" s="1"/>
+      <c r="I2" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="Q2" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="R2" s="2" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="5"/>
+      <c r="B3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="3">
         <v>0.369328801790407</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="3">
         <v>0.53943041482441201</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="3">
         <v>0.54435978810580099</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="3">
         <v>0.53458951487421003</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="3">
         <v>0.46134664184725299</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="3">
         <v>0.608489664053254</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="3">
         <v>0.62419701880038703</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="3">
         <v>0.61500231410869299</v>
       </c>
       <c r="N3" t="s">
         <v>298</v>
       </c>
-      <c r="O3" s="7">
+      <c r="O3" s="4">
         <f>AVERAGE(I3:I5)</f>
         <v>0.48235261073196534</v>
       </c>
-      <c r="P3" s="7">
+      <c r="P3" s="4">
         <f>AVERAGE(J3:J5)</f>
         <v>0.62677504211025326</v>
       </c>
-      <c r="Q3" s="7">
-        <f t="shared" ref="P3:R3" si="0">AVERAGE(K3:K5)</f>
+      <c r="Q3" s="4">
+        <f t="shared" ref="Q3:R3" si="0">AVERAGE(K3:K5)</f>
         <v>0.6453518346409034</v>
       </c>
-      <c r="R3" s="7">
+      <c r="R3" s="4">
         <f t="shared" si="0"/>
         <v>0.63652623645490536</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="4"/>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="5"/>
+      <c r="B4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="3">
         <v>0.61370826912064302</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="3">
         <v>0.76061860853581698</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="3">
         <v>0.70173546729434699</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="3">
         <v>0.83028875071652097</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="3">
         <v>0.494077291772059</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="3">
         <v>0.64189951299723702</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="3">
         <v>0.63425758562163403</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="3">
         <v>0.65991566761756504</v>
       </c>
       <c r="N4" t="s">
         <v>299</v>
       </c>
-      <c r="O4" s="7">
+      <c r="O4" s="4">
         <f>AVERAGE(I6:I8)</f>
         <v>0.49060027696865899</v>
       </c>
-      <c r="P4" s="7">
+      <c r="P4" s="4">
         <f t="shared" ref="P4:R4" si="1">AVERAGE(J6:J8)</f>
         <v>0.63309321610143998</v>
       </c>
-      <c r="Q4" s="7">
+      <c r="Q4" s="4">
         <f t="shared" si="1"/>
         <v>0.62647291276647499</v>
       </c>
-      <c r="R4" s="7">
+      <c r="R4" s="4">
         <f t="shared" si="1"/>
         <v>0.64843435211098999</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="5"/>
+      <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="3">
         <v>0.32915328187489001</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="3">
         <v>0.49528265304448499</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="3">
         <v>0.62144706560014995</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="3">
         <v>0.41170040906327598</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="3">
         <v>0.49163389857658402</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="3">
         <v>0.62993594928026897</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="3">
         <v>0.67760089950068902</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="3">
         <v>0.63466072763845804</v>
       </c>
+      <c r="N5" t="s">
+        <v>396</v>
+      </c>
+      <c r="O5" s="4">
+        <f>AVERAGE(I9:I11)</f>
+        <v>0.42794431539406697</v>
+      </c>
+      <c r="P5" s="4">
+        <f t="shared" ref="P5:R5" si="2">AVERAGE(J9:J11)</f>
+        <v>0.55687483401917792</v>
+      </c>
+      <c r="Q5" s="4">
+        <f t="shared" si="2"/>
+        <v>0.54332934741445038</v>
+      </c>
+      <c r="R5" s="4">
+        <f t="shared" si="2"/>
+        <v>0.57794372239386593</v>
+      </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="4"/>
-      <c r="B6" s="3" t="s">
+      <c r="A6" s="5"/>
+      <c r="B6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="3">
         <v>0.71644917826667898</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="3">
         <v>0.83480383496139399</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="3">
         <v>0.81181673677266797</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="3">
         <v>0.85913065634836305</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="3">
         <v>0.479617171604384</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="3">
         <v>0.62640641628480997</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="3">
         <v>0.62044992181797898</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="3">
         <v>0.64361895944876601</v>
       </c>
+      <c r="N6" t="s">
+        <v>397</v>
+      </c>
+      <c r="O6" s="4">
+        <f>AVERAGE(I12:I14)</f>
+        <v>0.45125409018044632</v>
+      </c>
+      <c r="P6" s="4">
+        <f t="shared" ref="P6:R6" si="3">AVERAGE(J12:J14)</f>
+        <v>0.57800902150615874</v>
+      </c>
+      <c r="Q6" s="4">
+        <f t="shared" si="3"/>
+        <v>0.55671318671804237</v>
+      </c>
+      <c r="R6" s="4">
+        <f t="shared" si="3"/>
+        <v>0.60846202232782765</v>
+      </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="3" t="s">
+      <c r="A7" s="5"/>
+      <c r="B7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="3">
         <v>0.58270324189242395</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="3">
         <v>0.73633922831381904</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="3">
         <v>0.72522717384876201</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="3">
         <v>0.74779710308453295</v>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="3">
         <v>0.50291469212262296</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="3">
         <v>0.64961111726211496</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="3">
         <v>0.63982373802536097</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="3">
         <v>0.66656018785672599</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" s="4"/>
-      <c r="B8" s="3" t="s">
+      <c r="A8" s="5"/>
+      <c r="B8" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="3">
         <v>0.54465806541614803</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="3">
         <v>0.70521506035630099</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="3">
         <v>0.72748889133609795</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="3">
         <v>0.68426464418961197</v>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="3">
         <v>0.48926896717897</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="3">
         <v>0.62326211475739501</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="3">
         <v>0.61914507845608502</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="3">
         <v>0.63512390902747795</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
-      <c r="B9" s="3" t="s">
+      <c r="A9" s="5"/>
+      <c r="B9" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="3">
         <v>0.54135660125221696</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="3">
         <v>0.70244173322696701</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="3">
         <v>0.60942028827127703</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="3">
         <v>0.82897599229386798</v>
       </c>
-      <c r="G9" s="2"/>
+      <c r="H9" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0.45164687109993101</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0.57961341402462097</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0.56649028126595602</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0.59881034694954405</v>
+      </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="4"/>
-      <c r="B10" s="3" t="s">
+      <c r="A10" s="5"/>
+      <c r="B10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="3">
         <v>0.72637375403692295</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="3">
         <v>0.84150231354987104</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="3">
         <v>0.74544208841279502</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="3">
         <v>0.96598207848368101</v>
       </c>
-      <c r="G10" s="2"/>
+      <c r="H10" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0.41016298164486698</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0.539034193955096</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0.525532334826462</v>
+      </c>
+      <c r="L10" s="3">
+        <v>0.559667841173214</v>
+      </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
-      <c r="B11" s="3" t="s">
+      <c r="A11" s="5"/>
+      <c r="B11" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="3">
         <v>0.162017006564732</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="3">
         <v>0.27885479411992897</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="3">
         <v>0.31349026052461298</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="3">
         <v>0.25111117994126497</v>
       </c>
-      <c r="G11" s="2"/>
+      <c r="H11" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0.42202309343740302</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0.55197689407781703</v>
+      </c>
+      <c r="K11" s="3">
+        <v>0.53796542615093301</v>
+      </c>
+      <c r="L11" s="3">
+        <v>0.57535297905883998</v>
+      </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" s="4"/>
-      <c r="B12" s="3" t="s">
+      <c r="A12" s="5"/>
+      <c r="B12" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="3">
         <v>0.585951062806081</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="3">
         <v>0.738927040749084</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="3">
         <v>0.67427258870173101</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="3">
         <v>0.81729564570034896</v>
       </c>
-      <c r="G12" s="2"/>
+      <c r="H12" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0.46392979579793198</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0.59131335379634897</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0.58104836106955404</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0.60534226343265396</v>
+      </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="4"/>
-      <c r="B13" s="3" t="s">
+      <c r="A13" s="5"/>
+      <c r="B13" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="3">
         <v>0.32011139129892502</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="3">
         <v>0.484976333677344</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="3">
         <v>0.71479160205688597</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="3">
         <v>0.36698548502905698</v>
       </c>
-      <c r="G13" s="2"/>
+      <c r="H13" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0.43836814407297803</v>
+      </c>
+      <c r="J13" s="3">
+        <v>0.56497754922529397</v>
+      </c>
+      <c r="K13" s="3">
+        <v>0.54798409448723595</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0.59268194492750703</v>
+      </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="4"/>
-      <c r="B14" s="3" t="s">
+      <c r="A14" s="5"/>
+      <c r="B14" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="3">
         <v>0.498890140468289</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="3">
         <v>0.66567939437165702</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="3">
         <v>0.64537090292710197</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="3">
         <v>0.68730754547635098</v>
       </c>
-      <c r="G14" s="2"/>
+      <c r="H14" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0.45146433067042901</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0.57773616149683304</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0.54110710459733702</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0.62736185862332206</v>
+      </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="4"/>
-      <c r="B15" s="3" t="s">
+      <c r="A15" s="5"/>
+      <c r="B15" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="3">
         <v>0.12844030808720799</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="3">
         <v>0.227642183936029</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="3">
         <v>0.31902241494704098</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="3">
         <v>0.176955387540189</v>
       </c>
-      <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="4"/>
-      <c r="B16" s="3" t="s">
+      <c r="A16" s="5"/>
+      <c r="B16" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="3">
         <v>0.46134664184725299</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="3">
         <v>0.608489664053254</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="3">
         <v>0.62419701880038703</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="3">
         <v>0.61500231410869299</v>
       </c>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="3">
         <v>0.362191524818194</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="3">
         <v>0.53177768062612796</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="3">
         <v>0.57806551088236602</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="3">
         <v>0.49235315385095202</v>
       </c>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="4"/>
-      <c r="B18" s="3" t="s">
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
+      <c r="B18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="3">
         <v>0.305468086594191</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="3">
         <v>0.46798246503462299</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="3">
         <v>0.47158010680510298</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="3">
         <v>0.46443929983147703</v>
       </c>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="3" t="s">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="5"/>
+      <c r="B19" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="3">
         <v>0.62163749441418203</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="3">
         <v>0.766678738689067</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="3">
         <v>0.70895581763779303</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="3">
         <v>0.83463436030615401</v>
       </c>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="4"/>
-      <c r="B20" s="3" t="s">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="5"/>
+      <c r="B20" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="3">
         <v>0.39795410082275301</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="3">
         <v>0.56933786393779395</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="3">
         <v>0.553470158047081</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="3">
         <v>0.58614226232022704</v>
       </c>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="4"/>
-      <c r="B21" s="3" t="s">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="5"/>
+      <c r="B21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="3">
         <v>0.74578354144299097</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="3">
         <v>0.85438260097991003</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="3">
         <v>0.803987847007818</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="3">
         <v>0.911517414677537</v>
       </c>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="4"/>
-      <c r="B22" s="3" t="s">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="5"/>
+      <c r="B22" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="3">
         <v>0.56862375917376295</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="3">
         <v>0.72499699924636196</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="3">
         <v>0.77104957880960401</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="3">
         <v>0.68413554557280698</v>
       </c>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="4"/>
-      <c r="B23" s="3" t="s">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="5"/>
+      <c r="B23" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="3">
         <v>0.52737845711995102</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="3">
         <v>0.69056683975284505</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="3">
         <v>0.692953002666861</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="3">
         <v>0.68819705380630702</v>
       </c>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="4"/>
-      <c r="B24" s="3" t="s">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="5"/>
+      <c r="B24" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="3">
         <v>0.60125874921646305</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="3">
         <v>0.75098262477650701</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="3">
         <v>0.73435308503088403</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="3">
         <v>0.76838277207419603</v>
       </c>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="4"/>
-      <c r="B25" s="3" t="s">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="5"/>
+      <c r="B25" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="3">
         <v>0.80415464417522697</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="3">
         <v>0.89144757825662801</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="3">
         <v>0.81105125003510203</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="3">
         <v>0.989536443402114</v>
       </c>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="4"/>
-      <c r="B26" s="3" t="s">
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="5"/>
+      <c r="B26" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="3">
         <v>0.13451248083758299</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="3">
         <v>0.23712825219564901</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="3">
         <v>0.35137891953110201</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26" s="3">
         <v>0.178944533158782</v>
       </c>
-      <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="4"/>
-      <c r="B27" s="3" t="s">
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="5"/>
+      <c r="B27" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="3">
         <v>0.57575994762528604</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="3">
         <v>0.73077114124263998</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="3">
         <v>0.63027987242098205</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27" s="3">
         <v>0.86938514445598702</v>
       </c>
-      <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="4"/>
-      <c r="B28" s="3" t="s">
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="5"/>
+      <c r="B28" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="3">
         <v>0.49112218735145702</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28" s="3">
         <v>0.65872829405589095</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="3">
         <v>0.64140720895849701</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="3">
         <v>0.67701084898082098</v>
       </c>
-      <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="4"/>
-      <c r="B29" s="3" t="s">
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="5"/>
+      <c r="B29" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="3">
         <v>0.47939236775147798</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="3">
         <v>0.64809360680980699</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="3">
         <v>0.67112210178944198</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29" s="3">
         <v>0.62659305571869595</v>
       </c>
-      <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="4"/>
-      <c r="B30" s="3" t="s">
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="5"/>
+      <c r="B30" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="3">
         <v>0.30184474346530799</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="3">
         <v>0.46371849635747597</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="3">
         <v>0.45995173908024101</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30" s="3">
         <v>0.46754745848985801</v>
       </c>
-      <c r="G30" s="2"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="4"/>
-      <c r="B31" s="3" t="s">
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="5"/>
+      <c r="B31" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="3">
         <v>0.494077291772059</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="3">
         <v>0.64189951299723702</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="3">
         <v>0.63425758562163403</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F31" s="3">
         <v>0.65991566761756504</v>
       </c>
-      <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="3">
         <v>0.36945233038494302</v>
       </c>
-      <c r="D32" s="6">
+      <c r="D32" s="3">
         <v>0.53956216246109501</v>
       </c>
-      <c r="E32" s="6">
+      <c r="E32" s="3">
         <v>0.58332883739475505</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F32" s="3">
         <v>0.50190467439636599</v>
       </c>
-      <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="4"/>
-      <c r="B33" s="3" t="s">
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="5"/>
+      <c r="B33" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="3">
         <v>0.41263959909724102</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="3">
         <v>0.58421072064090795</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E33" s="3">
         <v>0.58173745838649504</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F33" s="3">
         <v>0.58670510288243205</v>
       </c>
-      <c r="G33" s="2"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="4"/>
-      <c r="B34" s="3" t="s">
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="5"/>
+      <c r="B34" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="3">
         <v>0.60407341520808899</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="3">
         <v>0.75317427429557604</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E34" s="3">
         <v>0.69393849897559601</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F34" s="3">
         <v>0.82346680720293997</v>
       </c>
-      <c r="G34" s="2"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="4"/>
-      <c r="B35" s="3" t="s">
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="5"/>
+      <c r="B35" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="3">
         <v>0.39101377937631698</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D35" s="3">
         <v>0.56219972105759397</v>
       </c>
-      <c r="E35" s="6">
+      <c r="E35" s="3">
         <v>0.60676431554863597</v>
       </c>
-      <c r="F35" s="6">
+      <c r="F35" s="3">
         <v>0.52373343742466505</v>
       </c>
-      <c r="G35" s="2"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="4"/>
-      <c r="B36" s="3" t="s">
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="5"/>
+      <c r="B36" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="3">
         <v>0.79108313280514897</v>
       </c>
-      <c r="D36" s="6">
+      <c r="D36" s="3">
         <v>0.88335724714929897</v>
       </c>
-      <c r="E36" s="6">
+      <c r="E36" s="3">
         <v>0.82561253355201503</v>
       </c>
-      <c r="F36" s="6">
+      <c r="F36" s="3">
         <v>0.94978692412641696</v>
       </c>
-      <c r="G36" s="2"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="4"/>
-      <c r="B37" s="3" t="s">
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="5"/>
+      <c r="B37" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="3">
         <v>0.49878937317280603</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D37" s="3">
         <v>0.66558968471588897</v>
       </c>
-      <c r="E37" s="6">
+      <c r="E37" s="3">
         <v>0.71704993541002504</v>
       </c>
-      <c r="F37" s="6">
+      <c r="F37" s="3">
         <v>0.62102109908847802</v>
       </c>
-      <c r="G37" s="2"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="4"/>
-      <c r="B38" s="3" t="s">
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="5"/>
+      <c r="B38" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="3">
         <v>0.58011168863526796</v>
       </c>
-      <c r="D38" s="6">
+      <c r="D38" s="3">
         <v>0.73426668862415201</v>
       </c>
-      <c r="E38" s="6">
+      <c r="E38" s="3">
         <v>0.79692390627595899</v>
       </c>
-      <c r="F38" s="6">
+      <c r="F38" s="3">
         <v>0.68074398268876002</v>
       </c>
-      <c r="G38" s="2"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="4"/>
-      <c r="B39" s="3" t="s">
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="5"/>
+      <c r="B39" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39" s="3">
         <v>0.64594001498533105</v>
       </c>
-      <c r="D39" s="6">
+      <c r="D39" s="3">
         <v>0.78488888915078403</v>
       </c>
-      <c r="E39" s="6">
+      <c r="E39" s="3">
         <v>0.72174457903225797</v>
       </c>
-      <c r="F39" s="6">
+      <c r="F39" s="3">
         <v>0.86014131427787199</v>
       </c>
-      <c r="G39" s="2"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="4"/>
-      <c r="B40" s="3" t="s">
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="5"/>
+      <c r="B40" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40" s="3">
         <v>0.75102696645043399</v>
       </c>
-      <c r="D40" s="6">
+      <c r="D40" s="3">
         <v>0.85781313576553997</v>
       </c>
-      <c r="E40" s="6">
+      <c r="E40" s="3">
         <v>0.76640146623886796</v>
       </c>
-      <c r="F40" s="6">
+      <c r="F40" s="3">
         <v>0.97398397459010699</v>
       </c>
-      <c r="G40" s="2"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="4"/>
-      <c r="B41" s="3" t="s">
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="5"/>
+      <c r="B41" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41" s="3">
         <v>0.15356190634887701</v>
       </c>
-      <c r="D41" s="6">
+      <c r="D41" s="3">
         <v>0.26623955854248699</v>
       </c>
-      <c r="E41" s="6">
+      <c r="E41" s="3">
         <v>0.34217048650724302</v>
       </c>
-      <c r="F41" s="6">
+      <c r="F41" s="3">
         <v>0.217888091550582</v>
       </c>
-      <c r="G41" s="2"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="4"/>
-      <c r="B42" s="3" t="s">
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="5"/>
+      <c r="B42" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="6">
+      <c r="C42" s="3">
         <v>0.59565915197838104</v>
       </c>
-      <c r="D42" s="6">
+      <c r="D42" s="3">
         <v>0.74659948678870702</v>
       </c>
-      <c r="E42" s="6">
+      <c r="E42" s="3">
         <v>0.70405163715291597</v>
       </c>
-      <c r="F42" s="6">
+      <c r="F42" s="3">
         <v>0.794620682285197</v>
       </c>
-      <c r="G42" s="2"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="4"/>
-      <c r="B43" s="3" t="s">
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="5"/>
+      <c r="B43" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C43" s="6">
+      <c r="C43" s="3">
         <v>0.51716625236911296</v>
       </c>
-      <c r="D43" s="6">
+      <c r="D43" s="3">
         <v>0.68175290817540701</v>
       </c>
-      <c r="E43" s="6">
+      <c r="E43" s="3">
         <v>0.82851294186704205</v>
       </c>
-      <c r="F43" s="6">
+      <c r="F43" s="3">
         <v>0.57916206204239695</v>
       </c>
-      <c r="G43" s="2"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="4"/>
-      <c r="B44" s="3" t="s">
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="5"/>
+      <c r="B44" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C44" s="6">
+      <c r="C44" s="3">
         <v>0.54434607471601104</v>
       </c>
-      <c r="D44" s="6">
+      <c r="D44" s="3">
         <v>0.70495348630469501</v>
       </c>
-      <c r="E44" s="6">
+      <c r="E44" s="3">
         <v>0.67008619753750498</v>
       </c>
-      <c r="F44" s="6">
+      <c r="F44" s="3">
         <v>0.74364851952088196</v>
       </c>
-      <c r="G44" s="2"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="4"/>
-      <c r="B45" s="3" t="s">
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="5"/>
+      <c r="B45" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C45" s="6">
+      <c r="C45" s="3">
         <v>2.8010894544210501E-2</v>
       </c>
-      <c r="D45" s="6">
+      <c r="D45" s="3">
         <v>5.4495326251634203E-2</v>
       </c>
-      <c r="E45" s="6">
+      <c r="E45" s="3">
         <v>0.64808979913032605</v>
       </c>
-      <c r="F45" s="6">
+      <c r="F45" s="3">
         <v>2.84435148613198E-2</v>
       </c>
-      <c r="G45" s="2"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="4"/>
-      <c r="B46" s="3" t="s">
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="5"/>
+      <c r="B46" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C46" s="6">
+      <c r="C46" s="3">
         <v>0.49163389857658402</v>
       </c>
-      <c r="D46" s="6">
+      <c r="D46" s="3">
         <v>0.62993594928026897</v>
       </c>
-      <c r="E46" s="6">
+      <c r="E46" s="3">
         <v>0.67760089950068902</v>
       </c>
-      <c r="F46" s="6">
+      <c r="F46" s="3">
         <v>0.63466072763845804</v>
       </c>
-      <c r="G46" s="2"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="4" t="s">
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C47" s="6">
+      <c r="C47" s="3">
         <v>0.34256749633908401</v>
       </c>
-      <c r="D47" s="6">
+      <c r="D47" s="3">
         <v>0.51031698186228602</v>
       </c>
-      <c r="E47" s="6">
+      <c r="E47" s="3">
         <v>0.518793846507694</v>
       </c>
-      <c r="F47" s="6">
+      <c r="F47" s="3">
         <v>0.50211268018194299</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="4"/>
-      <c r="B48" s="3" t="s">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="5"/>
+      <c r="B48" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C48" s="6">
+      <c r="C48" s="3">
         <v>0.38120064752059302</v>
       </c>
-      <c r="D48" s="6">
+      <c r="D48" s="3">
         <v>0.551984461062758</v>
       </c>
-      <c r="E48" s="6">
+      <c r="E48" s="3">
         <v>0.58468756733620098</v>
       </c>
-      <c r="F48" s="6">
+      <c r="F48" s="3">
         <v>0.52274591363559098</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="4"/>
-      <c r="B49" s="3" t="s">
+      <c r="A49" s="5"/>
+      <c r="B49" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C49" s="6">
+      <c r="C49" s="3">
         <v>0.64096333366603198</v>
       </c>
-      <c r="D49" s="6">
+      <c r="D49" s="3">
         <v>0.78120372407599503</v>
       </c>
-      <c r="E49" s="6">
+      <c r="E49" s="3">
         <v>0.74514303806055604</v>
       </c>
-      <c r="F49" s="6">
+      <c r="F49" s="3">
         <v>0.82093217328466905</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="4"/>
-      <c r="B50" s="3" t="s">
+      <c r="A50" s="5"/>
+      <c r="B50" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C50" s="6">
+      <c r="C50" s="3">
         <v>0.35744492886734203</v>
       </c>
-      <c r="D50" s="6">
+      <c r="D50" s="3">
         <v>0.526643727883084</v>
       </c>
-      <c r="E50" s="6">
+      <c r="E50" s="3">
         <v>0.58727205537472305</v>
       </c>
-      <c r="F50" s="6">
+      <c r="F50" s="3">
         <v>0.47736218823611198</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="4"/>
-      <c r="B51" s="3" t="s">
+      <c r="A51" s="5"/>
+      <c r="B51" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C51" s="6">
+      <c r="C51" s="3">
         <v>0.73036661655678903</v>
       </c>
-      <c r="D51" s="6">
+      <c r="D51" s="3">
         <v>0.84417557478093996</v>
       </c>
-      <c r="E51" s="6">
+      <c r="E51" s="3">
         <v>0.82548553298020599</v>
       </c>
-      <c r="F51" s="6">
+      <c r="F51" s="3">
         <v>0.86373155514065403</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="4"/>
-      <c r="B52" s="3" t="s">
+      <c r="A52" s="5"/>
+      <c r="B52" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="6">
+      <c r="C52" s="3">
         <v>0.58046584160867498</v>
       </c>
-      <c r="D52" s="6">
+      <c r="D52" s="3">
         <v>0.73455031589654396</v>
       </c>
-      <c r="E52" s="6">
+      <c r="E52" s="3">
         <v>0.73343925763717799</v>
       </c>
-      <c r="F52" s="6">
+      <c r="F52" s="3">
         <v>0.73566474545979299</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="4"/>
-      <c r="B53" s="3" t="s">
+      <c r="A53" s="5"/>
+      <c r="B53" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C53" s="6">
+      <c r="C53" s="3">
         <v>0.54060936226362899</v>
       </c>
-      <c r="D53" s="6">
+      <c r="D53" s="3">
         <v>0.70181238087415898</v>
       </c>
-      <c r="E53" s="6">
+      <c r="E53" s="3">
         <v>0.70639451239581197</v>
       </c>
-      <c r="F53" s="6">
+      <c r="F53" s="3">
         <v>0.69728931157194496</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="4"/>
-      <c r="B54" s="3" t="s">
+      <c r="A54" s="5"/>
+      <c r="B54" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C54" s="6">
+      <c r="C54" s="3">
         <v>0.53895431549331596</v>
       </c>
-      <c r="D54" s="6">
+      <c r="D54" s="3">
         <v>0.70041626326061901</v>
       </c>
-      <c r="E54" s="6">
+      <c r="E54" s="3">
         <v>0.58991251530559696</v>
       </c>
-      <c r="F54" s="6">
+      <c r="F54" s="3">
         <v>0.86186225150709905</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="4"/>
-      <c r="B55" s="3" t="s">
+      <c r="A55" s="5"/>
+      <c r="B55" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C55" s="6">
+      <c r="C55" s="3">
         <v>0.78202710114089902</v>
       </c>
-      <c r="D55" s="6">
+      <c r="D55" s="3">
         <v>0.87768261284042803</v>
       </c>
-      <c r="E55" s="6">
+      <c r="E55" s="3">
         <v>0.80595276252695902</v>
       </c>
-      <c r="F55" s="6">
+      <c r="F55" s="3">
         <v>0.96342774745061999</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="4"/>
-      <c r="B56" s="3" t="s">
+      <c r="A56" s="5"/>
+      <c r="B56" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C56" s="6">
+      <c r="C56" s="3">
         <v>0.141580695039356</v>
       </c>
-      <c r="D56" s="6">
+      <c r="D56" s="3">
         <v>0.24804325380515499</v>
       </c>
-      <c r="E56" s="6">
+      <c r="E56" s="3">
         <v>0.237551124563013</v>
       </c>
-      <c r="F56" s="6">
+      <c r="F56" s="3">
         <v>0.25950504096246002</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="4"/>
-      <c r="B57" s="3" t="s">
+      <c r="A57" s="5"/>
+      <c r="B57" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C57" s="6">
+      <c r="C57" s="3">
         <v>0.61567067491082195</v>
       </c>
-      <c r="D57" s="6">
+      <c r="D57" s="3">
         <v>0.762123970523639</v>
       </c>
-      <c r="E57" s="6">
+      <c r="E57" s="3">
         <v>0.70094494047084999</v>
       </c>
-      <c r="F57" s="6">
+      <c r="F57" s="3">
         <v>0.83500376067397297</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="4"/>
-      <c r="B58" s="3" t="s">
+      <c r="A58" s="5"/>
+      <c r="B58" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C58" s="6">
+      <c r="C58" s="3">
         <v>0.34550919126602497</v>
       </c>
-      <c r="D58" s="6">
+      <c r="D58" s="3">
         <v>0.51357388490364198</v>
       </c>
-      <c r="E58" s="6">
+      <c r="E58" s="3">
         <v>0.66645865130858095</v>
       </c>
-      <c r="F58" s="6">
+      <c r="F58" s="3">
         <v>0.41774395361024702</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="4"/>
-      <c r="B59" s="3" t="s">
+      <c r="A59" s="5"/>
+      <c r="B59" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C59" s="6">
+      <c r="C59" s="3">
         <v>0.51342913480778896</v>
       </c>
-      <c r="D59" s="6">
+      <c r="D59" s="3">
         <v>0.67849775453542605</v>
       </c>
-      <c r="E59" s="6">
+      <c r="E59" s="3">
         <v>0.665759412399335</v>
       </c>
-      <c r="F59" s="6">
+      <c r="F59" s="3">
         <v>0.69173306489432895</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="4"/>
-      <c r="B60" s="3" t="s">
+      <c r="A60" s="5"/>
+      <c r="B60" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C60" s="6">
+      <c r="C60" s="3">
         <v>0.20385106298103101</v>
       </c>
-      <c r="D60" s="6">
+      <c r="D60" s="3">
         <v>0.33866492168266399</v>
       </c>
-      <c r="E60" s="6">
+      <c r="E60" s="3">
         <v>0.318503688585002</v>
       </c>
-      <c r="F60" s="6">
+      <c r="F60" s="3">
         <v>0.361551045673288</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="4"/>
-      <c r="B61" s="3" t="s">
+      <c r="A61" s="5"/>
+      <c r="B61" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C61" s="6">
+      <c r="C61" s="3">
         <v>0.479617171604384</v>
       </c>
-      <c r="D61" s="6">
+      <c r="D61" s="3">
         <v>0.62640641628480997</v>
       </c>
-      <c r="E61" s="6">
+      <c r="E61" s="3">
         <v>0.62044992181797898</v>
       </c>
-      <c r="F61" s="6">
+      <c r="F61" s="3">
         <v>0.64361895944876601</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C62" s="6">
+      <c r="C62" s="3">
         <v>0.38076881240172</v>
       </c>
-      <c r="D62" s="6">
+      <c r="D62" s="3">
         <v>0.55153159454609602</v>
       </c>
-      <c r="E62" s="6">
+      <c r="E62" s="3">
         <v>0.571860322646494</v>
       </c>
-      <c r="F62" s="6">
+      <c r="F62" s="3">
         <v>0.53259855988397697</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="4"/>
-      <c r="B63" s="3" t="s">
+      <c r="A63" s="5"/>
+      <c r="B63" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C63" s="6">
+      <c r="C63" s="3">
         <v>0.28826615048698101</v>
       </c>
-      <c r="D63" s="6">
+      <c r="D63" s="3">
         <v>0.44752577000957799</v>
       </c>
-      <c r="E63" s="6">
+      <c r="E63" s="3">
         <v>0.53763300666798597</v>
       </c>
-      <c r="F63" s="6">
+      <c r="F63" s="3">
         <v>0.38328692138119302</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="4"/>
-      <c r="B64" s="3" t="s">
+      <c r="A64" s="5"/>
+      <c r="B64" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C64" s="6">
+      <c r="C64" s="3">
         <v>0.61639626390128099</v>
       </c>
-      <c r="D64" s="6">
+      <c r="D64" s="3">
         <v>0.76267964442526903</v>
       </c>
-      <c r="E64" s="6">
+      <c r="E64" s="3">
         <v>0.697786299468383</v>
       </c>
-      <c r="F64" s="6">
+      <c r="F64" s="3">
         <v>0.840880599111959</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="4"/>
-      <c r="B65" s="3" t="s">
+      <c r="A65" s="5"/>
+      <c r="B65" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C65" s="6">
+      <c r="C65" s="3">
         <v>0.44477084330292799</v>
       </c>
-      <c r="D65" s="6">
+      <c r="D65" s="3">
         <v>0.61569742407886097</v>
       </c>
-      <c r="E65" s="6">
+      <c r="E65" s="3">
         <v>0.60736252568486104</v>
       </c>
-      <c r="F65" s="6">
+      <c r="F65" s="3">
         <v>0.62426426680421199</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="4"/>
-      <c r="B66" s="3" t="s">
+      <c r="A66" s="5"/>
+      <c r="B66" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C66" s="6">
+      <c r="C66" s="3">
         <v>0.73987648082972901</v>
       </c>
-      <c r="D66" s="6">
+      <c r="D66" s="3">
         <v>0.85049311141546002</v>
       </c>
-      <c r="E66" s="6">
+      <c r="E66" s="3">
         <v>0.79204936302685502</v>
       </c>
-      <c r="F66" s="6">
+      <c r="F66" s="3">
         <v>0.91824887066535898</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="4"/>
-      <c r="B67" s="3" t="s">
+      <c r="A67" s="5"/>
+      <c r="B67" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C67" s="6">
+      <c r="C67" s="3">
         <v>0.57354836174909296</v>
       </c>
-      <c r="D67" s="6">
+      <c r="D67" s="3">
         <v>0.728987269398647</v>
       </c>
-      <c r="E67" s="6">
+      <c r="E67" s="3">
         <v>0.768346666419776</v>
       </c>
-      <c r="F67" s="6">
+      <c r="F67" s="3">
         <v>0.69346382756959102</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="4"/>
-      <c r="B68" s="3" t="s">
+      <c r="A68" s="5"/>
+      <c r="B68" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C68" s="6">
+      <c r="C68" s="3">
         <v>0.52005702057784897</v>
       </c>
-      <c r="D68" s="6">
+      <c r="D68" s="3">
         <v>0.68425988438269203</v>
       </c>
-      <c r="E68" s="6">
+      <c r="E68" s="3">
         <v>0.67801940566847796</v>
       </c>
-      <c r="F68" s="6">
+      <c r="F68" s="3">
         <v>0.69061630473489899</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="4"/>
-      <c r="B69" s="3" t="s">
+      <c r="A69" s="5"/>
+      <c r="B69" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C69" s="6">
+      <c r="C69" s="3">
         <v>0.60390185995395795</v>
       </c>
-      <c r="D69" s="6">
+      <c r="D69" s="3">
         <v>0.75304091233025106</v>
       </c>
-      <c r="E69" s="6">
+      <c r="E69" s="3">
         <v>0.71302868719437595</v>
       </c>
-      <c r="F69" s="6">
+      <c r="F69" s="3">
         <v>0.79781075708042903</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="4"/>
-      <c r="B70" s="3" t="s">
+      <c r="A70" s="5"/>
+      <c r="B70" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C70" s="6">
+      <c r="C70" s="3">
         <v>0.80692212975389999</v>
       </c>
-      <c r="D70" s="6">
+      <c r="D70" s="3">
         <v>0.89314543938183</v>
       </c>
-      <c r="E70" s="6">
+      <c r="E70" s="3">
         <v>0.814192497551676</v>
       </c>
-      <c r="F70" s="6">
+      <c r="F70" s="3">
         <v>0.98905494176440201</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="4"/>
-      <c r="B71" s="3" t="s">
+      <c r="A71" s="5"/>
+      <c r="B71" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C71" s="6">
+      <c r="C71" s="3">
         <v>0.125209470557927</v>
       </c>
-      <c r="D71" s="6">
+      <c r="D71" s="3">
         <v>0.22255317580262299</v>
       </c>
-      <c r="E71" s="6">
+      <c r="E71" s="3">
         <v>0.26171546484687502</v>
       </c>
-      <c r="F71" s="6">
+      <c r="F71" s="3">
         <v>0.19358562441067201</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="4"/>
-      <c r="B72" s="3" t="s">
+      <c r="A72" s="5"/>
+      <c r="B72" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C72" s="6">
+      <c r="C72" s="3">
         <v>0.64623705654484698</v>
       </c>
-      <c r="D72" s="6">
+      <c r="D72" s="3">
         <v>0.78510813977323701</v>
       </c>
-      <c r="E72" s="6">
+      <c r="E72" s="3">
         <v>0.72096065570835099</v>
       </c>
-      <c r="F72" s="6">
+      <c r="F72" s="3">
         <v>0.86178551784603696</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="4"/>
-      <c r="B73" s="3" t="s">
+      <c r="A73" s="5"/>
+      <c r="B73" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C73" s="6">
+      <c r="C73" s="3">
         <v>0.49910559361749302</v>
       </c>
-      <c r="D73" s="6">
+      <c r="D73" s="3">
         <v>0.66587116443625705</v>
       </c>
-      <c r="E73" s="6">
+      <c r="E73" s="3">
         <v>0.64868126004787796</v>
       </c>
-      <c r="F73" s="6">
+      <c r="F73" s="3">
         <v>0.68399692585647098</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="4"/>
-      <c r="B74" s="3" t="s">
+      <c r="A74" s="5"/>
+      <c r="B74" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C74" s="6">
+      <c r="C74" s="3">
         <v>0.45535743056222899</v>
       </c>
-      <c r="D74" s="6">
+      <c r="D74" s="3">
         <v>0.62576714283351997</v>
       </c>
-      <c r="E74" s="6">
+      <c r="E74" s="3">
         <v>0.62332153336478902</v>
       </c>
-      <c r="F74" s="6">
+      <c r="F74" s="3">
         <v>0.62823201864981204</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="4"/>
-      <c r="B75" s="3" t="s">
+      <c r="A75" s="5"/>
+      <c r="B75" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C75" s="6">
+      <c r="C75" s="3">
         <v>0.340388215476783</v>
       </c>
-      <c r="D75" s="6">
+      <c r="D75" s="3">
         <v>0.50789496885527996</v>
       </c>
-      <c r="E75" s="6">
+      <c r="E75" s="3">
         <v>0.52257464405827403</v>
       </c>
-      <c r="F75" s="6">
+      <c r="F75" s="3">
         <v>0.49401749423515201</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="4"/>
-      <c r="B76" s="3" t="s">
+      <c r="A76" s="5"/>
+      <c r="B76" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C76" s="6">
+      <c r="C76" s="3">
         <v>0.50291469212262296</v>
       </c>
-      <c r="D76" s="6">
+      <c r="D76" s="3">
         <v>0.64961111726211496</v>
       </c>
-      <c r="E76" s="6">
+      <c r="E76" s="3">
         <v>0.63982373802536097</v>
       </c>
-      <c r="F76" s="6">
+      <c r="F76" s="3">
         <v>0.66656018785672599</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="4" t="s">
+      <c r="A77" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B77" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C77" s="6">
+      <c r="C77" s="3">
         <v>0.36842938203614201</v>
       </c>
-      <c r="D77" s="6">
+      <c r="D77" s="3">
         <v>0.53847043460575394</v>
       </c>
-      <c r="E77" s="6">
+      <c r="E77" s="3">
         <v>0.52011888808864704</v>
       </c>
-      <c r="F77" s="6">
+      <c r="F77" s="3">
         <v>0.55816435330080205</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="4"/>
-      <c r="B78" s="3" t="s">
+      <c r="A78" s="5"/>
+      <c r="B78" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C78" s="6">
+      <c r="C78" s="3">
         <v>0.41650001275612503</v>
       </c>
-      <c r="D78" s="6">
+      <c r="D78" s="3">
         <v>0.58806919732493101</v>
       </c>
-      <c r="E78" s="6">
+      <c r="E78" s="3">
         <v>0.60624282057788004</v>
       </c>
-      <c r="F78" s="6">
+      <c r="F78" s="3">
         <v>0.57095345967189703</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="4"/>
-      <c r="B79" s="3" t="s">
+      <c r="A79" s="5"/>
+      <c r="B79" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C79" s="6">
+      <c r="C79" s="3">
         <v>0.62758944620254897</v>
       </c>
-      <c r="D79" s="6">
+      <c r="D79" s="3">
         <v>0.77118888632120997</v>
       </c>
-      <c r="E79" s="6">
+      <c r="E79" s="3">
         <v>0.74907296391012101</v>
       </c>
-      <c r="F79" s="6">
+      <c r="F79" s="3">
         <v>0.79465045640105803</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="4"/>
-      <c r="B80" s="3" t="s">
+      <c r="A80" s="5"/>
+      <c r="B80" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C80" s="6">
+      <c r="C80" s="3">
         <v>0.39710154039075701</v>
       </c>
-      <c r="D80" s="6">
+      <c r="D80" s="3">
         <v>0.56846482365153095</v>
       </c>
-      <c r="E80" s="6">
+      <c r="E80" s="3">
         <v>0.573922423518333</v>
       </c>
-      <c r="F80" s="6">
+      <c r="F80" s="3">
         <v>0.56311004195277903</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="4"/>
-      <c r="B81" s="3" t="s">
+      <c r="A81" s="5"/>
+      <c r="B81" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C81" s="6">
+      <c r="C81" s="3">
         <v>0.79916472198490796</v>
       </c>
-      <c r="D81" s="6">
+      <c r="D81" s="3">
         <v>0.88837304580231902</v>
       </c>
-      <c r="E81" s="6">
+      <c r="E81" s="3">
         <v>0.830815602833337</v>
       </c>
-      <c r="F81" s="6">
+      <c r="F81" s="3">
         <v>0.95449906111383298</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="4"/>
-      <c r="B82" s="3" t="s">
+      <c r="A82" s="5"/>
+      <c r="B82" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C82" s="6">
+      <c r="C82" s="3">
         <v>0.48091135571277299</v>
       </c>
-      <c r="D82" s="6">
+      <c r="D82" s="3">
         <v>0.64948027288413501</v>
       </c>
-      <c r="E82" s="6">
+      <c r="E82" s="3">
         <v>0.68780658773166903</v>
       </c>
-      <c r="F82" s="6">
+      <c r="F82" s="3">
         <v>0.61519979153228899</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="4"/>
-      <c r="B83" s="3" t="s">
+      <c r="A83" s="5"/>
+      <c r="B83" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C83" s="6">
+      <c r="C83" s="3">
         <v>0.58233840877416798</v>
       </c>
-      <c r="D83" s="6">
+      <c r="D83" s="3">
         <v>0.73604787135933003</v>
       </c>
-      <c r="E83" s="6">
+      <c r="E83" s="3">
         <v>0.77185433857515995</v>
       </c>
-      <c r="F83" s="6">
+      <c r="F83" s="3">
         <v>0.70341625944236696</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="4"/>
-      <c r="B84" s="3" t="s">
+      <c r="A84" s="5"/>
+      <c r="B84" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C84" s="6">
+      <c r="C84" s="3">
         <v>0.643288723463459</v>
       </c>
-      <c r="D84" s="6">
+      <c r="D84" s="3">
         <v>0.78292842186324796</v>
       </c>
-      <c r="E84" s="6">
+      <c r="E84" s="3">
         <v>0.71087527006782103</v>
       </c>
-      <c r="F84" s="6">
+      <c r="F84" s="3">
         <v>0.87123541501810997</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="4"/>
-      <c r="B85" s="3" t="s">
+      <c r="A85" s="5"/>
+      <c r="B85" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C85" s="6">
+      <c r="C85" s="3">
         <v>0.76870074469013905</v>
       </c>
-      <c r="D85" s="6">
+      <c r="D85" s="3">
         <v>0.86922646128563597</v>
       </c>
-      <c r="E85" s="6">
+      <c r="E85" s="3">
         <v>0.78072644700141203</v>
       </c>
-      <c r="F85" s="6">
+      <c r="F85" s="3">
         <v>0.98035563897086497</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="4"/>
-      <c r="B86" s="3" t="s">
+      <c r="A86" s="5"/>
+      <c r="B86" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C86" s="6">
+      <c r="C86" s="3">
         <v>0.112840451297495</v>
       </c>
-      <c r="D86" s="6">
+      <c r="D86" s="3">
         <v>0.20279717755753901</v>
       </c>
-      <c r="E86" s="6">
+      <c r="E86" s="3">
         <v>0.26039243310353899</v>
       </c>
-      <c r="F86" s="6">
+      <c r="F86" s="3">
         <v>0.16606570749632499</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="4"/>
-      <c r="B87" s="3" t="s">
+      <c r="A87" s="5"/>
+      <c r="B87" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C87" s="6">
+      <c r="C87" s="3">
         <v>0.58171557760027304</v>
       </c>
-      <c r="D87" s="6">
+      <c r="D87" s="3">
         <v>0.73555016570404297</v>
       </c>
-      <c r="E87" s="6">
+      <c r="E87" s="3">
         <v>0.67735270113260004</v>
       </c>
-      <c r="F87" s="6">
+      <c r="F87" s="3">
         <v>0.80468816564541501</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="4"/>
-      <c r="B88" s="3" t="s">
+      <c r="A88" s="5"/>
+      <c r="B88" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C88" s="6">
+      <c r="C88" s="3">
         <v>0.52765700771868296</v>
       </c>
-      <c r="D88" s="6">
+      <c r="D88" s="3">
         <v>0.69080559975521705</v>
       </c>
-      <c r="E88" s="6">
+      <c r="E88" s="3">
         <v>0.77719124425948405</v>
       </c>
-      <c r="F88" s="6">
+      <c r="F88" s="3">
         <v>0.62170267708730298</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="4"/>
-      <c r="B89" s="3" t="s">
+      <c r="A89" s="5"/>
+      <c r="B89" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C89" s="6">
+      <c r="C89" s="3">
         <v>0.54352816787811498</v>
       </c>
-      <c r="D89" s="6">
+      <c r="D89" s="3">
         <v>0.70426724848863897</v>
       </c>
-      <c r="E89" s="6">
+      <c r="E89" s="3">
         <v>0.72165937758519005</v>
       </c>
-      <c r="F89" s="6">
+      <c r="F89" s="3">
         <v>0.68769369875164099</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="4"/>
-      <c r="B90" s="3" t="s">
+      <c r="A90" s="5"/>
+      <c r="B90" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C90" s="6">
+      <c r="C90" s="3">
         <v>0</v>
       </c>
-      <c r="D90" s="6">
+      <c r="D90" s="3">
         <v>0</v>
       </c>
-      <c r="E90" s="6">
+      <c r="E90" s="3">
         <v>0</v>
       </c>
-      <c r="F90" s="6">
+      <c r="F90" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="4"/>
-      <c r="B91" s="3" t="s">
+      <c r="A91" s="5"/>
+      <c r="B91" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C91" s="6">
+      <c r="C91" s="3">
         <v>0.48926896717897</v>
       </c>
-      <c r="D91" s="6">
+      <c r="D91" s="3">
         <v>0.62326211475739501</v>
       </c>
-      <c r="E91" s="6">
+      <c r="E91" s="3">
         <v>0.61914507845608502</v>
       </c>
-      <c r="F91" s="6">
+      <c r="F91" s="3">
         <v>0.63512390902747795</v>
       </c>
     </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" s="3">
+        <v>0.23212999981496299</v>
+      </c>
+      <c r="D92" s="3">
+        <v>0.37679465616424102</v>
+      </c>
+      <c r="E92" s="3">
+        <v>0.34554295221533698</v>
+      </c>
+      <c r="F92" s="3">
+        <v>0.41426141703944602</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="7"/>
+      <c r="B93" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C93" s="3">
+        <v>0.41678663948761402</v>
+      </c>
+      <c r="D93" s="3">
+        <v>0.58835484168363805</v>
+      </c>
+      <c r="E93" s="3">
+        <v>0.62934624802411399</v>
+      </c>
+      <c r="F93" s="3">
+        <v>0.55237671598711402</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="7"/>
+      <c r="B94" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C94" s="3">
+        <v>0.59179303975610598</v>
+      </c>
+      <c r="D94" s="3">
+        <v>0.74355525495548103</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0.74927874823930196</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0.73791853856732004</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="7"/>
+      <c r="B95" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C95" s="3">
+        <v>0.42834265329105897</v>
+      </c>
+      <c r="D95" s="3">
+        <v>0.59977576431553004</v>
+      </c>
+      <c r="E95" s="3">
+        <v>0.66192061219435605</v>
+      </c>
+      <c r="F95" s="3">
+        <v>0.54829841083007103</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" s="7"/>
+      <c r="B96" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C96" s="3">
+        <v>0.82415379371304898</v>
+      </c>
+      <c r="D96" s="3">
+        <v>0.903601216688524</v>
+      </c>
+      <c r="E96" s="3">
+        <v>0.89598142201867903</v>
+      </c>
+      <c r="F96" s="3">
+        <v>0.91135172675403797</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" s="7"/>
+      <c r="B97" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C97" s="3">
+        <v>0.39938855199543399</v>
+      </c>
+      <c r="D97" s="3">
+        <v>0.57080437227520897</v>
+      </c>
+      <c r="E97" s="3">
+        <v>0.56062584058492904</v>
+      </c>
+      <c r="F97" s="3">
+        <v>0.58135933420937602</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" s="7"/>
+      <c r="B98" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C98" s="3">
+        <v>0.59531916042898403</v>
+      </c>
+      <c r="D98" s="3">
+        <v>0.74633236432627303</v>
+      </c>
+      <c r="E98" s="3">
+        <v>0.73449562150207204</v>
+      </c>
+      <c r="F98" s="3">
+        <v>0.75855686542707701</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" s="7"/>
+      <c r="B99" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C99" s="3">
+        <v>0.59335789775623504</v>
+      </c>
+      <c r="D99" s="3">
+        <v>0.74478922606377496</v>
+      </c>
+      <c r="E99" s="3">
+        <v>0.68707561692603303</v>
+      </c>
+      <c r="F99" s="3">
+        <v>0.81308771524981804</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="7"/>
+      <c r="B100" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C100" s="3">
+        <v>0.71493952967314001</v>
+      </c>
+      <c r="D100" s="3">
+        <v>0.83377812138881002</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0.73080672281074999</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0.97052623980341901</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" s="7"/>
+      <c r="B101" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C101" s="3">
+        <v>0</v>
+      </c>
+      <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="7"/>
+      <c r="B102" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C102" s="3">
+        <v>0.58239544611637195</v>
+      </c>
+      <c r="D102" s="3">
+        <v>0.73609343043261199</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0.72020686870649997</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0.75269666280123804</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" s="7"/>
+      <c r="B103" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C103" s="3">
+        <v>0.37333167941260698</v>
+      </c>
+      <c r="D103" s="3">
+        <v>0.54368756653496297</v>
+      </c>
+      <c r="E103" s="3">
+        <v>0.48365896127088098</v>
+      </c>
+      <c r="F103" s="3">
+        <v>0.62072833062500998</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" s="7"/>
+      <c r="B104" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C104" s="3">
+        <v>0.57111780395346901</v>
+      </c>
+      <c r="D104" s="3">
+        <v>0.72702098151563299</v>
+      </c>
+      <c r="E104" s="3">
+        <v>0.731924323230431</v>
+      </c>
+      <c r="F104" s="3">
+        <v>0.72218289999969398</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="7"/>
+      <c r="B105" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C105" s="3">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3">
+        <v>0</v>
+      </c>
+      <c r="E105" s="3">
+        <v>0</v>
+      </c>
+      <c r="F105" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="7"/>
+      <c r="B106" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C106" s="3">
+        <v>0.45164687109993101</v>
+      </c>
+      <c r="D106" s="3">
+        <v>0.57961341402462097</v>
+      </c>
+      <c r="E106" s="3">
+        <v>0.56649028126595602</v>
+      </c>
+      <c r="F106" s="3">
+        <v>0.59881034694954405</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" s="3">
+        <v>0.18488700826885199</v>
+      </c>
+      <c r="D107" s="3">
+        <v>0.31207534048158098</v>
+      </c>
+      <c r="E107" s="3">
+        <v>0.28126613441878201</v>
+      </c>
+      <c r="F107" s="3">
+        <v>0.35046435026112399</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="7"/>
+      <c r="B108" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C108" s="3">
+        <v>0.33951918690615102</v>
+      </c>
+      <c r="D108" s="3">
+        <v>0.50692694845279296</v>
+      </c>
+      <c r="E108" s="3">
+        <v>0.53292065053932103</v>
+      </c>
+      <c r="F108" s="3">
+        <v>0.48335104989909</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="7"/>
+      <c r="B109" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C109" s="3">
+        <v>0.62811790033716997</v>
+      </c>
+      <c r="D109" s="3">
+        <v>0.77158773355061305</v>
+      </c>
+      <c r="E109" s="3">
+        <v>0.78847489035623997</v>
+      </c>
+      <c r="F109" s="3">
+        <v>0.75540877019904795</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="7"/>
+      <c r="B110" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C110" s="3">
+        <v>0.33117204268325801</v>
+      </c>
+      <c r="D110" s="3">
+        <v>0.497564600313737</v>
+      </c>
+      <c r="E110" s="3">
+        <v>0.50019842490670396</v>
+      </c>
+      <c r="F110" s="3">
+        <v>0.494958367554795</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="7"/>
+      <c r="B111" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C111" s="3">
+        <v>0.72053363609314702</v>
+      </c>
+      <c r="D111" s="3">
+        <v>0.83756995036642001</v>
+      </c>
+      <c r="E111" s="3">
+        <v>0.86082272227294498</v>
+      </c>
+      <c r="F111" s="3">
+        <v>0.81554035771301303</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="7"/>
+      <c r="B112" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C112" s="3">
+        <v>0.453489753102923</v>
+      </c>
+      <c r="D112" s="3">
+        <v>0.62400130738425796</v>
+      </c>
+      <c r="E112" s="3">
+        <v>0.60878403047076601</v>
+      </c>
+      <c r="F112" s="3">
+        <v>0.63999883526453805</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="7"/>
+      <c r="B113" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C113" s="3">
+        <v>0.54451773616851895</v>
+      </c>
+      <c r="D113" s="3">
+        <v>0.70509742091962302</v>
+      </c>
+      <c r="E113" s="3">
+        <v>0.68663490114653303</v>
+      </c>
+      <c r="F113" s="3">
+        <v>0.72458023020443596</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="7"/>
+      <c r="B114" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C114" s="3">
+        <v>0.48458091693611399</v>
+      </c>
+      <c r="D114" s="3">
+        <v>0.65281846399614896</v>
+      </c>
+      <c r="E114" s="3">
+        <v>0.54703677510505899</v>
+      </c>
+      <c r="F114" s="3">
+        <v>0.80931805305087101</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" s="7"/>
+      <c r="B115" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C115" s="3">
+        <v>0.72793223919907402</v>
+      </c>
+      <c r="D115" s="3">
+        <v>0.84254720490252899</v>
+      </c>
+      <c r="E115" s="3">
+        <v>0.76174113400779098</v>
+      </c>
+      <c r="F115" s="3">
+        <v>0.942531671644671</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="7"/>
+      <c r="B116" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C116" s="3">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3">
+        <v>0</v>
+      </c>
+      <c r="E116" s="3">
+        <v>0</v>
+      </c>
+      <c r="F116" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="7"/>
+      <c r="B117" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C117" s="3">
+        <v>0.54382084481558302</v>
+      </c>
+      <c r="D117" s="3">
+        <v>0.70451289298473596</v>
+      </c>
+      <c r="E117" s="3">
+        <v>0.66050618601505295</v>
+      </c>
+      <c r="F117" s="3">
+        <v>0.75480213651490202</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="7"/>
+      <c r="B118" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C118" s="3">
+        <v>0.24056409764176601</v>
+      </c>
+      <c r="D118" s="3">
+        <v>0.38783017838266198</v>
+      </c>
+      <c r="E118" s="3">
+        <v>0.43594624902365098</v>
+      </c>
+      <c r="F118" s="3">
+        <v>0.34927963746738999</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" s="7"/>
+      <c r="B119" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C119" s="3">
+        <v>0.54314638087558198</v>
+      </c>
+      <c r="D119" s="3">
+        <v>0.70394667363623797</v>
+      </c>
+      <c r="E119" s="3">
+        <v>0.69312058930762699</v>
+      </c>
+      <c r="F119" s="3">
+        <v>0.71511631665111197</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" s="7"/>
+      <c r="B120" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C120" s="3">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3">
+        <v>0</v>
+      </c>
+      <c r="E120" s="3">
+        <v>0</v>
+      </c>
+      <c r="F120" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="7"/>
+      <c r="B121" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C121" s="3">
+        <v>0.41016298164486698</v>
+      </c>
+      <c r="D121" s="3">
+        <v>0.539034193955096</v>
+      </c>
+      <c r="E121" s="3">
+        <v>0.525532334826462</v>
+      </c>
+      <c r="F121" s="3">
+        <v>0.559667841173214</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" s="3">
+        <v>0.18924188081997401</v>
+      </c>
+      <c r="D122" s="3">
+        <v>0.31825633434553002</v>
+      </c>
+      <c r="E122" s="3">
+        <v>0.35015705212468401</v>
+      </c>
+      <c r="F122" s="3">
+        <v>0.29168285173858199</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" s="7"/>
+      <c r="B123" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C123" s="3">
+        <v>0.28229891542195201</v>
+      </c>
+      <c r="D123" s="3">
+        <v>0.44030126209544401</v>
+      </c>
+      <c r="E123" s="3">
+        <v>0.52384551625155296</v>
+      </c>
+      <c r="F123" s="3">
+        <v>0.37973942464291299</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" s="7"/>
+      <c r="B124" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C124" s="3">
+        <v>0.59372566336698696</v>
+      </c>
+      <c r="D124" s="3">
+        <v>0.74507887651460802</v>
+      </c>
+      <c r="E124" s="3">
+        <v>0.78629464501944801</v>
+      </c>
+      <c r="F124" s="3">
+        <v>0.707968771323918</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" s="7"/>
+      <c r="B125" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C125" s="3">
+        <v>0.384789647231846</v>
+      </c>
+      <c r="D125" s="3">
+        <v>0.55573732516130403</v>
+      </c>
+      <c r="E125" s="3">
+        <v>0.53501977977274096</v>
+      </c>
+      <c r="F125" s="3">
+        <v>0.57812399293833705</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" s="7"/>
+      <c r="B126" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C126" s="3">
+        <v>0.730430179134122</v>
+      </c>
+      <c r="D126" s="3">
+        <v>0.84421803080158597</v>
+      </c>
+      <c r="E126" s="3">
+        <v>0.79396506069500405</v>
+      </c>
+      <c r="F126" s="3">
+        <v>0.90126223379650905</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" s="7"/>
+      <c r="B127" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C127" s="3">
+        <v>0.461980253742103</v>
+      </c>
+      <c r="D127" s="3">
+        <v>0.63199246714805202</v>
+      </c>
+      <c r="E127" s="3">
+        <v>0.63816890667559201</v>
+      </c>
+      <c r="F127" s="3">
+        <v>0.62593443743121102</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" s="7"/>
+      <c r="B128" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C128" s="3">
+        <v>0.52328604394685996</v>
+      </c>
+      <c r="D128" s="3">
+        <v>0.68704895712300595</v>
+      </c>
+      <c r="E128" s="3">
+        <v>0.70949521147893402</v>
+      </c>
+      <c r="F128" s="3">
+        <v>0.66597940939766598</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" s="7"/>
+      <c r="B129" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C129" s="3">
+        <v>0.57842061768262998</v>
+      </c>
+      <c r="D129" s="3">
+        <v>0.73291062116489902</v>
+      </c>
+      <c r="E129" s="3">
+        <v>0.66212542960574905</v>
+      </c>
+      <c r="F129" s="3">
+        <v>0.82064221015038397</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" s="7"/>
+      <c r="B130" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C130" s="3">
+        <v>0.75702737771891104</v>
+      </c>
+      <c r="D130" s="3">
+        <v>0.86171380972074996</v>
+      </c>
+      <c r="E130" s="3">
+        <v>0.788325578584676</v>
+      </c>
+      <c r="F130" s="3">
+        <v>0.95016862672881297</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" s="7"/>
+      <c r="B131" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C131" s="3">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3">
+        <v>0</v>
+      </c>
+      <c r="E131" s="3">
+        <v>0</v>
+      </c>
+      <c r="F131" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132" s="7"/>
+      <c r="B132" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C132" s="3">
+        <v>0.54325802662993505</v>
+      </c>
+      <c r="D132" s="3">
+        <v>0.70404043556639195</v>
+      </c>
+      <c r="E132" s="3">
+        <v>0.64285267718772698</v>
+      </c>
+      <c r="F132" s="3">
+        <v>0.77810138486420499</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" s="7"/>
+      <c r="B133" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C133" s="3">
+        <v>0.42001349166406099</v>
+      </c>
+      <c r="D133" s="3">
+        <v>0.59156267757972103</v>
+      </c>
+      <c r="E133" s="3">
+        <v>0.58241662301375896</v>
+      </c>
+      <c r="F133" s="3">
+        <v>0.60100056751528796</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" s="7"/>
+      <c r="B134" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C134" s="3">
+        <v>0.44385121076425799</v>
+      </c>
+      <c r="D134" s="3">
+        <v>0.61481571986814199</v>
+      </c>
+      <c r="E134" s="3">
+        <v>0.518849485703195</v>
+      </c>
+      <c r="F134" s="3">
+        <v>0.754337796295935</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="7"/>
+      <c r="B135" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C135" s="3">
+        <v>0</v>
+      </c>
+      <c r="D135" s="3">
+        <v>0</v>
+      </c>
+      <c r="E135" s="3">
+        <v>0</v>
+      </c>
+      <c r="F135" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" s="7"/>
+      <c r="B136" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C136" s="3">
+        <v>0.42202309343740302</v>
+      </c>
+      <c r="D136" s="3">
+        <v>0.55197689407781703</v>
+      </c>
+      <c r="E136" s="3">
+        <v>0.53796542615093301</v>
+      </c>
+      <c r="F136" s="3">
+        <v>0.57535297905883998</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" s="3">
+        <v>0.249691986412404</v>
+      </c>
+      <c r="D137" s="3">
+        <v>0.39960564543462601</v>
+      </c>
+      <c r="E137" s="3">
+        <v>0.38105934475264303</v>
+      </c>
+      <c r="F137" s="3">
+        <v>0.42004961724656698</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" s="7"/>
+      <c r="B138" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C138" s="3">
+        <v>0.41375645454691801</v>
+      </c>
+      <c r="D138" s="3">
+        <v>0.58532918200471695</v>
+      </c>
+      <c r="E138" s="3">
+        <v>0.58156878767346198</v>
+      </c>
+      <c r="F138" s="3">
+        <v>0.58913852185385895</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" s="7"/>
+      <c r="B139" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C139" s="3">
+        <v>0.63272118071966699</v>
+      </c>
+      <c r="D139" s="3">
+        <v>0.77505110877630401</v>
+      </c>
+      <c r="E139" s="3">
+        <v>0.75607427390951898</v>
+      </c>
+      <c r="F139" s="3">
+        <v>0.79500507432482403</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140" s="7"/>
+      <c r="B140" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C140" s="3">
+        <v>0.44724098161547199</v>
+      </c>
+      <c r="D140" s="3">
+        <v>0.61806013966829798</v>
+      </c>
+      <c r="E140" s="3">
+        <v>0.653186011705429</v>
+      </c>
+      <c r="F140" s="3">
+        <v>0.58651934850949905</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" s="7"/>
+      <c r="B141" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C141" s="3">
+        <v>0.81206556731301904</v>
+      </c>
+      <c r="D141" s="3">
+        <v>0.89628717852320605</v>
+      </c>
+      <c r="E141" s="3">
+        <v>0.85385154531337804</v>
+      </c>
+      <c r="F141" s="3">
+        <v>0.94316143054505197</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142" s="7"/>
+      <c r="B142" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C142" s="3">
+        <v>0.407663064496116</v>
+      </c>
+      <c r="D142" s="3">
+        <v>0.57920545729746997</v>
+      </c>
+      <c r="E142" s="3">
+        <v>0.55949556601975603</v>
+      </c>
+      <c r="F142" s="3">
+        <v>0.60035473399185602</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="7"/>
+      <c r="B143" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C143" s="3">
+        <v>0.55184351948879395</v>
+      </c>
+      <c r="D143" s="3">
+        <v>0.71121026386807495</v>
+      </c>
+      <c r="E143" s="3">
+        <v>0.76979591401750103</v>
+      </c>
+      <c r="F143" s="3">
+        <v>0.66091132252989804</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" s="7"/>
+      <c r="B144" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C144" s="3">
+        <v>0.627048713017755</v>
+      </c>
+      <c r="D144" s="3">
+        <v>0.77078050337502402</v>
+      </c>
+      <c r="E144" s="3">
+        <v>0.70839262930610103</v>
+      </c>
+      <c r="F144" s="3">
+        <v>0.84521858852762499</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145" s="7"/>
+      <c r="B145" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C145" s="3">
+        <v>0.73321997275574502</v>
+      </c>
+      <c r="D145" s="3">
+        <v>0.84607837929533802</v>
+      </c>
+      <c r="E145" s="3">
+        <v>0.76989305013272102</v>
+      </c>
+      <c r="F145" s="3">
+        <v>0.93899756971993098</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146" s="7"/>
+      <c r="B146" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C146" s="3">
+        <v>0</v>
+      </c>
+      <c r="D146" s="3">
+        <v>0</v>
+      </c>
+      <c r="E146" s="3">
+        <v>0</v>
+      </c>
+      <c r="F146" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147" s="7"/>
+      <c r="B147" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C147" s="3">
+        <v>0.58589227461454196</v>
+      </c>
+      <c r="D147" s="3">
+        <v>0.73888029343852601</v>
+      </c>
+      <c r="E147" s="3">
+        <v>0.72736896096382397</v>
+      </c>
+      <c r="F147" s="3">
+        <v>0.75076184135848301</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148" s="7"/>
+      <c r="B148" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C148" s="3">
+        <v>0.44958773472684999</v>
+      </c>
+      <c r="D148" s="3">
+        <v>0.62029737691119102</v>
+      </c>
+      <c r="E148" s="3">
+        <v>0.60656757090403901</v>
+      </c>
+      <c r="F148" s="3">
+        <v>0.63466313286669696</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149" s="7"/>
+      <c r="B149" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C149" s="3">
+        <v>0.58428569146376896</v>
+      </c>
+      <c r="D149" s="3">
+        <v>0.73760142455611</v>
+      </c>
+      <c r="E149" s="3">
+        <v>0.76742340027538503</v>
+      </c>
+      <c r="F149" s="3">
+        <v>0.71001050658286102</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150" s="7"/>
+      <c r="B150" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C150" s="3">
+        <v>0</v>
+      </c>
+      <c r="D150" s="3">
+        <v>0</v>
+      </c>
+      <c r="E150" s="3">
+        <v>0</v>
+      </c>
+      <c r="F150" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151" s="7"/>
+      <c r="B151" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C151" s="3">
+        <v>0.46392979579793198</v>
+      </c>
+      <c r="D151" s="3">
+        <v>0.59131335379634897</v>
+      </c>
+      <c r="E151" s="3">
+        <v>0.58104836106955404</v>
+      </c>
+      <c r="F151" s="3">
+        <v>0.60534226343265396</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" s="3">
+        <v>0.20747655792023501</v>
+      </c>
+      <c r="D152" s="3">
+        <v>0.34365314433531402</v>
+      </c>
+      <c r="E152" s="3">
+        <v>0.32680247522691402</v>
+      </c>
+      <c r="F152" s="3">
+        <v>0.36233600182780201</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153" s="7"/>
+      <c r="B153" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C153" s="3">
+        <v>0.40468044978718098</v>
+      </c>
+      <c r="D153" s="3">
+        <v>0.57618862688448902</v>
+      </c>
+      <c r="E153" s="3">
+        <v>0.65803045028752005</v>
+      </c>
+      <c r="F153" s="3">
+        <v>0.51245285852936895</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A154" s="7"/>
+      <c r="B154" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C154" s="3">
+        <v>0.68029657546156497</v>
+      </c>
+      <c r="D154" s="3">
+        <v>0.80973393077908595</v>
+      </c>
+      <c r="E154" s="3">
+        <v>0.81171113248776405</v>
+      </c>
+      <c r="F154" s="3">
+        <v>0.80776633797452901</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155" s="7"/>
+      <c r="B155" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C155" s="3">
+        <v>0.32535970167280998</v>
+      </c>
+      <c r="D155" s="3">
+        <v>0.49097569703101102</v>
+      </c>
+      <c r="E155" s="3">
+        <v>0.45524664073767901</v>
+      </c>
+      <c r="F155" s="3">
+        <v>0.53279062677015598</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A156" s="7"/>
+      <c r="B156" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C156" s="3">
+        <v>0.74730693046876795</v>
+      </c>
+      <c r="D156" s="3">
+        <v>0.85538140716729205</v>
+      </c>
+      <c r="E156" s="3">
+        <v>0.83753562123492598</v>
+      </c>
+      <c r="F156" s="3">
+        <v>0.87400424818031197</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A157" s="7"/>
+      <c r="B157" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C157" s="3">
+        <v>0.458450081741759</v>
+      </c>
+      <c r="D157" s="3">
+        <v>0.62868121093901697</v>
+      </c>
+      <c r="E157" s="3">
+        <v>0.57055674481671703</v>
+      </c>
+      <c r="F157" s="3">
+        <v>0.69999162846393703</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A158" s="7"/>
+      <c r="B158" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C158" s="3">
+        <v>0.56625877150762804</v>
+      </c>
+      <c r="D158" s="3">
+        <v>0.72307179606415395</v>
+      </c>
+      <c r="E158" s="3">
+        <v>0.70573249205631094</v>
+      </c>
+      <c r="F158" s="3">
+        <v>0.74128458769126404</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A159" s="7"/>
+      <c r="B159" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C159" s="3">
+        <v>0.60586975023948897</v>
+      </c>
+      <c r="D159" s="3">
+        <v>0.75456898064009603</v>
+      </c>
+      <c r="E159" s="3">
+        <v>0.67105211159287803</v>
+      </c>
+      <c r="F159" s="3">
+        <v>0.86182933572986598</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A160" s="7"/>
+      <c r="B160" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C160" s="3">
+        <v>0.71693430702153604</v>
+      </c>
+      <c r="D160" s="3">
+        <v>0.83513306722287195</v>
+      </c>
+      <c r="E160" s="3">
+        <v>0.74301209577711502</v>
+      </c>
+      <c r="F160" s="3">
+        <v>0.95332990009250096</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A161" s="7"/>
+      <c r="B161" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C161" s="3">
+        <v>0</v>
+      </c>
+      <c r="D161" s="3">
+        <v>0</v>
+      </c>
+      <c r="E161" s="3">
+        <v>0</v>
+      </c>
+      <c r="F161" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A162" s="7"/>
+      <c r="B162" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C162" s="3">
+        <v>0.56429857284600504</v>
+      </c>
+      <c r="D162" s="3">
+        <v>0.72147169682492096</v>
+      </c>
+      <c r="E162" s="3">
+        <v>0.66971086563501203</v>
+      </c>
+      <c r="F162" s="3">
+        <v>0.78190372631930605</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A163" s="7"/>
+      <c r="B163" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C163" s="3">
+        <v>0.27756885975703999</v>
+      </c>
+      <c r="D163" s="3">
+        <v>0.434526652144334</v>
+      </c>
+      <c r="E163" s="3">
+        <v>0.54715073576387296</v>
+      </c>
+      <c r="F163" s="3">
+        <v>0.36035260886731901</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A164" s="7"/>
+      <c r="B164" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C164" s="3">
+        <v>0.58265345859768003</v>
+      </c>
+      <c r="D164" s="3">
+        <v>0.73629947912153004</v>
+      </c>
+      <c r="E164" s="3">
+        <v>0.67523595720458995</v>
+      </c>
+      <c r="F164" s="3">
+        <v>0.809505368538737</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A165" s="7"/>
+      <c r="B165" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C165" s="3">
+        <v>0</v>
+      </c>
+      <c r="D165" s="3">
+        <v>0</v>
+      </c>
+      <c r="E165" s="3">
+        <v>0</v>
+      </c>
+      <c r="F165" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A166" s="7"/>
+      <c r="B166" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C166" s="3">
+        <v>0.43836814407297803</v>
+      </c>
+      <c r="D166" s="3">
+        <v>0.56497754922529397</v>
+      </c>
+      <c r="E166" s="3">
+        <v>0.54798409448723595</v>
+      </c>
+      <c r="F166" s="3">
+        <v>0.59268194492750703</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A167" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" s="3">
+        <v>0.21260467106935799</v>
+      </c>
+      <c r="D167" s="3">
+        <v>0.35065784610885398</v>
+      </c>
+      <c r="E167" s="3">
+        <v>0.270442575783718</v>
+      </c>
+      <c r="F167" s="3">
+        <v>0.49852365248948499</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A168" s="7"/>
+      <c r="B168" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C168" s="3">
+        <v>0.29236646449771803</v>
+      </c>
+      <c r="D168" s="3">
+        <v>0.45245133254265801</v>
+      </c>
+      <c r="E168" s="3">
+        <v>0.53187459822876404</v>
+      </c>
+      <c r="F168" s="3">
+        <v>0.39366630397338798</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A169" s="7"/>
+      <c r="B169" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C169" s="3">
+        <v>0.64282506497476899</v>
+      </c>
+      <c r="D169" s="3">
+        <v>0.78258492481016695</v>
+      </c>
+      <c r="E169" s="3">
+        <v>0.72236459231845096</v>
+      </c>
+      <c r="F169" s="3">
+        <v>0.85375902875452503</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A170" s="7"/>
+      <c r="B170" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C170" s="3">
+        <v>0.42902692307614398</v>
+      </c>
+      <c r="D170" s="3">
+        <v>0.60044624233196997</v>
+      </c>
+      <c r="E170" s="3">
+        <v>0.55870696050590796</v>
+      </c>
+      <c r="F170" s="3">
+        <v>0.64892547220199104</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A171" s="7"/>
+      <c r="B171" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C171" s="3">
+        <v>0.765969006861277</v>
+      </c>
+      <c r="D171" s="3">
+        <v>0.86747729307284105</v>
+      </c>
+      <c r="E171" s="3">
+        <v>0.82722734811633702</v>
+      </c>
+      <c r="F171" s="3">
+        <v>0.91184440343331896</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A172" s="7"/>
+      <c r="B172" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C172" s="3">
+        <v>0.46496957222268398</v>
+      </c>
+      <c r="D172" s="3">
+        <v>0.63478393140578604</v>
+      </c>
+      <c r="E172" s="3">
+        <v>0.57741481459226296</v>
+      </c>
+      <c r="F172" s="3">
+        <v>0.7048104572817</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A173" s="7"/>
+      <c r="B173" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C173" s="3">
+        <v>0.51291004190923895</v>
+      </c>
+      <c r="D173" s="3">
+        <v>0.67804433535514697</v>
+      </c>
+      <c r="E173" s="3">
+        <v>0.627285931303313</v>
+      </c>
+      <c r="F173" s="3">
+        <v>0.73774044128626604</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A174" s="7"/>
+      <c r="B174" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C174" s="3">
+        <v>0.61426910397939805</v>
+      </c>
+      <c r="D174" s="3">
+        <v>0.76104919863130505</v>
+      </c>
+      <c r="E174" s="3">
+        <v>0.68250950935012999</v>
+      </c>
+      <c r="F174" s="3">
+        <v>0.86001534826665504</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A175" s="7"/>
+      <c r="B175" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C175" s="3">
+        <v>0.77860253332756102</v>
+      </c>
+      <c r="D175" s="3">
+        <v>0.87552167360392197</v>
+      </c>
+      <c r="E175" s="3">
+        <v>0.79967752240854595</v>
+      </c>
+      <c r="F175" s="3">
+        <v>0.96725991175147896</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A176" s="7"/>
+      <c r="B176" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C176" s="3">
+        <v>0</v>
+      </c>
+      <c r="D176" s="3">
+        <v>0</v>
+      </c>
+      <c r="E176" s="3">
+        <v>0</v>
+      </c>
+      <c r="F176" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A177" s="7"/>
+      <c r="B177" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C177" s="3">
+        <v>0.62329127340919699</v>
+      </c>
+      <c r="D177" s="3">
+        <v>0.76793522347985699</v>
+      </c>
+      <c r="E177" s="3">
+        <v>0.71953717149554997</v>
+      </c>
+      <c r="F177" s="3">
+        <v>0.82331356127308697</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A178" s="7"/>
+      <c r="B178" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C178" s="3">
+        <v>0.457991484231488</v>
+      </c>
+      <c r="D178" s="3">
+        <v>0.62824987550993405</v>
+      </c>
+      <c r="E178" s="3">
+        <v>0.58812561009376596</v>
+      </c>
+      <c r="F178" s="3">
+        <v>0.67424988079722503</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A179" s="7"/>
+      <c r="B179" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C179" s="3">
+        <v>0.52567448982717802</v>
+      </c>
+      <c r="D179" s="3">
+        <v>0.68910438410322306</v>
+      </c>
+      <c r="E179" s="3">
+        <v>0.670332830165976</v>
+      </c>
+      <c r="F179" s="3">
+        <v>0.70895755921739301</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A180" s="7"/>
+      <c r="B180" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C180" s="3">
+        <v>0</v>
+      </c>
+      <c r="D180" s="3">
+        <v>0</v>
+      </c>
+      <c r="E180" s="3">
+        <v>0</v>
+      </c>
+      <c r="F180" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A181" s="7"/>
+      <c r="B181" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C181" s="3">
+        <v>0.45146433067042901</v>
+      </c>
+      <c r="D181" s="3">
+        <v>0.57773616149683304</v>
+      </c>
+      <c r="E181" s="3">
+        <v>0.54110710459733702</v>
+      </c>
+      <c r="F181" s="3">
+        <v>0.62736185862332206</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="13">
+    <mergeCell ref="A122:A136"/>
+    <mergeCell ref="A137:A151"/>
+    <mergeCell ref="A152:A166"/>
+    <mergeCell ref="A167:A181"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="A47:A61"/>
+    <mergeCell ref="A92:A106"/>
+    <mergeCell ref="A107:A121"/>
     <mergeCell ref="A62:A76"/>
     <mergeCell ref="A77:A91"/>
     <mergeCell ref="A2:A16"/>
     <mergeCell ref="A17:A31"/>
     <mergeCell ref="A32:A46"/>
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="A47:A61"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
